--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_6_13.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_6_13.xlsx
@@ -625,76 +625,76 @@
         <v>24</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.738649731982257</v>
+        <v>-1.704200504269892</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.1579458998987491</v>
+        <v>2.086936337141161</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.413096628943805</v>
+        <v>-3.544352923131257</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-10.26582770899635</v>
+        <v>-8.428559390427623</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.7958649803642</v>
+        <v>-0.4843660443549211</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.126420215905547</v>
+        <v>6.191574204418302</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.505005685124523</v>
+        <v>9.571110160404864</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.230331548820544</v>
+        <v>9.296793417901611</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.27466305188149</v>
+        <v>9.341112789273851</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.940623634511127</v>
+        <v>-3.873308010784633</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.4820924240311868</v>
+        <v>0.5491518715186459</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.355574678149353</v>
+        <v>4.42301500640675</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.38865956208749</v>
+        <v>7.457456490340327</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.170168231952196</v>
+        <v>7.239259843151942</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>6.515414379218562</v>
+        <v>6.585307575128333</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>11.26765659984499</v>
+        <v>11.33691105624916</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>6.979248329714324</v>
+        <v>7.048685404530218</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.441844050121922</v>
+        <v>-1.37226386480873</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>7.094323757360605</v>
+        <v>7.163709766158611</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.040094776478405</v>
+        <v>-0.9708994675005513</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>2.579697757504874</v>
+        <v>2.649572410526233</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-1.659673904344473</v>
+        <v>-1.589672641280835</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.779821885957219</v>
+        <v>2.849546698176631</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="7">
@@ -707,76 +707,76 @@
         <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.870280726803699</v>
+        <v>1.903341225841338</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.500057442907796</v>
+        <v>-9.469691168337746</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.412643826622812</v>
+        <v>-5.379351259485247</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-17.16774847233032</v>
+        <v>-17.13724203429611</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-17.53768724235924</v>
+        <v>-17.47771637753542</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.83186233826926</v>
+        <v>-11.76682920169833</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.549918675616659</v>
+        <v>-1.483885319012231</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.827868584239482</v>
+        <v>-1.761473740086551</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.786828282064754</v>
+        <v>-1.720441422565862</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>2.974782680782674</v>
+        <v>3.042129297107792</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.284827251573908</v>
+        <v>-2.217784234556355</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>2.971513964380812</v>
+        <v>3.03894557083445</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.223091673093819</v>
+        <v>-9.154363395919759</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.907734876592215</v>
+        <v>-3.838685595531942</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.565774580099394</v>
+        <v>-4.495919598111762</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-9.51576717139104</v>
+        <v>-9.446574579477449</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-4.108587776445432</v>
+        <v>-4.039180418257629</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.760056550226892</v>
+        <v>-9.690496258183941</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-9.547327589284293</v>
+        <v>-9.477972931988596</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.734349137214195</v>
+        <v>1.80354736402284</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-4.358483082975191</v>
+        <v>-4.288616770450041</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.116440530024377</v>
+        <v>1.186443236937698</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.716411802339934</v>
+        <v>-9.64669179522862</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-9.795321637425637</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="8">
@@ -789,158 +789,158 @@
         <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-9.856716310697166</v>
+        <v>-9.823754183965583</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.980568110622762</v>
+        <v>-3.948536658123572</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7.008313625740612</v>
+        <v>7.045433528477993</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.301744635929815</v>
+        <v>6.339448528856209</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.489087324673562</v>
+        <v>-6.42577801291786</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.126039030443451</v>
+        <v>6.191183880693316</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.249939804341061</v>
+        <v>2.315991477844229</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.246479556055164</v>
+        <v>-4.180104365747994</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.53846398021737</v>
+        <v>-13.47214740436512</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.089239115927235</v>
+        <v>-8.021953905255216</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.818280400394798</v>
+        <v>-7.751268525662205</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.099213441207766</v>
+        <v>-8.031834523316107</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.108078440504251</v>
+        <v>-6.039342157741821</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.09972883588898895</v>
+        <v>-0.03066912808507993</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-6.989478039455513</v>
+        <v>-6.919634595339538</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-3.280632884069099</v>
+        <v>-3.211425257642816</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-3.415485932668986</v>
+        <v>-3.346079405827552</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-9.759780729203271</v>
+        <v>-9.690223082761349</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.54710339357495</v>
+        <v>-9.47775092198102</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-9.363242819449624</v>
+        <v>-9.294062335192777</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-19.27531920097436</v>
+        <v>-19.20547066956738</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-16.23408916406738</v>
+        <v>-16.16410000455165</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-15.96445987287522</v>
+        <v>-15.89474262945792</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-16.04532163742832</v>
+        <v>-15.97546728971891</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.001879</t>
+          <t>X ≈ -0.001878</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>37</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.615725035995908</v>
+        <v>1.649726016415187</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.412792488132574</v>
+        <v>-1.378646746139395</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-5.567774243762592</v>
+        <v>-5.533190768131092</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.9276941353762282</v>
+        <v>-0.8908286886933183</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.452799118252543</v>
+        <v>9.522461745186533</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.586476456726146</v>
+        <v>1.653442755665885</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.7970246861792276</v>
+        <v>0.8649456285328796</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.17802872038078</v>
+        <v>-2.1097517576831</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.830730806374312</v>
+        <v>-4.762471419960562</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.933422017913323</v>
+        <v>-2.864186217708209</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.040271339224937</v>
+        <v>-7.971340998393423</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.632377796963098</v>
+        <v>-5.563061722811661</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.394998773666899</v>
+        <v>-1.324281669386814</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.315424980532889</v>
+        <v>-4.244411701025498</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-7.692322439837056</v>
+        <v>-7.620482021956974</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-7.084300258628673</v>
+        <v>-7.013123329006653</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.828747476328154</v>
+        <v>-1.757351504937333</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-5.712829470745042</v>
+        <v>-7.266544019106234</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-8.197516562719223</v>
+        <v>-9.745795187934554</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.08480277059592822</v>
+        <v>-1.457149694294991</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.4579024720182758</v>
+        <v>-2.016809480287577</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.166928719998054</v>
+        <v>2.236930410240568</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.442126031089074</v>
+        <v>2.511849552404279</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-5.741267583372235</v>
+        <v>-5.671413235666186</v>
       </c>
     </row>
     <row r="10">
@@ -950,79 +950,79 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.342499089404669</v>
+        <v>-1.626848882083422</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.267249813317143</v>
+        <v>-1.971497052815941</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.160466885029635</v>
+        <v>-4.84355137661322</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.7893176096591858</v>
+        <v>0.02867424526066742</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9998047109741108</v>
+        <v>-0.9168557021558286</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6171573870711171</v>
+        <v>0.6748052578639587</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.514754395615221</v>
+        <v>5.50305216395931</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.4609434473496421</v>
+        <v>-0.385622546566708</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.000112411257717</v>
+        <v>1.057024279107267</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.641192739528506</v>
+        <v>-2.530306225976041</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.9394642215435454</v>
+        <v>-0.8517935293655796</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.222603296958034</v>
+        <v>-1.132475812189206</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.223568415675892</v>
+        <v>-5.076246839586908</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.174878075312535</v>
+        <v>-1.086228647534789</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.431785933147566</v>
+        <v>-0.3498190503470084</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.67268136464449</v>
+        <v>-2.559595122665868</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.04364694368988609</v>
+        <v>0.1170603296417596</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.06973917797598972</v>
+        <v>0.008002161762910021</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.4181064475241101</v>
+        <v>-1.180380333601569</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.2278816300076869</v>
+        <v>-0.9905700246299318</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.6477342402082655</v>
+        <v>-0.134275410244399</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.5715789326111178</v>
+        <v>-0.2101213716535</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.2806235939484552</v>
+        <v>-0.4944586294342415</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>1.633249791144529</v>
+        <v>0.8379129919705122</v>
       </c>
     </row>
     <row r="11">
@@ -1032,79 +1032,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.218118549291972</v>
+        <v>2.206625251189386</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.865367880080335</v>
+        <v>1.864695511206101</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.560186053648408</v>
+        <v>-6.707126002759217</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.862849329222009</v>
+        <v>-5.066143897225523</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-4.232283470932899</v>
+        <v>-5.404308536175527</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-4.038796007779666</v>
+        <v>-5.209626309265907</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.684466668518318</v>
+        <v>-9.38376782138409</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.975452820819186</v>
+        <v>-9.662901299438225</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-7.509002687508229</v>
+        <v>-7.252946491770203</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-10.73554462299666</v>
+        <v>-10.39668542536479</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.596341545396037</v>
+        <v>-5.381525365023691</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.850714489534965</v>
+        <v>3.831816926262995</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.136876114351161</v>
+        <v>5.087019353630716</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.91523608914283</v>
+        <v>4.867681459858332</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6.673188899491272</v>
+        <v>6.588623236644473</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.411819491919907</v>
+        <v>2.431096889208291</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.595439275671545</v>
+        <v>-2.456442383988737</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>4.602266543325186</v>
+        <v>4.572024193407927</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.823552377660953</v>
+        <v>4.789030301606651</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>7.455740791597904</v>
+        <v>7.35651232109214</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>9.338179614564019</v>
+        <v>9.19657312224799</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.386550783292641</v>
+        <v>4.360342802754282</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.670555938005712</v>
+        <v>4.634696802645152</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>3.619312508914561</v>
+        <v>2.179294615042281</v>
       </c>
     </row>
     <row r="12">
@@ -1117,76 +1117,76 @@
         <v>56</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12.33074787912776</v>
+        <v>12.35987603446801</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.22195579276346</v>
+        <v>10.25547405398414</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10.56688912677086</v>
+        <v>10.60543557098722</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.306967112618274</v>
+        <v>6.344972712188692</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.721323985126347</v>
+        <v>7.786845220966143</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.909105753610632</v>
+        <v>7.971805469488444</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.807363588329714</v>
+        <v>1.872268442784666</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.583888925240103</v>
+        <v>-5.513734584406549</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.985276240456798</v>
+        <v>-1.917367876991591</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.362873742162868</v>
+        <v>4.427731063863064</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.857195762853522</v>
+        <v>2.922754059839924</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.141060386479666</v>
+        <v>6.20469424532719</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.584220828395082</v>
+        <v>8.647585891285239</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>8.365742878673721</v>
+        <v>8.429458241704225</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>9.493696174388198</v>
+        <v>9.557610154075071</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>6.524288390887413</v>
+        <v>6.589523092228305</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>8.17625893396324</v>
+        <v>8.240587291417654</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>11.63943887875375</v>
+        <v>11.70543525435731</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.503425988993051</v>
+        <v>6.572872931308005</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>4.907706634156739</v>
+        <v>4.976966214308987</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>6.151336217889671</v>
+        <v>6.221261560547852</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>6.077273106788006</v>
+        <v>6.145436358878676</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>6.352048273269737</v>
+        <v>6.419786512919913</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>8.061821219715959</v>
+        <v>8.131675567423237</v>
       </c>
     </row>
     <row r="13">
@@ -1196,79 +1196,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.270589414541789</v>
+        <v>-4.187913023039322</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.80611047322494</v>
+        <v>1.822329615957294</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.759721453790974</v>
+        <v>6.726933630071329</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.24603552024589</v>
+        <v>9.188167108760013</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>13.16414661288904</v>
+        <v>13.08723029129274</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11.22076222463136</v>
+        <v>11.15897069483329</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.22245193534085</v>
+        <v>7.205474854783326</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>9.078763620702503</v>
+        <v>9.044331285420355</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6.97879651087888</v>
+        <v>6.969477827093172</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.046810871785794</v>
+        <v>4.073187934340019</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.76346390508574</v>
+        <v>10.71184251521687</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.050056299121785</v>
+        <v>4.073098331552018</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.20044045544747</v>
+        <v>7.187052551699203</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.905951776711412</v>
+        <v>5.906327103240187</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>5.231997017426714</v>
+        <v>5.243039775851891</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>5.83852019266525</v>
+        <v>5.843332612774077</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>7.855025994050024</v>
+        <v>7.835626861915401</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.596786386945396</v>
+        <v>5.606096484330195</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>6.890569636813318</v>
+        <v>6.888012658674477</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.648887922163937</v>
+        <v>6.016400611742327</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>7.176964729066178</v>
+        <v>6.533539051155167</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>5.393171605640696</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>8.022555185712768</v>
+        <v>6.735626286581635</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>9.021882663648377</v>
+        <v>8.359639093259098</v>
       </c>
     </row>
     <row r="14">
@@ -1278,79 +1278,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-6.038840884992126</v>
+        <v>-6.443477210350004</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.7422913874710915</v>
+        <v>-1.203359406323806</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.066156839510953</v>
+        <v>-4.508414622948322</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.789272484793401</v>
+        <v>1.809167285080463</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.243079578168071</v>
+        <v>4.263361743104468</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.433754585214899</v>
+        <v>4.448547491815866</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.536959158323839</v>
+        <v>5.54139054731808</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7.13781858777827</v>
+        <v>7.128408512586432</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.536552242141234</v>
+        <v>1.588543180113525</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.066572018128653</v>
+        <v>-1.973419623807914</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.09310489319603477</v>
+        <v>0.1609630685050121</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1871931119060406</v>
+        <v>-0.117307028190254</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.507070404630184</v>
+        <v>1.557996087477221</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.254016115712481</v>
+        <v>-6.120661037401042</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.3233419290740187</v>
+        <v>-0.2506243207271837</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.219080612796212</v>
+        <v>1.275818940201624</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>6.745898315600016</v>
+        <v>6.741994943688496</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.865114705825277</v>
+        <v>2.905380328789462</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.252631538096594</v>
+        <v>0.3203755789366838</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.385603317868458</v>
+        <v>1.441461922501176</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.4591580815680842</v>
+        <v>-0.03517967541998246</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>1.326599252340358</v>
+        <v>0.8235538024232483</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.54477064523779</v>
+        <v>2.032607954157854</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.52543307955402</v>
+        <v>1.022196261682026</v>
       </c>
     </row>
     <row r="15">
@@ -1363,76 +1363,76 @@
         <v>133</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.393869336767366</v>
+        <v>3.021737195604132</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.560754148456297</v>
+        <v>1.189100904027093</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.098925929270919</v>
+        <v>3.134280352939406</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.129867982853114</v>
+        <v>3.165151283921148</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.26877461999652</v>
+        <v>1.333626089025607</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7113770056586759</v>
+        <v>0.7760323409258021</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3972414101395927</v>
+        <v>-0.7544409688436033</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.246957126999163</v>
+        <v>-4.033806464641529</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.2069192469122285</v>
+        <v>-1.000494062532418</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.9781789962699179</v>
+        <v>-1.786237006420173</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.205976792407363</v>
+        <v>-2.570537169475017</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.735135818425803</v>
+        <v>-1.665131653333972</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.360601058294122</v>
+        <v>-4.285814211486944</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.080911110318183</v>
+        <v>-3.007414426378318</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.491811649382733</v>
+        <v>-4.415461060444756</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-3.146961110518617</v>
+        <v>-3.07312208507895</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-4.785965497344186</v>
+        <v>-4.710049523872343</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-3.38718951494306</v>
+        <v>-3.313919254734799</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.419186652763116</v>
+        <v>-2.347917147167777</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.7753759398496243</v>
+        <v>0.8443497760761502</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.9840552300999619</v>
+        <v>1.053991851528615</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.59565922403889</v>
+        <v>-0.525613508376729</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.3208840575569312</v>
+        <v>-0.2511387958948461</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.858813700919136</v>
+        <v>1.928668048626413</v>
       </c>
     </row>
     <row r="16">
@@ -1445,76 +1445,76 @@
         <v>179</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.324997225933224</v>
+        <v>4.058144795008268</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.759356459251961</v>
+        <v>1.793029467865303</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.518796200325674</v>
+        <v>2.554150623994161</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.468406181289424</v>
+        <v>3.503603861286919</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>6.201930556605269</v>
+        <v>5.95380661732753</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.589796621413619</v>
+        <v>5.033893523240337</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.579811549054625</v>
+        <v>2.014772895645116</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>2.295746976506415</v>
+        <v>1.724311955470085</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.656282199730022</v>
+        <v>2.082734215442521</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.666586470456572</v>
+        <v>4.406331022734115</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.4837719764954613</v>
+        <v>0.2275802782904393</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.7620193839976324</v>
+        <v>0.5050495393464871</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.598522611406842</v>
+        <v>-2.525260574677141</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.822564251984559</v>
+        <v>-2.748438616761902</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6941439268481133</v>
+        <v>-0.6224209488338133</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.213396821564793</v>
+        <v>-1.141510618793092</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.779330424023478</v>
+        <v>1.514807615426946</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>2.23300622580517</v>
+        <v>1.96716056827362</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.331810952982913</v>
+        <v>1.067354853890471</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.96019553072626</v>
+        <v>0.6983979588801503</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.534313557482363</v>
+        <v>1.604250178911016</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.458358501839882</v>
+        <v>1.528404217502043</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.733133668322012</v>
+        <v>1.802878929984097</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.215851546930637</v>
+        <v>2.285705894637914</v>
       </c>
     </row>
     <row r="17">
@@ -1527,76 +1527,76 @@
         <v>257</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.753708310270753</v>
+        <v>1.786982602589582</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6424137656159701</v>
+        <v>0.6760867742293115</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.79851272019107</v>
+        <v>-0.7631582965225832</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.2556235874115558</v>
+        <v>0.07529735100045087</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.2774557931247799</v>
+        <v>0.1276658006249107</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.791239402968245</v>
+        <v>2.642458905198076</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.022144614361096</v>
+        <v>1.869449878197543</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.461200154345896</v>
+        <v>4.527935406261328</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.891114609415794</v>
+        <v>4.957820978223296</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.674366241270256</v>
+        <v>5.739559552720145</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.562372024222348</v>
+        <v>5.624985095869469</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.839467526625313</v>
+        <v>6.898179289852408</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.10804821089075</v>
+        <v>6.166479829593989</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.500825738669526</v>
+        <v>5.560884681629403</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4.844390690263843</v>
+        <v>4.906253833613242</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>3.49592960694487</v>
+        <v>3.559551675194001</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.6381005042356378</v>
+        <v>0.7064038411300331</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.9222221465061153</v>
+        <v>0.99104309195355</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.083870601266725</v>
+        <v>3.152054669815321</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.438229571984429</v>
+        <v>4.507511952381158</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>4.28413422135224</v>
+        <v>4.354070842780892</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.542809515904175</v>
+        <v>6.612855231566336</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.704744215460238</v>
+        <v>3.774489477122323</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.294172525997226</v>
+        <v>1.364026873704503</v>
       </c>
     </row>
     <row r="18">
@@ -1609,814 +1609,814 @@
         <v>268</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.777692667562938</v>
+        <v>-4.744418375244109</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6491092761166968</v>
+        <v>-0.6154362675033553</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.570754987422518</v>
+        <v>-3.535400563754031</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.294039392053236</v>
+        <v>1.33023310947214</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.675410693063029</v>
+        <v>-1.609737663167351</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.7408189917974539</v>
+        <v>0.8062935947837246</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.02730712982859984</v>
+        <v>0.03908492132134711</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.4394805453760995</v>
+        <v>0.5062157972915315</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.12155431110881</v>
+        <v>-2.054847942301308</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.6611821939294984</v>
+        <v>-0.5935141600785201</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.131860652808349</v>
+        <v>-1.063908086684656</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6666682268346094</v>
+        <v>-0.5992407986457735</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.044107784044947</v>
+        <v>-0.9743942889127695</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2257928623595191</v>
+        <v>0.2938107346008678</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.924392451137962</v>
+        <v>-1.851379146416626</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-3.19580626621849</v>
+        <v>-3.120553983342873</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-4.449302945442042</v>
+        <v>-4.373843967158855</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.300555018253739</v>
+        <v>-5.225859784939686</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.711297526963719</v>
+        <v>-4.639622481015593</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-6.389925373134332</v>
+        <v>-6.320642992737604</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-5.813722797057657</v>
+        <v>-5.743786175629005</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-5.516543524342055</v>
+        <v>-5.446497808679894</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-5.241768357859925</v>
+        <v>-5.17202309619784</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-5.317709697128393</v>
+        <v>-5.247855349421116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0001363</t>
+          <t>X ≈ -0.0001364</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>327</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.586187627170766</v>
+        <v>2.619461919489595</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.926968777623642</v>
+        <v>-2.893295769010301</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.61741873836737</v>
+        <v>-1.582064314698883</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.551461193552534</v>
+        <v>-3.51526747613363</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.221494080248014</v>
+        <v>-4.155821050352337</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.515500355992501</v>
+        <v>-2.45002575300623</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.0682162039111418</v>
+        <v>0.1346082550610888</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8176706302226364</v>
+        <v>-0.7509353783072044</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4440945767920681</v>
+        <v>0.5108009455995699</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.197095054056469</v>
+        <v>1.263695336763938</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.5572636765555288</v>
+        <v>0.6234656739114328</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.298224446261827</v>
+        <v>-4.224536239881004</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.896099597405822</v>
+        <v>-3.819494768924166</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.508197054077741</v>
+        <v>-3.431912197527637</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.251558473541465</v>
+        <v>-3.17442720575503</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.352545505800393</v>
+        <v>-2.277227118784914</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.321501585270418</v>
+        <v>-4.244220730917725</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.120674603812191</v>
+        <v>-4.045625880486902</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.987120248219817</v>
+        <v>-2.915689704164635</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.576834862385354</v>
+        <v>-1.507552481988625</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.814224873829694</v>
+        <v>-1.744288252401041</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.72504231479347</v>
+        <v>-3.654996599131309</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.144456750757818</v>
+        <v>-3.074711489095733</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.302966897365742</v>
+        <v>-2.233112549658465</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 3.79e-05</t>
+          <t>X ≈ 3.779e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>292</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.974387332933048</v>
+        <v>-2.941113040614219</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5790036726557233</v>
+        <v>-0.5453306640423818</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.009549041665686</v>
+        <v>-1.974194617997199</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.021141607620102</v>
+        <v>-0.9849478902011981</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.727194858157247</v>
+        <v>-1.66152182826157</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.273450387283489</v>
+        <v>-4.207975784297219</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.3140407640891</v>
+        <v>-2.247648712939153</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8855310181096812</v>
+        <v>-0.8187957661942491</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5208354892920397</v>
+        <v>0.5875418580995415</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.9317283734641961</v>
+        <v>-0.8640797817518902</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3161760929463426</v>
+        <v>-0.2492366740768404</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.455673242634489</v>
+        <v>1.519861779486149</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.727161506539822</v>
+        <v>2.788478099086554</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.140005943104683</v>
+        <v>1.206279839039929</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.228798471367611</v>
+        <v>-1.154279742683002</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-2.00484327296558</v>
+        <v>-1.92792356332648</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.454005460265186</v>
+        <v>-1.379419271837882</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.586386136634445</v>
+        <v>-2.511172087142278</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-3.055194480551982</v>
+        <v>-2.982865251212637</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-4.238013698630141</v>
+        <v>-4.168731318233412</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-4.438748354203511</v>
+        <v>-4.368811732774859</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-3.829771902996725</v>
+        <v>-3.759726187334564</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.554996736514596</v>
+        <v>-3.485251474852511</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-5.34326684290636</v>
+        <v>-5.273412495199082</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0002122</t>
+          <t>X ≈ 0.000212</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.2928455256441822</v>
+        <v>0.1420283136776632</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.345620654873038</v>
+        <v>2.204790864271594</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.69419389294498</v>
+        <v>1.958063537015619</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.9832592866213474</v>
+        <v>1.247995744929533</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.007499440126487</v>
+        <v>3.311318927156748</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.4110172635250251</v>
+        <v>0.7034736008487101</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.4313626000400532</v>
+        <v>0.7279059340180822</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.247046310296497</v>
+        <v>0.04822417692085423</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.002639950483186</v>
+        <v>-0.7106054228013221</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3557829608358318</v>
+        <v>-0.2869816909596707</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.074363222961217</v>
+        <v>-2.012139697059034</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.754450951885794</v>
+        <v>-2.69209702854603</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.282900023693962</v>
+        <v>-4.219090866492593</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.308895691145523</v>
+        <v>-5.004638046426564</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.3782654722775618</v>
+        <v>-0.06459170447610774</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.3390898483080491</v>
+        <v>-0.2719520868519751</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3268164575430745</v>
+        <v>0.3938919135869412</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.421833041447748</v>
+        <v>1.489330190106244</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.3620437956203943</v>
+        <v>-0.3013234874207456</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.5749999999999602</v>
+        <v>-0.2695730412899735</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.118200408997957</v>
+        <v>-0.8121192092560037</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.7941554646405677</v>
+        <v>-0.4863587449622884</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.9193802981584369</v>
+        <v>-0.6134904581830938</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.1953216374269076</v>
+        <v>0.1138901399992491</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0003864</t>
+          <t>X ≈ 0.0003862</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.5719169139185354</v>
+        <v>0.8190865732738715</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.7013028619050417</v>
+        <v>-0.4493288179806427</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.441718079789254</v>
+        <v>4.197035817697277</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.846070014296139</v>
+        <v>1.611043294113607</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1.009338539861091</v>
+        <v>0.8059960442814287</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.154151951946993</v>
+        <v>-1.3466739810478</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.922138966358332</v>
+        <v>-2.113747703273155</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.197588718831703</v>
+        <v>-2.388856899693927</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.154298429211728</v>
+        <v>-2.345597004446425</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.047166199979898</v>
+        <v>-1.24636053300847</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.3018458331574436</v>
+        <v>-0.5034872918947784</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.831170945517087</v>
+        <v>0.6215450315132003</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.534492040783633</v>
+        <v>2.307719131701781</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.729745568750189</v>
+        <v>3.492194695443963</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>2.130001045466798</v>
+        <v>1.903864749339206</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.668457321503276</v>
+        <v>3.435411951269458</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.590967400939199</v>
+        <v>2.366845865253893</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>5.316172664089265</v>
+        <v>5.077417134191293</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>7.890786393058811</v>
+        <v>7.643586805170493</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.360849056603833</v>
+        <v>3.135596934387394</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>5.176139213643559</v>
+        <v>4.940468606796848</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>4.156787931585846</v>
+        <v>3.925655509237508</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.488166871652886</v>
+        <v>3.261163085569379</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>2.940527419176874</v>
+        <v>2.715847264270991</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005606</t>
+          <t>X ≈ 0.0005604</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>186</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.230234495919746</v>
+        <v>2.263508788238575</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2395901856989937</v>
+        <v>-0.2059171770856523</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.138943044954864</v>
+        <v>3.174297468623351</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.022947724444123</v>
+        <v>4.059141441863027</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4499977675561198</v>
+        <v>0.5156707974517971</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.770468860148434</v>
+        <v>2.835943463134704</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.07331910776162</v>
+        <v>3.139711158911567</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>7.606956063733477</v>
+        <v>7.673691315648909</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.116991704019355</v>
+        <v>7.183698072826857</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>7.949010410265139</v>
+        <v>8.01663651380558</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>9.306026238734347</v>
+        <v>9.361041786079419</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>7.433690172670197</v>
+        <v>7.481809015171464</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.857723622038314</v>
+        <v>6.899526184773826</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.18304518171437</v>
+        <v>7.21731251370241</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>5.994882360135087</v>
+        <v>6.037580413325152</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>7.127576818358612</v>
+        <v>7.173767433939702</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>7.048810165250742</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.275596482307961</v>
+        <v>5.340624120414844</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.491719645239776</v>
+        <v>5.561200011288911</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>9.979838709677352</v>
+        <v>10.04912109007408</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>9.974272709281614</v>
+        <v>10.04420933071027</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>10.43595206224116</v>
+        <v>10.50599777790332</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>9.635458411518989</v>
+        <v>9.705203673181074</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>9.559517072250493</v>
+        <v>9.629371419957771</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007349</t>
+          <t>X ≈ 0.0007346</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>149</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.342595101355869</v>
+        <v>-6.30932080903704</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.324671471031579</v>
+        <v>3.35834447964492</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.217882892635053</v>
+        <v>1.25323731630354</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.162946575570103</v>
+        <v>-2.1267528581512</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.528285639658826</v>
+        <v>-2.462612609763148</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.674500546028604</v>
+        <v>-3.609025943042333</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.115060984209478</v>
+        <v>-7.048668933059531</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.392472525159953</v>
+        <v>-3.325737273244521</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.350592745047393</v>
+        <v>-1.283886376239892</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.124497434881611</v>
+        <v>-2.056871331341171</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.18551536045544</v>
+        <v>-3.116537603879344</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.131225210896808</v>
+        <v>-2.061803569353735</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.262886576297966</v>
+        <v>-3.185277392001204</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.49283719665786</v>
+        <v>-3.406564105641948</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-3.087170032157616</v>
+        <v>-3.402833309677661</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.4786871637442829</v>
+        <v>-0.8050589391333602</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-3.968485555879788</v>
+        <v>-4.293256007927759</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-4.073468971975068</v>
+        <v>-4.410271504582454</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.515063929848623</v>
+        <v>-2.445583563799488</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.656879194630868</v>
+        <v>-1.587596814234139</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.1866567848368774</v>
+        <v>-0.1167201634082247</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.9337527800768015</v>
+        <v>-0.8637070644146405</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.6589776135946721</v>
+        <v>-0.5892323519325871</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.748341771655049</v>
+        <v>-2.678487423947772</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.0009092</t>
+          <t>X ≈ 0.0009089</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.26141828002757</v>
+        <v>2.779184382630973</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.943175364172667</v>
+        <v>1.595399710265454</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.203878899270279</v>
+        <v>1.872530267533634</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.937458231115649</v>
+        <v>5.503135303209028</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8.002628492340563</v>
+        <v>8.627628295228661</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>7.345940830301544</v>
+        <v>7.963444875026937</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.404227524201438</v>
+        <v>8.029795403734973</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>8.001273776458802</v>
+        <v>8.634859549533076</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.603883495837671</v>
+        <v>5.207496337746925</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.260488131317253</v>
+        <v>7.89486412627744</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.007562660624089</v>
+        <v>8.162498571588905</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>10.78760932984103</v>
+        <v>10.4736074358574</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>13.99220475637298</v>
+        <v>13.66187843986749</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>11.21443651352167</v>
+        <v>10.82952397286968</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>14.00378113655338</v>
+        <v>13.27328739848725</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>14.59884118617466</v>
+        <v>14.38616936161841</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>16.18888542306027</v>
+        <v>16.01952687140096</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>16.08390200696505</v>
+        <v>15.94371910254785</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>13.71381827334508</v>
+        <v>13.55091483129822</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>9.590517241379359</v>
+        <v>9.389934554309818</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>10.77145476341584</v>
+        <v>10.58651882112635</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>10.69549970777323</v>
+        <v>10.51067285971725</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>11.83234383977256</v>
+        <v>11.6547127895906</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>13.48054043153861</v>
+        <v>13.3180109711499</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.001084</t>
+          <t>X ≈ 0.001083</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>8.312798556877674</v>
+        <v>7.702656823575936</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>3.800315868974742</v>
+        <v>4.271587374307479</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.335701047990476</v>
+        <v>2.80896202606386</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-5.704989389670672</v>
+        <v>-6.192213778155697</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-11.32511228379882</v>
+        <v>-11.72813548429887</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-12.16566489284131</v>
+        <v>-12.55822966565562</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-14.04099131763897</v>
+        <v>-14.4210576146377</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-21.65059548044186</v>
+        <v>-21.95402627723858</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-14.2655727196859</v>
+        <v>-14.64547872786984</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-13.97847176587511</v>
+        <v>-14.36852563750217</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-7.400780203524739</v>
+        <v>-7.856769144946476</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-5.57876334192126</v>
+        <v>-6.056286264929902</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-7.198525879478389</v>
+        <v>-8.237519197927774</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.685744974681626</v>
+        <v>-5.370507523193197</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-6.449939371613688</v>
+        <v>-7.090822736784339</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-9.012774058834268</v>
+        <v>-9.596829515628727</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-7.041604595088515</v>
+        <v>-7.078548360454761</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-8.199219590131257</v>
+        <v>-7.625121477162288</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-4.825201690357247</v>
+        <v>-4.28423009623787</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.532894736842138</v>
+        <v>-2.014050952936628</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-2.023463566892723</v>
+        <v>-1.514930454236001</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-4.204681780430008</v>
+        <v>-3.674109748978367</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.877275035000508</v>
+        <v>-2.357968369829706</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.8479532163742434</v>
+        <v>-0.3504672897195391</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.001258</t>
+          <t>X ≈ 0.001257</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>85</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.443525653072733</v>
+        <v>0.4767999453915621</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.068120449806884</v>
+        <v>-1.034447441193542</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.374532027283479</v>
+        <v>3.409886450951966</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8686730506155911</v>
+        <v>-0.8324793331966873</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.118998340830977</v>
+        <v>1.184671370726655</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.306162953837728</v>
+        <v>1.371637556823998</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.886237998254259</v>
+        <v>2.952630049404206</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.431212764500444</v>
+        <v>1.497948016415876</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.8256700059937</v>
+        <v>3.892376374801202</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4775771694816555</v>
+        <v>-0.4099510659412147</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.556159078836899</v>
+        <v>-2.488832600249872</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.658782394076511</v>
+        <v>-1.591111415462578</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-6.312685377269531</v>
+        <v>-6.243685247024573</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.004630423598044</v>
+        <v>-2.935352358765321</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.1341498979294258</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.7155604365433703</v>
+        <v>-0.6461675579322943</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-3.202595307162888</v>
+        <v>-3.133025871380362</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-4.484049311493422</v>
+        <v>-4.414337163436798</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-3.091455560326352</v>
+        <v>-3.021975194277218</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.551470588235361</v>
+        <v>-0.4821882078386324</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.271141585468513</v>
+        <v>-2.20120496403986</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.347096641111193</v>
+        <v>-2.277050925449032</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-3.248792062864283</v>
+        <v>-3.179046801202198</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.9717922256622273</v>
+        <v>-0.9019378779549498</v>
       </c>
     </row>
     <row r="28">
@@ -2429,76 +2429,76 @@
         <v>42</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.849688118058729</v>
+        <v>5.882962410377559</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-6.390249301347431</v>
+        <v>-6.35657629273409</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6870926225764933</v>
+        <v>-0.6517381989080064</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.9800664451827217</v>
+        <v>1.016260162601625</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.959943488739228</v>
+        <v>-3.894468885752957</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.02909514111150457</v>
+        <v>0.09548719226145153</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.51244525749771</v>
+        <v>4.579180509413142</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.553961322520273</v>
+        <v>4.620667691327775</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.780125911750844</v>
+        <v>3.847752015291285</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.05448517886618</v>
+        <v>4.121811657453208</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.394438894438899</v>
+        <v>1.462109873052832</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.650900056904206</v>
+        <v>2.719900187149165</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.33236151603505</v>
+        <v>-2.263083451202327</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-5.372245136024659</v>
+        <v>-5.302179129735194</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-0.0152803244985904</v>
+        <v>0.05411255411248561</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.1493740186474426</v>
+        <v>-0.07980458286491654</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.2543574347427224</v>
+        <v>-0.1846452866860986</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-9.562043795620433</v>
+        <v>-9.492563429571298</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-4.61309523809517</v>
+        <v>-4.543812857698441</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-9.918200408997954</v>
+        <v>-9.848263787569302</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-5.232250702735875</v>
+        <v>-5.162204987073714</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-7.338427917206047</v>
+        <v>-7.268682655543962</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-5.033416875522136</v>
+        <v>-4.963562527814858</v>
       </c>
     </row>
     <row r="29">
@@ -2511,76 +2511,76 @@
         <v>48</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-7.840788072417467</v>
+        <v>-7.807513780098638</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.24070307960482</v>
+        <v>2.274376088218162</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.532330717814588</v>
+        <v>-7.496976294146101</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.253875968992283</v>
+        <v>4.290069686411186</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2780604826984643</v>
+        <v>-0.2123874528027869</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.174229203024979</v>
+        <v>-2.108754600038708</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.947095335079098</v>
+        <v>-2.880703283929151</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.225649980597659</v>
+        <v>-3.158914728682227</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.267467248908297</v>
+        <v>-5.200760880100795</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-8.124635993011061</v>
+        <v>-8.057009889470621</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.850276725895725</v>
+        <v>-7.782950247308698</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-8.129370629370626</v>
+        <v>-8.061699650756694</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-7.170528514524435</v>
+        <v>-7.101528384279476</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-7.391885325558675</v>
+        <v>-7.322607260725952</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-5.967483231262761</v>
+        <v>-5.897417224973296</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-5.372423181641381</v>
+        <v>-5.303030303030305</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.423183542456968</v>
+        <v>-3.353614106674442</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.528166958552248</v>
+        <v>-3.458454810495624</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-1.228710462287097</v>
+        <v>-1.159230096237962</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.041666666666664</v>
+        <v>-0.9723842862699357</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.668200408997954</v>
+        <v>-3.598263787569302</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-3.744155464640563</v>
+        <v>-3.674109748978402</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-3.469380298158434</v>
+        <v>-3.399635036496349</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-3.545321637426902</v>
+        <v>-3.475467289719624</v>
       </c>
     </row>
     <row r="30">
@@ -2593,322 +2593,322 @@
         <v>55</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.583212314841703</v>
+        <v>-4.549938022522873</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.100206011304216</v>
+        <v>-3.066533002690875</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-4.539906475390353</v>
+        <v>-4.504552051721866</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.071881606765373</v>
+        <v>-7.03568788934647</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.255333209971191</v>
+        <v>-9.189660180075514</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.249986778782613</v>
+        <v>-7.184512175796343</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.386489274472986</v>
+        <v>-4.320097223323039</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-8.301407556355173</v>
+        <v>-8.234672304439741</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-8.259891491332567</v>
+        <v>-8.193185122525065</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-9.033726902101968</v>
+        <v>-8.966100798561527</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-10.57754945316845</v>
+        <v>-10.51022297458142</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-18.12937062937063</v>
+        <v>-18.06169965075669</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-13.79931639331232</v>
+        <v>-13.73031626306736</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-19.47521865889218</v>
+        <v>-19.40594059405946</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-12.86142262520215</v>
+        <v>-12.79135661891269</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-15.90272621194435</v>
+        <v>-15.83333333333328</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-12.40045626972969</v>
+        <v>-12.33088683394717</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.414530594915888</v>
+        <v>-3.344818446859264</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-10.47113470471134</v>
+        <v>-10.4016543386622</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-13.92045454545455</v>
+        <v>-13.85117216505782</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-14.4636549544525</v>
+        <v>-14.39371833302385</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-12.72142819191324</v>
+        <v>-12.65138247625108</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-10.62847120724931</v>
+        <v>-10.55872594558723</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-12.52259436469963</v>
+        <v>-12.45274001699235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.001955</t>
+          <t>X ≈ 0.001954</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>40</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.174121405750824</v>
+        <v>-1.140847113431995</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.509296920395123</v>
+        <v>-6.475623911781781</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4489973844812525</v>
+        <v>-0.4136429608127656</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.16279069767438</v>
+        <v>-11.12659698025548</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-11.52806048269843</v>
+        <v>-11.46238745280275</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-8.840895869691678</v>
+        <v>-8.775421266705408</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.613762001745734</v>
+        <v>-4.547369950595787</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.392316647264259</v>
+        <v>-2.325581395348827</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.350800582241625</v>
+        <v>-2.284094213434123</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.624635993011097</v>
+        <v>-0.5570098894706561</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.850276725895718</v>
+        <v>-2.78295024730869</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.6293706293705839</v>
+        <v>-0.5616996507566512</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.75386184785777</v>
+        <v>-6.684861717612812</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.524781341107875</v>
+        <v>5.594059405940598</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.365850102070574</v>
+        <v>2.43591610836004</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.960910151691955</v>
+        <v>3.030303030303031</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.326816457543032</v>
+        <v>5.396385893325558</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>2.721833041447752</v>
+        <v>2.791545189504376</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.437956204379567</v>
+        <v>5.507436570428702</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.625</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.58179959100201</v>
+        <v>2.651736212430663</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.505844535359437</v>
+        <v>2.575890251021598</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.719380298158477</v>
+        <v>-4.649635036496392</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>2.704678362573134</v>
+        <v>2.774532710280411</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.002129</t>
+          <t>X ≈ 0.002128</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>17.1592119275826</v>
+        <v>17.19248621990143</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.32403641293827</v>
+        <v>4.357709421551611</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.448997384481324</v>
+        <v>-5.413642960812837</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.996124031007753</v>
+        <v>-1.959930313588849</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.971939517301536</v>
+        <v>6.037612547197213</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.992437463641679</v>
+        <v>2.057912066627949</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.55290466492108</v>
+        <v>9.619296716071027</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-7.392316647264266</v>
+        <v>-7.325581395348834</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.184133915574904</v>
+        <v>-3.117427546767402</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.957969326344333</v>
+        <v>-3.890343222803892</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.683610059228997</v>
+        <v>-3.616283580641969</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2039627039625884</v>
+        <v>0.2716336825765211</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.087195181191106</v>
+        <v>-5.018195050946147</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.308551992225517</v>
+        <v>-5.239273927392794</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-5.967483231262818</v>
+        <v>-5.897417224973353</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-9.539089848308045</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-13.83985020912364</v>
+        <v>-13.77028077334111</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-13.94483362521892</v>
+        <v>-13.8751214771623</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-17.89537712895376</v>
+        <v>-17.82589676290463</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-26.04166666666667</v>
+        <v>-25.97238428626994</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-14.08486707566456</v>
+        <v>-14.01493045423591</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-18.32748879797389</v>
+        <v>-18.25744308231173</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-18.05271363149176</v>
+        <v>-17.98296836982968</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-18.12865497076029</v>
+        <v>-18.05880062305302</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.002303</t>
+          <t>X ≈ 0.002302</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>22</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.416787685158297</v>
+        <v>5.450061977477127</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.5361576250593885</v>
+        <v>0.5698306336727299</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.73282079733698</v>
+        <v>12.76817522100547</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.928118393234676</v>
+        <v>2.96431211065358</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.982605937243953</v>
+        <v>-1.916932907348276</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.795441324237167</v>
+        <v>-1.729966721250896</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.568307456291194</v>
+        <v>-2.501915405141247</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.846862101809727</v>
+        <v>-2.780126849894295</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.350800582241597</v>
+        <v>-7.284094213434095</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-17.21554508392015</v>
+        <v>-17.14791898037971</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-16.94118581680488</v>
+        <v>-16.87385933821785</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-17.22027972027968</v>
+        <v>-17.15260874166575</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-13.79931639331232</v>
+        <v>-13.73031626306736</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.929764113437514</v>
+        <v>-4.860486048604791</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-14.67960444338397</v>
+        <v>-14.60953843709451</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-9.539089848308045</v>
+        <v>-9.469696969696969</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.673183542456968</v>
+        <v>-9.603614106674442</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-9.778166958552184</v>
+        <v>-9.70845481049556</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-5.01658925016595</v>
+        <v>-4.947108884116815</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.82954545454546</v>
+        <v>-4.760263074148732</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-14.4636549544525</v>
+        <v>-14.39371833302385</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-9.994155464640563</v>
+        <v>-9.924109748978402</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-5.173925752703894</v>
+        <v>-5.104180491041809</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-9.795321637426902</v>
+        <v>-9.725467289719624</v>
       </c>
     </row>
     <row r="34">
@@ -2921,76 +2921,76 @@
         <v>25</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.325878594249176</v>
+        <v>2.359152886568005</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>9.99070307960482</v>
+        <v>10.02437608821816</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-11.44899738448126</v>
+        <v>-11.41364296081277</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.162790697674446</v>
+        <v>-4.126596980255542</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-8.528060482698493</v>
+        <v>-8.462387452802815</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.340895869691707</v>
+        <v>-4.275421266705436</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-9.113762001745734</v>
+        <v>-9.047369950595787</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-9.392316647264266</v>
+        <v>-9.325581395348834</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.35080058224169</v>
+        <v>-13.28409421343419</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-18.12463599301106</v>
+        <v>-18.05700988947062</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-17.8502767258957</v>
+        <v>-17.78295024730867</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-18.12937062937063</v>
+        <v>-18.06169965075669</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.253861847857763</v>
+        <v>-3.184861717612804</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5247813411078752</v>
+        <v>0.5940594059405981</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.1341498979293689</v>
+        <v>-0.06408389163990336</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-7.539089848308045</v>
+        <v>-7.469696969696969</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.32681645754306</v>
+        <v>4.396385893325586</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>8.221833041447695</v>
+        <v>8.291545189504319</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.4379562043796241</v>
+        <v>0.5074365704287587</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-7.375</v>
+        <v>-7.305717619603271</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-3.918200408997926</v>
+        <v>-3.848263787569273</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-3.994155464640592</v>
+        <v>-3.924109748978431</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-3.719380298158406</v>
+        <v>-3.649635036496321</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-3.795321637426895</v>
+        <v>-3.725467289719617</v>
       </c>
     </row>
   </sheetData>
@@ -3180,83 +3180,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.002489</t>
+          <t>X &gt; -0.002488</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1788720737987006</v>
+        <v>0.1779805952714071</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2450760413599937</v>
+        <v>0.2440977346499551</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2746087839647657</v>
+        <v>0.2735608306564217</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3189654577690675</v>
+        <v>0.3178474641889295</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1484973808030219</v>
+        <v>0.1469782851936543</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.08534337043892748</v>
+        <v>0.08390277717244743</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1308935802020414</v>
+        <v>0.1293797528443434</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.07724082229319862</v>
+        <v>0.07578318489441926</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1358304338011465</v>
+        <v>0.1343034126786335</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1814561318032091</v>
+        <v>0.1798556492649084</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2353356403349522</v>
+        <v>0.233676831076103</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1816611874595893</v>
+        <v>0.1800585910015542</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.08581691478352127</v>
+        <v>0.08430049272586615</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.09038681566902085</v>
+        <v>0.08885881158695952</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.1932310544515232</v>
+        <v>0.1915641464099735</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.2108357247791801</v>
+        <v>0.2091611926580725</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.21365386075923</v>
+        <v>0.2119718540632221</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.2158753411200749</v>
+        <v>0.2141872603166348</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.2412935106966074</v>
+        <v>0.2395794275715559</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.2673248882265256</v>
+        <v>0.2655833628319755</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.2487644091296559</v>
+        <v>0.2470310307749486</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.2504016483925398</v>
+        <v>0.2486635605241361</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.125488436925103</v>
+        <v>0.1239048919899446</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.06740590658981205</v>
+        <v>0.06588889507918338</v>
       </c>
     </row>
     <row r="7">
@@ -3266,79 +3266,79 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3327</v>
+        <v>3331</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1927045124337425</v>
+        <v>0.1915417920258307</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2457045725878544</v>
+        <v>0.2308200022993674</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3156382188640237</v>
+        <v>0.3010690654480399</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3953210441839659</v>
+        <v>0.3808657063116527</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1366137551975299</v>
+        <v>0.1515271485707643</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.04176481790174336</v>
+        <v>0.03989673866932719</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.06327149107726626</v>
+        <v>0.06135167425490096</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.01121311642104672</v>
+        <v>0.009345404770677135</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.06990558173203709</v>
+        <v>0.06796795034350822</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2111916035169301</v>
+        <v>0.2090588698716829</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2335556094336226</v>
+        <v>0.2314038196769417</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1515518024951987</v>
+        <v>0.149487905330659</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.03313635465870135</v>
+        <v>0.03117658280610414</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.03931535369402894</v>
+        <v>0.03733986089420682</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.1476246824063097</v>
+        <v>0.1454969466833873</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.1310750692331766</v>
+        <v>0.1289852704947023</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1648488510643347</v>
+        <v>0.1627130353267532</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.2278336415077575</v>
+        <v>0.2256177097321341</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.1918577650038102</v>
+        <v>0.189690767071383</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2767562293605508</v>
+        <v>0.2744922754491981</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.2319497411521994</v>
+        <v>0.2297206155500788</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.2641803719469991</v>
+        <v>0.2619088528817812</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.1063408556877192</v>
+        <v>0.1042665241278939</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.01832428983489365</v>
+        <v>0.01635198377181979</v>
       </c>
     </row>
     <row r="8">
@@ -3348,79 +3348,79 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3309</v>
+        <v>3313</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1835789845223914</v>
+        <v>0.1822413423401485</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2987186905325316</v>
+        <v>0.2835242585841442</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3467984113145377</v>
+        <v>0.3319315966429741</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4908590469936485</v>
+        <v>0.4760440761670495</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.2327568249938494</v>
+        <v>0.247309334948639</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1063539048800024</v>
+        <v>0.1040443592327449</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.07204677756879363</v>
+        <v>0.06974716652136692</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.02121718732219335</v>
+        <v>0.0189665169371338</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.08000567527943048</v>
+        <v>0.07768463271971626</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1961584698237289</v>
+        <v>0.1936663954707711</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2472548815696527</v>
+        <v>0.2447106065698392</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1362120264559294</v>
+        <v>0.1337890710478149</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.08348754973259531</v>
+        <v>0.08108292739320433</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.06078616183701513</v>
+        <v>0.05839885824273949</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.1732642069530357</v>
+        <v>0.1707144226285493</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.183551092300938</v>
+        <v>0.1810106484903216</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1880951065177001</v>
+        <v>0.1855425198315785</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.2821648664854592</v>
+        <v>0.2794933666661734</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.2448361078195163</v>
+        <v>0.2422165583732436</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.26882734681557</v>
+        <v>0.2661847017714649</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.2569203639489004</v>
+        <v>0.2542693849276816</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.2595443239429542</v>
+        <v>0.2568857261347191</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.1597737803914114</v>
+        <v>0.1572448669436</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.07170767656523225</v>
+        <v>0.06928067285206652</v>
       </c>
     </row>
     <row r="9">
@@ -3430,161 +3430,161 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3277</v>
+        <v>3281</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.281622759147659</v>
+        <v>0.279831057927403</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3405060502020305</v>
+        <v>0.3248000736815726</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2817485221288081</v>
+        <v>0.2664539795083414</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.4341155807605261</v>
+        <v>0.4188575651990334</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2983958279811461</v>
+        <v>0.3123927836324967</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04757150511863273</v>
+        <v>0.04467573238522249</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.05077958902539592</v>
+        <v>0.04783926711193942</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.06289136974150011</v>
+        <v>0.05992057614039226</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2129904262638362</v>
+        <v>0.2098378254008182</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2770656174416857</v>
+        <v>0.2737943593912888</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3260150674173445</v>
+        <v>0.3226963829281004</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2166311948920665</v>
+        <v>0.2134294108892192</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1439483711203238</v>
+        <v>0.1407761924722379</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.06235359544313468</v>
+        <v>0.05926754936205469</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.2432085926366128</v>
+        <v>0.2398674761411925</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.2173789492566414</v>
+        <v>0.214097496706195</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2232841798329233</v>
+        <v>0.2199868665615696</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.3802247563426633</v>
+        <v>0.3767292479163018</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.3404546809182705</v>
+        <v>0.3370166069472589</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.3628847912221858</v>
+        <v>0.3594269770481731</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.4476532495386323</v>
+        <v>0.4440626436121846</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.4206051331026472</v>
+        <v>0.4170416369491008</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.3172273894559652</v>
+        <v>0.3138018922056602</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.2290909350479282</v>
+        <v>0.2257670900426376</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.001792</t>
+          <t>X &gt; -0.001791</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3240</v>
+        <v>3244</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2663876405540222</v>
+        <v>0.2642064853429176</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3605282865965975</v>
+        <v>0.3442290293946897</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3485486277886807</v>
+        <v>0.3326028252736535</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.4496671114694948</v>
+        <v>0.4337954170467597</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.1938548027527318</v>
+        <v>0.2073457578687794</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.02999759054780071</v>
+        <v>0.02632666337739664</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.04225765427394634</v>
+        <v>0.03851961995638931</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.08848212385709076</v>
+        <v>0.08466714714886336</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2705884773773022</v>
+        <v>0.2665503537850284</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3137285935244449</v>
+        <v>0.3095851366270139</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4215559924314647</v>
+        <v>0.4172954529370045</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2834254333792998</v>
+        <v>0.2793141741280962</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1615227675268471</v>
+        <v>0.157486161920076</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1123467458477947</v>
+        <v>0.1083539033276324</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.3338303976370796</v>
+        <v>0.329520044399402</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.3007623229269427</v>
+        <v>0.2965288069871335</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.246717874671802</v>
+        <v>0.2425397394794047</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.449805931158167</v>
+        <v>0.4639059158817247</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.4520178512168798</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.3660604192355166</v>
+        <v>0.3801462547422716</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.4579944722848097</v>
+        <v>0.4721305439156041</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.400662548931308</v>
+        <v>0.3962845825065031</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.2929615716348408</v>
+        <v>0.2887316815313881</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.2972709551656934</v>
+        <v>0.2930283946206984</v>
       </c>
     </row>
     <row r="11">
@@ -3594,79 +3594,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3170</v>
+        <v>3173</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3239971267045263</v>
+        <v>0.3065213076206632</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3964729134085729</v>
+        <v>0.3960464110010449</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4481167936868715</v>
+        <v>0.4484260047044657</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4421669427397603</v>
+        <v>0.4428605299357642</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.220213214727778</v>
+        <v>0.232501227034156</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.01703191680753946</v>
+        <v>0.01181611178314768</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.07858612234872453</v>
+        <v>-0.08375639978019933</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1006145497197082</v>
+        <v>0.09519049043716876</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2544791160613258</v>
+        <v>0.2488624720649284</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3789792223300239</v>
+        <v>0.3731313978135233</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4516100665571017</v>
+        <v>0.4456929687717022</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3166815883078868</v>
+        <v>0.3109048104434322</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2804364529603518</v>
+        <v>0.2745977418466481</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.140771268712534</v>
+        <v>0.1350842408981521</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.3507367519446305</v>
+        <v>0.3447211398065875</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.3664219627155845</v>
+        <v>0.3604382929642398</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2512020908133508</v>
+        <v>0.2453475044017068</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.4612785360917329</v>
+        <v>0.4741073550693784</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.456859796061984</v>
+        <v>0.4885448827712722</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.3791758588087006</v>
+        <v>0.4108178134675882</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.4538046351382334</v>
+        <v>0.4856996654867842</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.3968883701118813</v>
+        <v>0.4098537040776833</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.293234019091642</v>
+        <v>0.3062565829113382</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.2677698452229436</v>
+        <v>0.2808358933878452</v>
       </c>
     </row>
     <row r="12">
@@ -3676,79 +3676,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3129</v>
+        <v>3131</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2991780220940825</v>
+        <v>0.2810328484606899</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3772256479456217</v>
+        <v>0.3763455926654942</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5268449549974363</v>
+        <v>0.5444123299403216</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.4985765519281316</v>
+        <v>0.5167596631011335</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.2785552933829649</v>
+        <v>0.3081147722448918</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.07017635429814106</v>
+        <v>0.08185781784640511</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.0472819193236802</v>
+        <v>0.0409962286795178</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2326435564925049</v>
+        <v>0.2260879210263624</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3562057871851181</v>
+        <v>0.3494935728254163</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5246153609233133</v>
+        <v>0.5176003555182476</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.5308577546651421</v>
+        <v>0.5238607011317811</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2703743499089413</v>
+        <v>0.2636744339297152</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2168014174483517</v>
+        <v>0.2100427409859194</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.07821036822111438</v>
+        <v>0.07160002397181842</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.2678922207687222</v>
+        <v>0.2609639095072609</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.3396206528090957</v>
+        <v>0.3326619719670418</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2885022812978164</v>
+        <v>0.2815899749582087</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.4070182266329354</v>
+        <v>0.4191368960434474</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.3996420281343518</v>
+        <v>0.4308571192480954</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.2864500159693435</v>
+        <v>0.3176465680762703</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.3373906453151392</v>
+        <v>0.3688498778202316</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.3446109143942735</v>
+        <v>0.3568608768198089</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.235876972535074</v>
+        <v>0.2481938268497572</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.223853817990161</v>
+        <v>0.2553695036371266</v>
       </c>
     </row>
     <row r="13">
@@ -3758,79 +3758,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3073</v>
+        <v>3075</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.0799239016925668</v>
+        <v>0.06106041970738119</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1978228207052055</v>
+        <v>0.1964330093048972</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3438828744184192</v>
+        <v>0.3611871912415836</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3927288879519963</v>
+        <v>0.4106198482234475</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1429239732600891</v>
+        <v>0.1719167543169604</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.07267429534765313</v>
+        <v>-0.06182903369569459</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.01520753811171716</v>
+        <v>0.007646230634023254</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3386395926060786</v>
+        <v>0.3306180219383137</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3988751635430603</v>
+        <v>0.3907762528871217</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4546698778938989</v>
+        <v>0.4463914710735963</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4884643513268543</v>
+        <v>0.480173537526035</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1633914608598133</v>
+        <v>0.1554802519985756</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.06431997032404269</v>
+        <v>0.05638341857395801</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.07281528117209035</v>
+        <v>-0.0806081256844422</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.09976823072554453</v>
+        <v>0.09165913237041678</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.2269160015457103</v>
+        <v>0.21871588327285</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1447618411581217</v>
+        <v>0.1366456335852959</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2023271896922338</v>
+        <v>0.2135978039896003</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2884113409205256</v>
+        <v>0.3190025223455351</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.2022357723577315</v>
+        <v>0.2327939176082978</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.2314417510540991</v>
+        <v>0.2622693723786895</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.2401432662413114</v>
+        <v>0.2514429168213326</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.1244205479203231</v>
+        <v>0.1358005941928582</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.08102069905211096</v>
+        <v>0.1119310842641141</v>
       </c>
     </row>
     <row r="14">
@@ -3840,79 +3840,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2980</v>
+        <v>2981</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.215694954850207</v>
+        <v>0.195043480297187</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.14763129329436</v>
+        <v>0.1451635423390059</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.1436570395588035</v>
+        <v>0.16045583758509</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1164344192260458</v>
+        <v>0.1338370765057562</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2634430420035088</v>
+        <v>-0.2353423776775827</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4251204686221541</v>
+        <v>-0.4156549895768578</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2097165320031493</v>
+        <v>-0.2193232060214712</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.06587733266884754</v>
+        <v>0.05584813036927727</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.1935286248510408</v>
+        <v>0.183329775874256</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3425661488898797</v>
+        <v>0.332027543684454</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1678016135753211</v>
+        <v>0.1575378837511465</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.04209621590733548</v>
+        <v>0.03194583419313801</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1583844609231022</v>
+        <v>-0.1684682749898627</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2594009645221504</v>
+        <v>-0.2693944093204408</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.06039864080572954</v>
+        <v>-0.07077957292553805</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.05178875665507121</v>
+        <v>0.04135460431508164</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.09586049649923467</v>
+        <v>-0.1061266694885177</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.03397661742896219</v>
+        <v>0.043555913364969</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.08237083034400428</v>
+        <v>0.1118616458561306</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.001048305937601413</v>
+        <v>0.05041920132228483</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.01468549704231492</v>
+        <v>0.06451715842197103</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.03940158233930191</v>
+        <v>0.08930856702293966</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.1220648619168188</v>
+        <v>-0.07231199053861559</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.1980062011852866</v>
+        <v>-0.1481442437618909</v>
       </c>
     </row>
     <row r="15">
@@ -3925,76 +3925,76 @@
         <v>2874</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4463772092076468</v>
+        <v>0.442197869266991</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.1804537721256523</v>
+        <v>0.195369511548094</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2989250531918657</v>
+        <v>0.3342794768603525</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.0547361468008134</v>
+        <v>0.07146396157273927</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4296543842923697</v>
+        <v>-0.4028306660991845</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.6043274121526849</v>
+        <v>-0.5967509065946004</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.4216676882921746</v>
+        <v>-0.433796543393548</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.1949527901709587</v>
+        <v>-0.2074657043200858</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1439946988131879</v>
+        <v>0.1310132016732837</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4314209316678728</v>
+        <v>0.4178601278604077</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1705566074376108</v>
+        <v>0.1574103629548205</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.05055295520735115</v>
+        <v>0.03750256915312633</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2198104232573499</v>
+        <v>-0.2327451319084375</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.03830520738012666</v>
+        <v>-0.05154975754430069</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.05070066288074315</v>
+        <v>-0.0640838916399602</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.008736238648481276</v>
+        <v>-0.00460492384771527</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.3482009398125712</v>
+        <v>-0.3610845722755514</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.07044253266498401</v>
+        <v>-0.06299078546955172</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.07609120785904366</v>
+        <v>0.1040986010267559</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.05001739735560307</v>
+        <v>-0.001369793516317941</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.001707715887306449</v>
+        <v>0.06822890554134631</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.008073349122113882</v>
+        <v>0.06197236654004712</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.220424139494547</v>
+        <v>-0.1506788778324619</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.2615707675591139</v>
+        <v>-0.1917164198518364</v>
       </c>
     </row>
     <row r="16">
@@ -4007,76 +4007,76 @@
         <v>2741</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3033577079433556</v>
+        <v>0.3170323346435637</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1134782339819225</v>
+        <v>0.1471512425952639</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1630621868954236</v>
+        <v>0.1984166105639105</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.09447674418604635</v>
+        <v>-0.07864928683015648</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5120662987653475</v>
+        <v>-0.4870877797188768</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6681685969644064</v>
+        <v>-0.6633616953287245</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4228529108366104</v>
+        <v>-0.4182380944388342</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.04686210180972239</v>
+        <v>-0.02180232558139039</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1610218986605076</v>
+        <v>0.1859166916912827</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4998181554605523</v>
+        <v>0.5248082923475579</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2858717997686426</v>
+        <v>0.2897770254185801</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1371989263467839</v>
+        <v>0.1201185310614861</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.01888917026213477</v>
+        <v>-0.03608034256734527</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.1093294460641445</v>
+        <v>0.09187599982706729</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1647928654683213</v>
+        <v>0.1470555331871282</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.161858364675183</v>
+        <v>0.1442870069964073</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.1328697883526218</v>
+        <v>-0.1500621941061411</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.09049411404898677</v>
+        <v>0.09475218658892004</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.1971681708151749</v>
+        <v>0.2230763808552396</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.0900674936154644</v>
+        <v>-0.04240616810800901</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.04953933639671959</v>
+        <v>0.02039728503193317</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.02043774951485489</v>
+        <v>0.09048346517701589</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2155495794426372</v>
+        <v>-0.1458043177805521</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3644569894881968</v>
+        <v>-0.2946026417809193</v>
       </c>
     </row>
     <row r="17">
@@ -4089,76 +4089,76 @@
         <v>2562</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.02237664872391321</v>
+        <v>0.05565094104274237</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.001514819227807607</v>
+        <v>0.03215818938553383</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.001526567360635056</v>
+        <v>0.03382785630785179</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3434057229760867</v>
+        <v>-0.3289316106057072</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9811550720328412</v>
+        <v>-0.9370956240090109</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.10539567506342</v>
+        <v>-1.061413484604238</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6326409429679671</v>
+        <v>-0.5882259817241646</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.210533852402456</v>
+        <v>-0.143798600487024</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.01331517936113613</v>
+        <v>0.05339118944636567</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2086973403222743</v>
+        <v>0.2536168135266479</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2720450504969492</v>
+        <v>0.2941225436605563</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.09354441349764642</v>
+        <v>0.09322444422189591</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1613428305048075</v>
+        <v>0.1378319375059078</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3141729167709073</v>
+        <v>0.2903210881835889</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.2248044524412407</v>
+        <v>0.200816770611695</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.2579437192173231</v>
+        <v>0.2341222041144135</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2664700373828097</v>
+        <v>-0.2663821378635305</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.05919740351711766</v>
+        <v>-0.03606791501980666</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.1178937531695752</v>
+        <v>0.1640889309437199</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.1634465261514464</v>
+        <v>-0.09416414575471777</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.1601988477177017</v>
+        <v>-0.0902622262890489</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.08002587837982844</v>
+        <v>-0.00998016271766744</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.3516987993293981</v>
+        <v>-0.281953537667313</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.5447361573332259</v>
+        <v>-0.4748818096259484</v>
       </c>
     </row>
     <row r="18">
@@ -4171,896 +4171,896 @@
         <v>2305</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1706611981383475</v>
+        <v>-0.1373869058195183</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.07331076122557789</v>
+        <v>-0.03963775261223645</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.08733479544953582</v>
+        <v>0.1226892191180227</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4101955419650807</v>
+        <v>-0.3740018245461769</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.121486088234796</v>
+        <v>-1.055813058339119</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.539857807407941</v>
+        <v>-1.47438320442167</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.9286408944792726</v>
+        <v>-0.8622488433293256</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.7314169932850305</v>
+        <v>-0.6646817413695985</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.5601431427952619</v>
+        <v>-0.4934367739877601</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.4007069579613045</v>
+        <v>-0.358047951754358</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3178091934281895</v>
+        <v>-0.3002512853709831</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6586040637578066</v>
+        <v>-0.6655058791303929</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.5016954700414757</v>
+        <v>-0.5343426864709429</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2641219965600925</v>
+        <v>-0.2973296031463804</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.2902643818843202</v>
+        <v>-0.3238241513802222</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.1030811715184612</v>
+        <v>-0.1366523616415307</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.3673267094851624</v>
+        <v>-0.374844609274092</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1686224900056104</v>
+        <v>-0.1505874502875599</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.2128030147093725</v>
+        <v>-0.169059526709205</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.6765184381778724</v>
+        <v>-0.6072360577811438</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.6557275239654174</v>
+        <v>-0.5857909025367647</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.81845047548655</v>
+        <v>-0.748404759824389</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.8039789966399979</v>
+        <v>-0.7342337349779129</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.7497684920906735</v>
+        <v>-0.679914144383396</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002234</t>
+          <t>X &gt; -0.0002235</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2037</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4354676353450984</v>
+        <v>0.4687419276639275</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.002444762579436599</v>
+        <v>0.03611777119277804</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.5686151399805723</v>
+        <v>0.6039695636490592</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.634414963819232</v>
+        <v>-0.5982212464003283</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.048608427903943</v>
+        <v>-0.9829353980082658</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.839917396110458</v>
+        <v>-1.774442793124187</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.047225798223195</v>
+        <v>-0.9808337470732482</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8854673321957662</v>
+        <v>-0.8187320802803342</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.3547144765664854</v>
+        <v>-0.2880081077589836</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3664372656493384</v>
+        <v>-0.3270685978854928</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.2107076759446898</v>
+        <v>-0.1997799929055688</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6575430938488225</v>
+        <v>-0.6742241125962209</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4303324360930603</v>
+        <v>-0.476446844814383</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3285781488381758</v>
+        <v>-0.3751035896541097</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.07526864179595805</v>
+        <v>-0.1228498074088193</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.3038163863507677</v>
+        <v>0.2559277240805855</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.1697226922018444</v>
+        <v>0.1512878541098672</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.5065654911286543</v>
+        <v>0.5171459742027622</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.379046042376622</v>
+        <v>0.4191146862285038</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.07517182130584388</v>
+        <v>0.1444542017025725</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.0228894289991004</v>
+        <v>0.09282605042775316</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.200341031650872</v>
+        <v>-0.130295315988711</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.2201166751834691</v>
+        <v>-0.1503714135213841</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.1487826094445737</v>
+        <v>-0.07892826173729617</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -4.919e-05</t>
+          <t>X &gt; -4.931e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1710</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.02418960182054519</v>
+        <v>0.05746389413937436</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5626308606182704</v>
+        <v>0.5963038692316118</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.9866461798751729</v>
+        <v>1.02200060354366</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.0765938426947983</v>
+        <v>-0.04040012527589454</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4418636277188455</v>
+        <v>-0.3761905978231681</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.71072697044881</v>
+        <v>-1.64525236746254</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.260529619683972</v>
+        <v>-1.194137568534025</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.898431964678359</v>
+        <v>-0.8316967127629269</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5074691902789041</v>
+        <v>-0.4407628214714023</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.665428533803599</v>
+        <v>-0.6312673152132007</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3575653556333265</v>
+        <v>-0.3572076730512777</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.03865737529682178</v>
+        <v>0.004695224024899858</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2324195298421756</v>
+        <v>0.1628377582171296</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2794542383041332</v>
+        <v>0.2094440213252113</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.5321271330466075</v>
+        <v>0.4606974494679079</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.8117873446744071</v>
+        <v>0.740338036137338</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>1.028570843507943</v>
+        <v>0.9918324782642642</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.391423684722604</v>
+        <v>1.389676030625878</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.022751526016997</v>
+        <v>1.056822894215962</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.3910818713450368</v>
+        <v>0.4603642517417654</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.3741972518207533</v>
+        <v>0.444133873249406</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.4736807926693771</v>
+        <v>0.5437265083315381</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.3390992340053103</v>
+        <v>0.4088444956673953</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.2631578947368425</v>
+        <v>0.33301224244412</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.000125</t>
+          <t>X &gt; 0.0001249</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>1418</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6416680679334092</v>
+        <v>0.6749423602522384</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.797720623464528</v>
+        <v>0.8313936320778694</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.603634194466103</v>
+        <v>1.63898861813459</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1179110567115487</v>
+        <v>0.1541047741304524</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1771832897160124</v>
+        <v>-0.111510259820335</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.183001132849576</v>
+        <v>-1.117526529863305</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.043586563149212</v>
+        <v>-0.9771945119992651</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.9010885770888279</v>
+        <v>-0.8343533251733959</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7192216348732074</v>
+        <v>-0.6525152660657056</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6105910491908446</v>
+        <v>-0.5833256789442984</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3660883913911519</v>
+        <v>-0.3794414753788757</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.2531399683298403</v>
+        <v>-0.307313685844413</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.2813073088007698</v>
+        <v>-0.3778441737531608</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.1022461298402675</v>
+        <v>0.004171765491157942</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.8947436891036915</v>
+        <v>0.7932597485568138</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.391798727150352</v>
+        <v>1.289796701189111</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.53979248011003</v>
+        <v>1.480129735690092</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.21054954356341</v>
+        <v>2.1929536402086</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.862497812278022</v>
+        <v>1.888690974938925</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.344322990126948</v>
+        <v>1.413605370523676</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.365297475346196</v>
+        <v>1.435234096774849</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.359864281480739</v>
+        <v>1.4299099971429</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.140986415522811</v>
+        <v>1.210731677184896</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.417654385140096</v>
+        <v>1.487508732847374</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0002993</t>
+          <t>X &gt; 0.0002991</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7163304271562794</v>
+        <v>0.7884544197877972</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.466406404413064</v>
+        <v>0.5388564970768215</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.584250697360176</v>
+        <v>1.571024841572239</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.06730902674517836</v>
+        <v>-0.07889680989776338</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8588362712747681</v>
+        <v>-0.8405816606392378</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.524186577279067</v>
+        <v>-1.505404230930274</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.359286298420891</v>
+        <v>-1.340385282793378</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.041080500631701</v>
+        <v>-1.022344598074554</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6585584680046281</v>
+        <v>-0.6401419136044808</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6651304516640835</v>
+        <v>-0.6464477088914009</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.0004473743598936153</v>
+        <v>-0.03167256417411579</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2822433757531968</v>
+        <v>0.2006512862109417</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.5751979812020593</v>
+        <v>0.4403512295762866</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.260452855222503</v>
+        <v>1.071061109518112</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.167219965084271</v>
+        <v>0.9759843095535601</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.762280014705652</v>
+        <v>1.622453200951497</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.799419197269053</v>
+        <v>1.711501179405829</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.37936728802309</v>
+        <v>2.342827240786427</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.338641135886412</v>
+        <v>2.355169675646842</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.755136986301366</v>
+        <v>1.772126691773977</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.896868084152729</v>
+        <v>1.913926118333173</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.82091302851012</v>
+        <v>1.838080156924072</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.581989564855263</v>
+        <v>1.599295673512202</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.762897540655295</v>
+        <v>1.780093018235895</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0004735</t>
+          <t>X &gt; 0.0004733</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>956</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.7483551811378604</v>
+        <v>0.7816294734566895</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7253544843915591</v>
+        <v>0.7590274930049006</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9505863824282059</v>
+        <v>0.9859408060966928</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4916148391936659</v>
+        <v>-0.4554211217747621</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.273117714748409</v>
+        <v>-1.207444684852732</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.606244464904997</v>
+        <v>-1.540769861918726</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.234469597999613</v>
+        <v>-1.168077546849666</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7846163350894528</v>
+        <v>-0.7178810831740208</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.3268671795361158</v>
+        <v>-0.260160810728614</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5804112271421715</v>
+        <v>-0.5127851236017307</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.06638994077094651</v>
+        <v>0.07344933645820362</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1605146678139349</v>
+        <v>0.1068747509082328</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.1407101771944212</v>
+        <v>0.02429541037886196</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.7128691154025475</v>
+        <v>0.531624442360993</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.9537162108571877</v>
+        <v>0.7692494416933684</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.339571239558062</v>
+        <v>1.218519922899489</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.623887587250145</v>
+        <v>1.565488189776495</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.728109192075365</v>
+        <v>1.733551459096851</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.107412271325174</v>
+        <v>1.176892637374308</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.399058577405853</v>
+        <v>1.468340957802582</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.169665699788659</v>
+        <v>1.239602321217312</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.30291566506655</v>
+        <v>1.372961380728711</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.159280789707672</v>
+        <v>1.229026051369758</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.501749492280211</v>
+        <v>1.571603839987489</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.0006478</t>
+          <t>X &gt; 0.0006475</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>770</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.3903947232814602</v>
+        <v>0.4236690156002894</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9584450150887491</v>
+        <v>0.9921180237020906</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.421970357454228</v>
+        <v>0.4573247811227148</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.582145536384097</v>
+        <v>-1.545951818965193</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.689350805279112</v>
+        <v>-1.623677775383435</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.663476514852974</v>
+        <v>-2.598001911866703</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.275052324326353</v>
+        <v>-2.208660273176406</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.811671485973946</v>
+        <v>-2.744936234058514</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.124994130628728</v>
+        <v>-2.058287761821227</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.640765025269125</v>
+        <v>-2.573138921728685</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.165522203931907</v>
+        <v>-2.170047021502242</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.596382272320177</v>
+        <v>-1.674602876563149</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.481841122469163</v>
+        <v>-1.636474620838619</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.8500565317844675</v>
+        <v>-1.083359948898106</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.2640200277995532</v>
+        <v>-0.5033603774280735</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.05857036778856894</v>
+        <v>-0.2200203849621687</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.2409454788177854</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.8711836907984036</v>
+        <v>0.8622326084408201</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.04834581476917776</v>
+        <v>0.1178261808183123</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.6737012987013031</v>
+        <v>-0.6044189183045745</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.9571614479589954</v>
+        <v>-0.8872248265303426</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.90324637373147</v>
+        <v>-0.833200658069309</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.8882114669896026</v>
+        <v>-0.8184662053275176</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.4446722867775463</v>
+        <v>-0.3748179390702688</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.000822</t>
+          <t>X &gt; 0.0008218</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>621</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.005878594249197</v>
+        <v>2.039152886568026</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.3907030796048829</v>
+        <v>0.4243760882182244</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.231002615518733</v>
+        <v>0.2663570391872199</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.442790697674418</v>
+        <v>-1.406596980255514</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.488060482698465</v>
+        <v>-1.422387452802788</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.420895869691677</v>
+        <v>-2.355421266705406</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.113762001745698</v>
+        <v>-1.047369950595751</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.672316647264267</v>
+        <v>-2.605581395348835</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.310800582241633</v>
+        <v>-2.244094213434131</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.764635993011062</v>
+        <v>-2.697009889470621</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.920789546408542</v>
+        <v>-1.942950247308694</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.468054417492617</v>
+        <v>-1.581699650756697</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.054504934674497</v>
+        <v>-1.26486171761281</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.2159593996328724</v>
+        <v>-0.5259405940594064</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.4133541278354684</v>
+        <v>0.1923263647702953</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.04223060257762512</v>
+        <v>-0.07964881560386772</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.357412270747545</v>
+        <v>1.328861777569934</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.057581833718281</v>
+        <v>2.127293981774905</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.6633990385180581</v>
+        <v>0.7328794045671927</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.4378019323671509</v>
+        <v>-0.3685195519704223</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.142032937178314</v>
+        <v>-1.072096315749661</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.8959268011945127</v>
+        <v>-0.8258810855323517</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.9432128263387938</v>
+        <v>-0.8734675646767087</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.1080600050851714</v>
+        <v>0.1779143527924489</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.0009963</t>
+          <t>X &gt; 0.000996</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.947180369397131</v>
+        <v>1.870963910190085</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.03409558453584083</v>
+        <v>0.1582343559347592</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2221729268875663</v>
+        <v>-0.09868233089151346</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.908352827851928</v>
+        <v>-2.976990681042906</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.668099930430216</v>
+        <v>-3.706481940991765</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.66436727008616</v>
+        <v>-4.700618117099111</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.070369496814742</v>
+        <v>-3.110362076580003</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.124072071327383</v>
+        <v>-5.160227064640175</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.899124053642034</v>
+        <v>-3.937637520520738</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.067436781965689</v>
+        <v>-5.104253983958813</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.201361538519002</v>
+        <v>-4.23964316069452</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.28321678321678</v>
+        <v>-4.321542170441731</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.510778843905207</v>
+        <v>-4.6573026624947</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.841555292555498</v>
+        <v>-3.106727995634202</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-2.708407323672006</v>
+        <v>-2.780619324710827</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.3014660859318</v>
+        <v>-3.367334764972561</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-2.049421166219346</v>
+        <v>-2.009925743755304</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.164305572413639</v>
+        <v>-1.012802636582578</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.334321023343207</v>
+        <v>-2.180310465144416</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.741336633663373</v>
+        <v>-2.586350030670474</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.878596448601911</v>
+        <v>-3.721781574130567</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-3.558511900284131</v>
+        <v>-3.402370618543621</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.877796139742586</v>
+        <v>-3.720781281555638</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-2.963638469110073</v>
+        <v>-2.808471242288789</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.001171</t>
+          <t>X &gt; 0.00117</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>410</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.47222005766384</v>
+        <v>0.5054943499826692</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8385652130780485</v>
+        <v>-0.8048922044647071</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.8148510430178391</v>
+        <v>-0.7794966193493522</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.26035167328417</v>
+        <v>-2.224157955865266</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.893914141235044</v>
+        <v>-1.828241111339366</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.926261723350208</v>
+        <v>-2.860787120363938</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.5283961480871753</v>
+        <v>-0.4620040969372283</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.294755671654507</v>
+        <v>-1.228020419739074</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.497142045656261</v>
+        <v>-1.430435676848759</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.002684773498864</v>
+        <v>-2.935058669958423</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.4600328234567</v>
+        <v>-3.392706344869673</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.98302916595599</v>
+        <v>-3.915358187342058</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.888008189321177</v>
+        <v>-3.819008059076218</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.645950366209206</v>
+        <v>-2.576672301376483</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.841466971100161</v>
+        <v>-1.771400964810695</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.978114238551953</v>
+        <v>-1.908721359940877</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8926957375789257</v>
+        <v>-0.8231263017963997</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.4657354804721408</v>
+        <v>0.5354476285287646</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.757165746839952</v>
+        <v>-1.687685380790818</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.78963414634147</v>
+        <v>-2.720351765944741</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-4.308444311436972</v>
+        <v>-4.238507690008319</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.408789610982033</v>
+        <v>-3.338743895319872</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-4.109624200597452</v>
+        <v>-4.039878938935367</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.453858222792761</v>
+        <v>-3.384003875085483</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.001345</t>
+          <t>X &gt; 0.001344</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>325</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4797247480953573</v>
+        <v>0.5129990404141864</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7785276896258964</v>
+        <v>-0.7448546810125549</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.910535846019727</v>
+        <v>-1.87518142235124</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.624329159212884</v>
+        <v>-2.58813544179398</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.681906636544618</v>
+        <v>-2.61623360664894</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-4.033203561999365</v>
+        <v>-3.967728959013094</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.421454309438012</v>
+        <v>-1.355062258288065</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.007701262648879</v>
+        <v>-1.940966010733447</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.889262120703172</v>
+        <v>-2.822555751895671</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.663097531472602</v>
+        <v>-3.595471427932161</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.696430572049572</v>
+        <v>-3.629104093462544</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.590909090909093</v>
+        <v>-4.523238112295161</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.253861847857763</v>
+        <v>-3.184861717612804</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.552141735815205</v>
+        <v>-2.482863670982482</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.287996051775579</v>
+        <v>-2.217930045486113</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-2.308320617538818</v>
+        <v>-2.238927738927742</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2885681578415884</v>
+        <v>-0.2189987220590623</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.760294579909292</v>
+        <v>1.830006727965916</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.408197641774279</v>
+        <v>-1.338717275725145</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-3.374999999999993</v>
+        <v>-3.305717619603264</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-4.841277332074874</v>
+        <v>-4.771340710646221</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-3.686463156948257</v>
+        <v>-3.616417441286096</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-4.334764913543047</v>
+        <v>-4.265019651880962</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-4.103013945119208</v>
+        <v>-4.033159597411931</v>
       </c>
     </row>
     <row r="29">
@@ -5073,76 +5073,76 @@
         <v>283</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.3172309463868359</v>
+        <v>-0.2839566540680067</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.0543073198875561</v>
+        <v>0.08798032850089754</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.092106925117299</v>
+        <v>-2.056752501448813</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.159257128769823</v>
+        <v>-3.12306341135092</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.171170023334504</v>
+        <v>-3.105496993438827</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-4.044076081705811</v>
+        <v>-3.97860147871954</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.636730199625568</v>
+        <v>-1.570338148475621</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.975355516522221</v>
+        <v>-2.908620264606789</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.993910122877672</v>
+        <v>-3.92720375407017</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.767745533647101</v>
+        <v>-4.70011943010666</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.846743156991131</v>
+        <v>-4.779416678404104</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.479193950925399</v>
+        <v>-5.411522972311467</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.130186936196992</v>
+        <v>-4.061186805952033</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.584759294934521</v>
+        <v>-2.515481230101798</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.830262972134371</v>
+        <v>-1.760196965844905</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-2.648630484350441</v>
+        <v>-2.579237605739365</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.3092259452838206</v>
+        <v>-0.2396565095012946</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.059288871836443</v>
+        <v>2.129001019893067</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.1980861984472853</v>
+        <v>-0.1286058323981507</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.191254416961129</v>
+        <v>-3.121972036564401</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-4.08781171641845</v>
+        <v>-4.017875094989797</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-3.457052991142326</v>
+        <v>-3.387007275480165</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-3.88899160557893</v>
+        <v>-3.819246343916845</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-3.964932944847398</v>
+        <v>-3.89507859714012</v>
       </c>
     </row>
     <row r="30">
@@ -5155,76 +5155,76 @@
         <v>235</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.219495615525801</v>
+        <v>1.25276990784463</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3922756437993797</v>
+        <v>-0.3586026351860383</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9809122780982804</v>
+        <v>-0.9455578544297936</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-4.673428995546764</v>
+        <v>-4.637235278127861</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.762103035889957</v>
+        <v>-3.69643000599428</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.426002252670408</v>
+        <v>-4.360527649684137</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.369081150681872</v>
+        <v>-1.302689099531925</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.924231540881287</v>
+        <v>-2.857496288965855</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.733779305645889</v>
+        <v>-3.667072936838387</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.0820828015217</v>
+        <v>-4.014456697981259</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.233255449299982</v>
+        <v>-4.165928970712955</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-4.937881267668502</v>
+        <v>-4.870210289054569</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.509180996793937</v>
+        <v>-3.440180866548978</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.602878233360215</v>
+        <v>-1.533600168527492</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.9852137277166619</v>
+        <v>-0.9151477214271964</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.092281337669739</v>
+        <v>-2.022888459058663</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.3268164575430319</v>
+        <v>0.396385893325558</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.200556445703072</v>
+        <v>3.270268593759695</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.0124242894859492</v>
+        <v>0.08190465553508375</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-3.630319148936167</v>
+        <v>-3.561036768539438</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-4.173519557934121</v>
+        <v>-4.103582936505468</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-3.398410783789494</v>
+        <v>-3.328365068127333</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.974699447094601</v>
+        <v>-3.904954185432516</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-4.050640786363068</v>
+        <v>-3.980786438655791</v>
       </c>
     </row>
     <row r="31">
@@ -5237,240 +5237,240 @@
         <v>180</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.992545260915868</v>
+        <v>3.025819553234697</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.4351475240493201</v>
+        <v>0.4688205326626615</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1065581710742975</v>
+        <v>0.1419125947427844</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.940568475452189</v>
+        <v>-3.904374758033285</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.083616038254021</v>
+        <v>-2.017943008358344</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.5631180919139</v>
+        <v>-3.497643488927629</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.447095335079041</v>
+        <v>-0.380703283929094</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.281205536153152</v>
+        <v>-1.21447028423772</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.350800582241625</v>
+        <v>-2.284094213434123</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.569080437455504</v>
+        <v>-2.501454333915063</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.294721170340168</v>
+        <v>-2.22739469175314</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.9071484071484051</v>
+        <v>-0.8394774285344724</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.3649729589688775</v>
+        <v>-0.2959728287239187</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.858114674441204</v>
+        <v>3.927392739273927</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.643627879848353</v>
+        <v>2.713693886137818</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.127576818358627</v>
+        <v>2.196969696969703</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.215705346431918</v>
+        <v>4.285274782214444</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.221833041447752</v>
+        <v>5.291545189504376</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.215733982157346</v>
+        <v>3.28521434820648</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4861111111111072</v>
+        <v>-0.4168287307143785</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-1.029311520109061</v>
+        <v>-0.9593748986804087</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.5497110201961206</v>
+        <v>-0.4796653045339596</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.941602520380663</v>
+        <v>-1.871857258718578</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-1.461988304093566</v>
+        <v>-1.392133956386289</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.002042</t>
+          <t>X &gt; 0.002041</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>140</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.183021451392065</v>
+        <v>4.216295743710894</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.419274508176308</v>
+        <v>2.452947516789649</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2652883298044557</v>
+        <v>0.3006427534729426</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.877076411960132</v>
+        <v>-1.840882694541229</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6147966601586745</v>
+        <v>0.6804696900543519</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-2.055181583977394</v>
+        <v>-1.989706980991123</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.7433808553971559</v>
+        <v>0.8097729065471029</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.9637452186928357</v>
+        <v>-0.8970099667774036</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.350800582241625</v>
+        <v>-2.284094213434123</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.124635993011054</v>
+        <v>-3.057009889470613</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.13599101161001</v>
+        <v>-2.068664533022982</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.460423866427938</v>
+        <v>1.529423996672897</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.381924198250729</v>
+        <v>3.451202263083452</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>2.722992959213428</v>
+        <v>2.793058965502894</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.889481580263386</v>
+        <v>1.958874458874462</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.898245028971601</v>
+        <v>3.967814464754127</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>5.93611875573346</v>
+        <v>6.005830903790084</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.580813347236713</v>
+        <v>2.650293713285848</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.8035714285714235</v>
+        <v>-0.7342890481746949</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-2.061057551855093</v>
+        <v>-1.99112093042644</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1.422726893211987</v>
+        <v>-1.352681177549826</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-1.147951726729858</v>
+        <v>-1.078206465067773</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-2.652464494569763</v>
+        <v>-2.582610146862486</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.002216</t>
+          <t>X &gt; 0.002215</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.498292387352649</v>
+        <v>1.531566679671478</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.025185838225561</v>
+        <v>2.058858846838902</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.447554339656676</v>
+        <v>1.482908763325163</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.852445870088211</v>
+        <v>-1.816252152669307</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.493577724077781</v>
+        <v>-0.4279046941821036</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2.892620007622718</v>
+        <v>-2.827145404636447</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.079279243125022</v>
+        <v>-1.012887191975075</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.3663040423909081</v>
+        <v>0.4330392943063401</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.178386789138187</v>
+        <v>-2.111680420330686</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.952222199907617</v>
+        <v>-2.884596096367176</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.815793967275042</v>
+        <v>-1.748467488688014</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.232818905232691</v>
+        <v>-1.165147926618758</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.81510366938361</v>
+        <v>2.884103799628569</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.179953754900986</v>
+        <v>5.249231819733708</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.521022515863685</v>
+        <v>4.59108852215315</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.25401359996782</v>
+        <v>4.323406478578896</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>7.568195767887858</v>
+        <v>7.637765203670384</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>10.04941924834431</v>
+        <v>10.11913139640093</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>6.817266549207154</v>
+        <v>6.886746915256289</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>4.418103448275865</v>
+        <v>4.487385828672593</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.4266271772089425</v>
+        <v>0.4965637986375953</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>2.074810052600817</v>
+        <v>2.144855768262978</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.349585219082947</v>
+        <v>2.419330480745032</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.5495059487799949</v>
+        <v>0.6193602964872724</v>
       </c>
     </row>
     <row r="34">
@@ -5483,76 +5483,76 @@
         <v>94</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.5811977431853705</v>
+        <v>0.6144720355041997</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.373681803009127</v>
+        <v>2.407354811622469</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.193678235545093</v>
+        <v>-1.158323811876606</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.971301335972292</v>
+        <v>-2.935107618553388</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1450817592942144</v>
+        <v>-0.07940872939853705</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.149406507989553</v>
+        <v>-3.083931905003283</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.7307832783414554</v>
+        <v>-0.6643912271915084</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.118321650608074</v>
+        <v>1.185056902523506</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.9678218588373824</v>
+        <v>-0.9011154900298806</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.3860023048612788</v>
+        <v>0.4536284084017197</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.724191359210657</v>
+        <v>1.791517837797684</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.508927242969804</v>
+        <v>2.576598221583737</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.703584960652869</v>
+        <v>6.772585090897827</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.546057936852556</v>
+        <v>7.615336001685279</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>9.014786272283352</v>
+        <v>9.084852278572818</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.482186747436636</v>
+        <v>7.551579626047712</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>11.60341220222388</v>
+        <v>11.67298163800641</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>14.68991814783072</v>
+        <v>14.75963029588735</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>9.586892374592345</v>
+        <v>9.65637274064148</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>6.582446808510639</v>
+        <v>6.651729188907368</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>3.911586825044601</v>
+        <v>3.981523446473254</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>4.899461556636034</v>
+        <v>4.969507272298195</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>4.110406935884122</v>
+        <v>4.180152197546207</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>2.970635809381605</v>
+        <v>3.040490157088882</v>
       </c>
     </row>
     <row r="35">
@@ -5565,76 +5565,76 @@
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.05093299995368739</v>
+        <v>-0.01765870763485822</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3861085145980141</v>
+        <v>-0.3524355059846727</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.522017108272365</v>
+        <v>2.557371531940852</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-2.539602291877308</v>
+        <v>-2.503408574458405</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.892229372373997</v>
+        <v>2.957902402269674</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-2.71770746389457</v>
+        <v>-2.652232860908299</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.306527853326756</v>
+        <v>2.372919904476703</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.926523932445875</v>
+        <v>4.993259184361307</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3.51876463514968</v>
+        <v>3.585471003957181</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.092755311336767</v>
+        <v>7.160381414877207</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.816389940770932</v>
+        <v>8.88371641935796</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>9.986571399614888</v>
+        <v>10.05424237822882</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.31135554344657</v>
+        <v>10.38035567369153</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.08999873241222</v>
+        <v>10.15927679724494</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>12.32961821801261</v>
+        <v>12.39968422430207</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>12.92467826763399</v>
+        <v>12.99407114624506</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>14.23985993580389</v>
+        <v>14.30942937158642</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>17.0334272443463</v>
+        <v>17.10313939240292</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.9017243203216</v>
+        <v>12.97120468637073</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.63949275362319</v>
+        <v>11.70877513401992</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>6.748466257668703</v>
+        <v>6.818402879097356</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>8.121786564344951</v>
+        <v>8.191832280007112</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>6.947286368508223</v>
+        <v>7.017031630170308</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>5.422069666920926</v>
+        <v>5.491924014628204</v>
       </c>
     </row>
   </sheetData>
@@ -5824,83 +5824,83 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.002489</t>
+          <t>X &lt; -0.002488</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>69</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.746585173866741</v>
+        <v>-8.713310881547912</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.98031141314875</v>
+        <v>-11.94663840453541</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-13.42001187723488</v>
+        <v>-13.3846574535664</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.58308055274688</v>
+        <v>-15.54688683532797</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.252698163857879</v>
+        <v>-7.187025133962202</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.16698282621342</v>
+        <v>-4.10150822322715</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.389124320586284</v>
+        <v>-6.322732269436337</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.769128241467158</v>
+        <v>-3.702392989551726</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.626162901082211</v>
+        <v>-6.559456532274709</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.849273674170476</v>
+        <v>-8.781647570630035</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-11.47346513169283</v>
+        <v>-11.4061386531058</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.854008310530041</v>
+        <v>-8.786337331916108</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.181398079741825</v>
+        <v>-4.112397949496867</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.40275489077618</v>
+        <v>-4.333476825943457</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-9.409512216770004</v>
+        <v>-9.339446210480538</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-10.26372752946746</v>
+        <v>-10.19433465085638</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-10.39782122361638</v>
+        <v>-10.32825178783386</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-10.50280463971166</v>
+        <v>-10.43309249165504</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-11.73595683909869</v>
+        <v>-11.66647647304956</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-12.9981884057971</v>
+        <v>-12.92890602540037</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-12.09211345247621</v>
+        <v>-12.02217683104756</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-12.16806850811882</v>
+        <v>-12.09802279245666</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-6.096191892361325</v>
+        <v>-6.02644663069924</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.27358250699212</v>
+        <v>-3.203728159284843</v>
       </c>
     </row>
     <row r="7">
@@ -5913,76 +5913,76 @@
         <v>93</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.865610767452921</v>
+        <v>-6.832336475134092</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.848006597814482</v>
+        <v>-8.230943060717955</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-11.36297587910492</v>
+        <v>-10.73279189698299</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-14.22730682670667</v>
+        <v>-13.57340549089381</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.915157256892016</v>
+        <v>-5.398557665568745</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.502186192272326</v>
+        <v>-1.436711589286055</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.275052324326353</v>
+        <v>-2.208660273176406</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.4030693354363066</v>
+        <v>-0.3363340835208746</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.51209090482228</v>
+        <v>-2.445384536014778</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-7.58700158440891</v>
+        <v>-7.519375480868469</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-8.387911134497877</v>
+        <v>-8.320584655910849</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.441198586359874</v>
+        <v>-5.373527607745942</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.189345718825507</v>
+        <v>-1.120345588580548</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.410702529859861</v>
+        <v>-1.341424465027139</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-5.295440220510073</v>
+        <v>-5.225374214220608</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-4.700380170888693</v>
+        <v>-4.630987292277617</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-5.909742682241919</v>
+        <v>-5.840173246459393</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-8.1652637327458</v>
+        <v>-8.095551584689176</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-6.873871752609681</v>
+        <v>-6.804391386560546</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-9.912634408602152</v>
+        <v>-9.843352028205423</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-8.305297183191506</v>
+        <v>-8.235360561762853</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-9.456521056038412</v>
+        <v>-9.386475340376251</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-3.805401803534785</v>
+        <v>-3.7356565418727</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.655536691190342</v>
+        <v>-0.5856823434830645</v>
       </c>
     </row>
     <row r="8">
@@ -5995,76 +5995,76 @@
         <v>111</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.459835691465081</v>
+        <v>-5.426561399146252</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.96425187535008</v>
+        <v>-8.439909626067497</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-10.40395233943622</v>
+        <v>-9.877928675098488</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-14.72134925623298</v>
+        <v>-14.1623112659698</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.978510933148918</v>
+        <v>-7.355244595659933</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.187742716538523</v>
+        <v>-3.122268113552252</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.158807046790749</v>
+        <v>-2.092414995640802</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.6355598905075084</v>
+        <v>-0.5688246385920763</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.395845627286675</v>
+        <v>-2.329139258479174</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.872383740758814</v>
+        <v>-5.804757637218373</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.399826275445278</v>
+        <v>-7.332499796858251</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.07531657531657</v>
+        <v>-4.007645596702638</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.497105091101012</v>
+        <v>-2.428104960856054</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.817561001234466</v>
+        <v>-1.748282936401743</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-5.179194942974469</v>
+        <v>-5.109128936685003</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-5.485035794253989</v>
+        <v>-5.415642915642913</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-5.619129488402912</v>
+        <v>-5.549560052620386</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-8.426815607200901</v>
+        <v>-8.357103459144277</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-7.309791543368185</v>
+        <v>-7.24031117731905</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-8.023648648648653</v>
+        <v>-7.954366268251924</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-7.665948156745706</v>
+        <v>-7.596011535317054</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.741903212388316</v>
+        <v>-7.671857496726155</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-4.764425343203477</v>
+        <v>-4.694680081541392</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-2.137663979769243</v>
+        <v>-2.067809632061966</v>
       </c>
     </row>
     <row r="9">
@@ -6077,158 +6077,158 @@
         <v>143</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.451899183528575</v>
+        <v>-6.418624891209745</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.855450766548969</v>
+        <v>-7.447846134004003</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.497948433432306</v>
+        <v>-6.108087405257216</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-10.00894454382826</v>
+        <v>-9.598819202477735</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-6.877710832348811</v>
+        <v>-7.15683189724723</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.096140624936439</v>
+        <v>-1.030666021950168</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.169706057689758</v>
+        <v>-1.103314006539811</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.448260703208319</v>
+        <v>-1.381525451292887</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.903248134689186</v>
+        <v>-4.836541765881684</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.376384244759315</v>
+        <v>-6.308758141218874</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.500626376245371</v>
+        <v>-7.433299897658344</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.98251748251748</v>
+        <v>-4.914846503903547</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.309805903801823</v>
+        <v>-3.240805773556865</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.433260616934085</v>
+        <v>-1.363982552101362</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-5.588695352474886</v>
+        <v>-5.518629346185421</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-4.993635302853505</v>
+        <v>-4.924242424242429</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.127728997002428</v>
+        <v>-5.058159561219902</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-8.729215909601194</v>
+        <v>-8.65950376154457</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-7.813792047368686</v>
+        <v>-7.744311681319552</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-8.326048951048946</v>
+        <v>-8.256766570652218</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-10.2678507586483</v>
+        <v>-10.19791413721965</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-9.64450511499021</v>
+        <v>-9.574459399328049</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-7.271827850605987</v>
+        <v>-7.202082588943902</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-5.249867091972362</v>
+        <v>-5.180012744265085</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.001792</t>
+          <t>X &lt; -0.001791</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>180</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.773022504651898</v>
+        <v>-4.739748212333069</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.49548476569899</v>
+        <v>-6.173426109583978</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-6.277726666249215</v>
+        <v>-5.96309351026332</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-8.09649235513298</v>
+        <v>-7.774948628607163</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.489386449549293</v>
+        <v>-3.715134705550035</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.5397908973159886</v>
+        <v>-0.4743162943297179</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7601708415247117</v>
+        <v>-0.6937787903747648</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.591211674888577</v>
+        <v>-1.524476422973144</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.864612736937765</v>
+        <v>-4.797906368130263</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.638448147707194</v>
+        <v>-5.570822044166754</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.574033631973066</v>
+        <v>-7.506707153386039</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.090696596221456</v>
+        <v>-5.023025617607523</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.900270687636777</v>
+        <v>-2.831270557391818</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.016655122980524</v>
+        <v>-1.947377058147801</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-5.990503489089654</v>
+        <v>-5.920437482800189</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-5.395443439468274</v>
+        <v>-5.326050560857198</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-4.424564757926575</v>
+        <v>-4.354995322144049</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-8.111500291885577</v>
+        <v>-8.327239340882365</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-7.895377128953761</v>
+        <v>-8.111347959958039</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-6.597222222222221</v>
+        <v>-6.819529774299404</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-8.251533742331283</v>
+        <v>-8.467048317956042</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-7.216377686862785</v>
+        <v>-7.146331971200624</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-5.274935853713991</v>
+        <v>-5.205190592051906</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-5.350877192982459</v>
+        <v>-5.281022845275182</v>
       </c>
     </row>
     <row r="11">
@@ -6238,79 +6238,79 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-4.067822193152367</v>
+        <v>-3.836925544804515</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.99743921288524</v>
+        <v>-4.95601606864453</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.646625842979283</v>
+        <v>-5.609721392185321</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.569905322180347</v>
+        <v>-5.538361686137868</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.773119771236011</v>
+        <v>-2.919080366188609</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.214413656252944</v>
+        <v>-0.1489390532666732</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.9890047966732638</v>
+        <v>1.055396847823211</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.265834433825532</v>
+        <v>-1.1990991819101</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.200602953783132</v>
+        <v>-3.133896584975631</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.764952198544655</v>
+        <v>-4.697326095004215</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.676363682417467</v>
+        <v>-5.609037203830439</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.979173000912127</v>
+        <v>-3.911502022298194</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.522636551415083</v>
+        <v>-3.453636421170124</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.767708777469203</v>
+        <v>-1.69843071263648</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.402924601486738</v>
+        <v>-4.332858595197273</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-4.598378385857444</v>
+        <v>-4.528985507246368</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.151444412022187</v>
+        <v>-3.081874976239661</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.80991299029828</v>
+        <v>-5.953514099033171</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-5.77718323785151</v>
+        <v>-6.132879635104892</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-4.793326693227094</v>
+        <v>-5.155519991144772</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.734933476727043</v>
+        <v>-6.093323076106849</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-5.014075783365669</v>
+        <v>-5.162204987073636</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.719380298158427</v>
+        <v>-3.872742606217471</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-3.39532163742691</v>
+        <v>-3.550168484938752</v>
       </c>
     </row>
     <row r="12">
@@ -6320,79 +6320,79 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.169070900700291</v>
+        <v>-2.969706173834652</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.618488909904983</v>
+        <v>-5.749213430611427</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.315333070555774</v>
+        <v>-5.455456040658198</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.96873844880016</v>
+        <v>-3.263734254149583</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.7476755307086265</v>
+        <v>-0.8700158613000042</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.5035925102202867</v>
+        <v>-0.4372004590703398</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.477062409976128</v>
+        <v>-2.410327158060696</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.791478548343328</v>
+        <v>-3.724772179535826</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.582263111655124</v>
+        <v>-5.514637008114683</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.646886895387254</v>
+        <v>-5.579560416800227</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.875133341235042</v>
+        <v>-2.807462362621109</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.304709305484884</v>
+        <v>-2.235709175239926</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.8311508622819588</v>
+        <v>-0.7618727974492359</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.846014304709094</v>
+        <v>-2.775948298419628</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-3.60688645847754</v>
+        <v>-3.537493579866464</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-3.06301405093155</v>
+        <v>-2.993444615149023</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.335990087803957</v>
+        <v>-4.45421752236004</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.271941406541934</v>
+        <v>-4.57730919228316</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.061006825938563</v>
+        <v>-3.373514229772766</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.604207234936517</v>
+        <v>-3.916060397738796</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.680162290579126</v>
+        <v>-3.801660769386572</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.527599476240631</v>
+        <v>-2.653048005779624</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-2.407005486224158</v>
+        <v>-2.728880259002899</v>
       </c>
     </row>
     <row r="13">
@@ -6402,79 +6402,79 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.6996171564590057</v>
+        <v>-0.5335024806636071</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.736569647667849</v>
+        <v>-1.715736906132065</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.027344962828842</v>
+        <v>-3.153755955163057</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.456237991121704</v>
+        <v>-3.584224098899575</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.257405212043196</v>
+        <v>-1.504880370649808</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.6391611103653005</v>
+        <v>0.5427605514764124</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1337050216887263</v>
+        <v>-0.06731297053877938</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.976362231309849</v>
+        <v>-2.909626979394417</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.504646736087786</v>
+        <v>-3.437940367280284</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.993581861956926</v>
+        <v>-3.925955758416485</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.28902316464216</v>
+        <v>-4.221696686055132</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.434213934213936</v>
+        <v>-1.366542955600003</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.5644031583990881</v>
+        <v>-0.4954030281541293</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.6387414550679935</v>
+        <v>0.7080195199007164</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.8748906386701734</v>
+        <v>-0.8048246323807078</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.989232298450496</v>
+        <v>-1.91983941983942</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.268625137898567</v>
+        <v>-1.199055702116041</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.778166958552255</v>
+        <v>-1.873696975737793</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.54198648903018</v>
+        <v>-2.797406734414608</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-1.78187679083095</v>
+        <v>-2.040760354646011</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.038544248539509</v>
+        <v>-2.298406237711752</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-2.114499304182118</v>
+        <v>-2.209824034692687</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.098690642986028</v>
+        <v>-1.196912973459092</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.7175118391560034</v>
+        <v>-0.9862122753929725</v>
       </c>
     </row>
     <row r="14">
@@ -6484,79 +6484,79 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.441978548607935</v>
+        <v>-1.302317046616821</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.9891626922072021</v>
+        <v>-0.9689423973051632</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.9646924517458331</v>
+        <v>-1.070658551013217</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.781624778391901</v>
+        <v>-0.8927439735739995</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.767903642862073</v>
+        <v>1.573326832911505</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.851929242415949</v>
+        <v>2.784981417858354</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.406417370451607</v>
+        <v>1.472809421601553</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.4416440015243595</v>
+        <v>-0.3749087496089274</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.296988923048815</v>
+        <v>-1.230282554241313</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.295039580455011</v>
+        <v>-2.22741347691457</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.123819326792585</v>
+        <v>-1.056492848205558</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2818369970836301</v>
+        <v>-0.2141660184696974</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.060039497433706</v>
+        <v>1.129039627678665</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.735543672946442</v>
+        <v>1.804821737779164</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.4039666939988251</v>
+        <v>0.4740327002882907</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.3462647362004176</v>
+        <v>-0.2768718575893416</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.6407178028345086</v>
+        <v>0.7102872386170347</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2276051607994347</v>
+        <v>-0.2914144517512227</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.5530347866114269</v>
+        <v>-0.7481688107372122</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.007054176072230689</v>
+        <v>-0.3371077541324183</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.0987873164471651</v>
+        <v>-0.4312234288249002</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2656486773102458</v>
+        <v>-0.5982670523491862</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.8248373889164</v>
+        <v>0.4855000986387807</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.341041998936731</v>
+        <v>0.9968803400772117</v>
       </c>
     </row>
     <row r="15">
@@ -6566,79 +6566,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.322770054399449</v>
+        <v>-2.294348011098037</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.9407048626333889</v>
+        <v>-1.013325886647138</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.561113116850159</v>
+        <v>-1.733212081100028</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2857563396273974</v>
+        <v>-0.3712012968022762</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.242283097771697</v>
+        <v>2.096171105755772</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.152775016384268</v>
+        <v>3.110860321742244</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.199077057928797</v>
+        <v>2.265469109078744</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.016363280403006</v>
+        <v>1.083098532318438</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.7504389185888343</v>
+        <v>-0.6837325497813325</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.247601634964042</v>
+        <v>-2.179975531423601</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.8882514094400236</v>
+        <v>-0.8209249308529962</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2631861809076952</v>
+        <v>-0.1955152022937625</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.143968170225413</v>
+        <v>1.212968300470372</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.1992840535852736</v>
+        <v>0.2685621184179965</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.263680120153758</v>
+        <v>0.3337461264432235</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.04541896223209818</v>
+        <v>0.02397391637897783</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.80963743403489</v>
+        <v>1.879206869817416</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.366760577679635</v>
+        <v>0.3277115547846634</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.3968895306476554</v>
+        <v>-0.5413880226996852</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.2613636363636331</v>
+        <v>0.007121440071230722</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.008939846011152497</v>
+        <v>-0.3545929014933549</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.04234088572439987</v>
+        <v>-0.3226604736160823</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>1.158133412993301</v>
+        <v>0.7859366513439454</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.376839534734273</v>
+        <v>1.001805437553102</v>
       </c>
     </row>
     <row r="16">
@@ -6648,79 +6648,79 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.210353289808765</v>
+        <v>-1.25989473247958</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.4534188362151497</v>
+        <v>-0.5845705207283913</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.6524857565742863</v>
+        <v>-0.7893655041653744</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3779069767441854</v>
+        <v>0.3133451326243701</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.047520912650377</v>
+        <v>1.943409648646487</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.67073203728507</v>
+        <v>2.650558413991256</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.692642656187338</v>
+        <v>1.673560281962388</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1878582798494364</v>
+        <v>0.08720930232558999</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6452612236410431</v>
+        <v>-0.7433965390155279</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.002187013419231</v>
+        <v>-2.097707563889223</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.144737367295136</v>
+        <v>-1.159951702912778</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.5491957022569238</v>
+        <v>-0.4815247236429911</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.0755842162821736</v>
+        <v>0.1445843465271324</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.4373177842565497</v>
+        <v>-0.3680397194238267</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.658931239037301</v>
+        <v>-0.5888652327478354</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.6469615684246648</v>
+        <v>-0.5775686898135888</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.5308980901960965</v>
+        <v>0.6004675259786225</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.3621085643916615</v>
+        <v>-0.3790087463556802</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.7901139710590215</v>
+        <v>-0.8919803391922869</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.3614568081991223</v>
+        <v>0.1695010392888534</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.1991016437879694</v>
+        <v>-0.08149993917280085</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.08226119151281353</v>
+        <v>-0.3620659533579698</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.8688549959592109</v>
+        <v>0.5842830921586213</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.471246845636429</v>
+        <v>1.182292593150073</v>
       </c>
     </row>
     <row r="17">
@@ -6730,79 +6730,79 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.06587398307038228</v>
+        <v>-0.1630820051081372</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.004464547494784199</v>
+        <v>-0.09434537296900203</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.00450433767717584</v>
+        <v>-0.09935724652705602</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.012869463060369</v>
+        <v>0.9672245300419675</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.897226873623381</v>
+        <v>2.758689294047159</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.267849815003373</v>
+        <v>3.128248458065237</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.872413113461668</v>
+        <v>1.735638086143624</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.6238309882605293</v>
+        <v>0.424131578244733</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.03949964870524525</v>
+        <v>-0.1576574318249371</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.6188623209556354</v>
+        <v>-0.7497601771576186</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.8063968182744858</v>
+        <v>-0.870507850995331</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.277176633989562</v>
+        <v>-0.2762325227290177</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4778803236083462</v>
+        <v>-0.4088801933633874</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.9301840168597906</v>
+        <v>-0.8609059520270677</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.6653277270287319</v>
+        <v>-0.5952617207392663</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.7631083240586207</v>
+        <v>-0.6937154454475447</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.7892442032077724</v>
+        <v>0.7889955930946115</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1755367451514616</v>
+        <v>0.1067876837307011</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.3499928106841637</v>
+        <v>-0.4856350231047912</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.4857888631090503</v>
+        <v>0.278577992405971</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.476689254184393</v>
+        <v>0.2673431488468836</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.2384026748943242</v>
+        <v>0.02959395472530701</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>1.048954975415491</v>
+        <v>0.8370393551606625</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.626589784484523</v>
+        <v>1.411423661556476</v>
       </c>
     </row>
     <row r="18">
@@ -6812,899 +6812,899 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3488670999963333</v>
+        <v>0.2798577323830145</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.149995115003108</v>
+        <v>0.08081347798894711</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.1788468087505208</v>
+        <v>-0.2503596421896503</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.840755401616363</v>
+        <v>0.7638623837020901</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.30068840816223</v>
+        <v>2.158302202369619</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.161768428709742</v>
+        <v>3.016614131524683</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.908460220476513</v>
+        <v>1.765738995374122</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.504480505760647</v>
+        <v>1.362361867062511</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.153206541533969</v>
+        <v>1.012267809635972</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8246071058313262</v>
+        <v>0.7351748352185439</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.6537303978798761</v>
+        <v>0.617049752691301</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.354155639551898</v>
+        <v>1.36890533144971</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.03108917618497</v>
+        <v>1.100089306429929</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5425907801105438</v>
+        <v>0.6118688449432668</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.5960371011801016</v>
+        <v>0.6661031074695671</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2115780056545589</v>
+        <v>0.2809708842656349</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.7546239441740425</v>
+        <v>0.770384112381663</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.3467215338652352</v>
+        <v>0.3093546285070445</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.3471516194046629</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.393543342269886</v>
+        <v>1.246374989479548</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.351924814615636</v>
+        <v>1.203429617065275</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.68892421306758</v>
+        <v>1.538869733626413</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.66054801725376</v>
+        <v>1.511079249217943</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.549969842393729</v>
+        <v>1.400538072210665</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002234</t>
+          <t>X &lt; -0.0002235</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.63623720274866</v>
+        <v>-0.6828998575517105</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.003574459737045288</v>
+        <v>-0.05265672205283067</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.8319608776809702</v>
+        <v>-0.8811661585286927</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.9288998467381901</v>
+        <v>0.8734030197444795</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.536455646333799</v>
+        <v>1.436111475002789</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.697841576506306</v>
+        <v>2.594392753323206</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.536632829553653</v>
+        <v>1.435092468874537</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.300212088367921</v>
+        <v>1.198773905510762</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5212339253069018</v>
+        <v>0.4219989765300269</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.5381965015971346</v>
+        <v>0.4795754763830331</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3093206860381343</v>
+        <v>0.293144512203142</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.9648062218155715</v>
+        <v>0.9900244871743453</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6311129903880968</v>
+        <v>0.7001131206330555</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.4816469054500772</v>
+        <v>0.5509249702828001</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.1102785707981013</v>
+        <v>0.1803445770875669</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.4449129971218468</v>
+        <v>-0.3755201185107708</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.2487231108022883</v>
+        <v>-0.2218743511029118</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.7428897807264718</v>
+        <v>-0.7580594115020958</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.5562801068596315</v>
+        <v>-0.6140587566741047</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.1104001441961131</v>
+        <v>-0.2115407684170734</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.03364052443806997</v>
+        <v>-0.1360335717419687</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.2946531996193684</v>
+        <v>0.1910810357588133</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.3239723029976389</v>
+        <v>0.2206819663854986</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.2191396785528497</v>
+        <v>0.1159169929047437</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -4.919e-05</t>
+          <t>X &lt; -4.931e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1710</v>
+        <v>1714</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.02406346832322015</v>
+        <v>-0.05703208453022768</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5600215580762864</v>
+        <v>-0.5921652651652352</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.982640075896569</v>
+        <v>-1.01549481266462</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.07632712008530262</v>
+        <v>0.04016619287708068</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.4405806322841102</v>
+        <v>0.3742290014266416</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.706750847333304</v>
+        <v>1.637622211555467</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.258331021510109</v>
+        <v>1.189288982118853</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8973866686170595</v>
+        <v>0.8288004966999196</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5071738065825855</v>
+        <v>0.43948302233823</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6646538789330592</v>
+        <v>0.6298001047188038</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.35694096909846</v>
+        <v>0.3565846364122365</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.03856736976643305</v>
+        <v>-0.004689761286073235</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.231743105133674</v>
+        <v>-0.1627429748887153</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.2784782630830449</v>
+        <v>-0.209200198250322</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.5299589782553866</v>
+        <v>-0.459892971965921</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.8080071940589235</v>
+        <v>-0.7386143154478475</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.024377485380668</v>
+        <v>-0.988945887815305</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.386558566943854</v>
+        <v>-1.384822680111448</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.019769743142298</v>
+        <v>-1.052516863797145</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.3901691948658055</v>
+        <v>-0.4582205299641586</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.3735419151275465</v>
+        <v>-0.4423231935098997</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.4731274272573884</v>
+        <v>-0.5418253666940274</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.338901046258961</v>
+        <v>-0.4076525292077235</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.2631578947368425</v>
+        <v>-0.3322350843520638</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.000125</t>
+          <t>X &lt; 0.0001249</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4531105038677481</v>
+        <v>-0.4756641262905177</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5635854677426693</v>
+        <v>-0.5862127291988983</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.13352119400507</v>
+        <v>-1.15621721823851</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.08338623117317923</v>
+        <v>-0.108766371043032</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.1253655351764138</v>
+        <v>0.07874237871357082</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.8374449152064827</v>
+        <v>0.7895266757834349</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7391207020316273</v>
+        <v>0.6907252874994754</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.6385137853563165</v>
+        <v>0.5900513589935912</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.5098959351713006</v>
+        <v>0.4616853297634833</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4325779373372001</v>
+        <v>0.4129354657206363</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.259176010422685</v>
+        <v>0.2687396135262929</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.179087082072158</v>
+        <v>0.2177633029976533</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.1988744705501944</v>
+        <v>0.2678746007951531</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.0722335842652555</v>
+        <v>-0.002955519432532583</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.6316623357403728</v>
+        <v>-0.5615963294509072</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.9818759179597834</v>
+        <v>-0.9124830393487073</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.086822168639152</v>
+        <v>-1.046400176326181</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.561035484448659</v>
+        <v>-1.549250830396119</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.315905280423621</v>
+        <v>-1.333359449471793</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.9502741774676053</v>
+        <v>-0.9972599081604869</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.9655819551326204</v>
+        <v>-1.013022373930674</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.9622193368960552</v>
+        <v>-1.009767119496324</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.8077477469851928</v>
+        <v>-0.8554148072985441</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.004112846218106</v>
+        <v>-1.051489223917038</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0002993</t>
+          <t>X &lt; 0.0002991</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.3701566480415437</v>
+        <v>-0.4072351468679543</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.241117105498688</v>
+        <v>-0.2784408131902296</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8193677548516334</v>
+        <v>-0.8121458229880218</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.03482729967891629</v>
+        <v>0.04080390080176244</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.4445785287754944</v>
+        <v>0.434924138206469</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7893469559153914</v>
+        <v>0.7792524546349782</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.7042591996677245</v>
+        <v>0.6941386510804719</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5396320933455385</v>
+        <v>0.5296701492230937</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3415071100660541</v>
+        <v>0.3317998263009656</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3450676779310058</v>
+        <v>0.3352162589392762</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.0002318986066995876</v>
+        <v>0.01643110487866295</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.146177352059695</v>
+        <v>-0.1041399690590836</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2976477832845745</v>
+        <v>-0.2286476530396158</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6516892471274147</v>
+        <v>-0.5563830719355067</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.60296900451943</v>
+        <v>-0.506561767746156</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.9107712642372547</v>
+        <v>-0.8413783856261787</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.9303769908854775</v>
+        <v>-0.8867999473824142</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.230779890350298</v>
+        <v>-1.212879589256687</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.21024937825225</v>
+        <v>-1.218227146385452</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.9086879432624073</v>
+        <v>-0.9170500675891091</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.9825019611043828</v>
+        <v>-0.9908678619714237</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.9435787122004555</v>
+        <v>-0.9520229080391047</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.8201348476480064</v>
+        <v>-0.8287130506807472</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.914326966023701</v>
+        <v>-0.9228065358393565</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0004735</t>
+          <t>X &lt; 0.0004733</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2464</v>
+        <v>2468</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2897539601424128</v>
+        <v>-0.3021504119034049</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2809615717453866</v>
+        <v>-0.2935313564497832</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3683522231909393</v>
+        <v>-0.3814368416501352</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1905775959923872</v>
+        <v>0.1762624639651875</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4937312848560111</v>
+        <v>0.4675077929667566</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.6231735691456279</v>
+        <v>0.5968076732381604</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4791297591589796</v>
+        <v>0.4526300494042346</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.3046530497054363</v>
+        <v>0.2782911338968219</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1269682132312866</v>
+        <v>0.1008936800283351</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2255459722133608</v>
+        <v>0.1989448945423007</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.02577207567333062</v>
+        <v>-0.02850759787413182</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.06224567991652208</v>
+        <v>-0.04149763055468014</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.05450883532238748</v>
+        <v>-0.009437303708203615</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2758656463567419</v>
+        <v>-0.206587581524019</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.3686828538534002</v>
+        <v>-0.2986168475639346</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.5180542496025353</v>
+        <v>-0.4725275398546671</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.6282624578758345</v>
+        <v>-0.6064446768321403</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.6688552176615588</v>
+        <v>-0.6708486641147076</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.4287914667423465</v>
+        <v>-0.4549572831903816</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.5419367909238275</v>
+        <v>-0.5678535419333741</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.4532632383453432</v>
+        <v>-0.479587138439399</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.5051043697500504</v>
+        <v>-0.531397198371117</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.4496034218906928</v>
+        <v>-0.4758804799957375</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.5826592997645648</v>
+        <v>-0.6087736106272459</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.0006478</t>
+          <t>X &lt; 0.0006475</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2650</v>
+        <v>2654</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1134017655708845</v>
+        <v>-0.1228830415756832</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.2785132683516309</v>
+        <v>-0.287866517547414</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1226658015855335</v>
+        <v>-0.1327440844082801</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4600986081417204</v>
+        <v>0.4488994603589447</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4914590368210625</v>
+        <v>0.4716455307054588</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.7751386778111353</v>
+        <v>0.7549499368941426</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.6623461875856265</v>
+        <v>0.6420524049931373</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.8188821501803076</v>
+        <v>0.798245996771243</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.6191242297884401</v>
+        <v>0.5987886694487514</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7696851803623943</v>
+        <v>0.7488481653547652</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6303550905766357</v>
+        <v>0.6317755227889776</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.4640855571656672</v>
+        <v>0.4877178614567583</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.430229915963217</v>
+        <v>0.4767924177255409</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.2464812282834998</v>
+        <v>0.3157592931162228</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.07645559285658265</v>
+        <v>0.1465215991460482</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.01696733754598512</v>
+        <v>0.06396230070543396</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.09471158159885107</v>
+        <v>-0.06995483627203924</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.2525645489136892</v>
+        <v>-0.2500117868025029</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.01402119675037738</v>
+        <v>-0.034120405878177</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1954596834966154</v>
+        <v>0.1750950214802529</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.2778041141833469</v>
+        <v>0.2571182222161639</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.262254791769692</v>
+        <v>0.2415529016240114</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.2579867331505028</v>
+        <v>0.2373706132211666</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.1292066644598933</v>
+        <v>0.1087452197001255</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.000822</t>
+          <t>X &lt; 0.0008218</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2799</v>
+        <v>2803</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.444880809583303</v>
+        <v>-0.4516196152037608</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.08668421183993047</v>
+        <v>-0.09402164308273342</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.05127011175398621</v>
+        <v>-0.05903303173475649</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3203354124499214</v>
+        <v>0.3118563719970595</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.3305038385524313</v>
+        <v>0.315469183109208</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5378812366005334</v>
+        <v>0.5225908028721591</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.2475466753524529</v>
+        <v>0.2324595948587813</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5941650318534855</v>
+        <v>0.5785038622000087</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.5139681010323969</v>
+        <v>0.4984217780370841</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.6151290479287752</v>
+        <v>0.5992290013932262</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4266901662367033</v>
+        <v>0.4318434938008266</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3255955507646533</v>
+        <v>0.3516763720109992</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2335002026940245</v>
+        <v>0.2813304532056975</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.04774324926025031</v>
+        <v>0.1170213140929732</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.09141485519438675</v>
+        <v>-0.04272397707961062</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.009342787388909812</v>
+        <v>0.01766508085482599</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.3004109123785597</v>
+        <v>-0.2942513441254988</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.455528812384685</v>
+        <v>-0.470291763147813</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.1469225402709284</v>
+        <v>-0.1620790990869665</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.09699429183017827</v>
+        <v>0.08152855068529163</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.2531058008521541</v>
+        <v>0.2372672174200119</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.1986328252559062</v>
+        <v>0.1828421226793537</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.2091911304129965</v>
+        <v>0.1934462759144893</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.02397472781632359</v>
+        <v>-0.03941662971248405</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.0009963</t>
+          <t>X &lt; 0.000996</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2915</v>
+        <v>2918</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3362467463502554</v>
+        <v>-0.3233921967936624</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.005889765369573752</v>
+        <v>-0.02735978652651028</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.03839184523926065</v>
+        <v>0.01706864967412258</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5027394762089799</v>
+        <v>0.5150923930414848</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6342860384475131</v>
+        <v>0.6415307754765962</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8068352800865597</v>
+        <v>0.8138766201384939</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.531289192793551</v>
+        <v>0.5387193777370101</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.8869595562181587</v>
+        <v>0.894063897966312</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6751557019113719</v>
+        <v>0.6824700990871975</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.8777555341498484</v>
+        <v>0.8849696327136769</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.7279871155260125</v>
+        <v>0.7353153723567161</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7424242424242422</v>
+        <v>0.7497757590793697</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.7803261863302566</v>
+        <v>0.8083053476417135</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.4905933069198412</v>
+        <v>0.5393772459952757</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.4677652867490991</v>
+        <v>0.482924655368592</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.570386716864725</v>
+        <v>0.5850225925465296</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.3541949654143508</v>
+        <v>0.3485062763624924</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.2012921308007094</v>
+        <v>0.1752661197369321</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.4037096290370954</v>
+        <v>0.3774331492860412</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.4742634463857485</v>
+        <v>0.4478758095548443</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.671244416224809</v>
+        <v>0.6447180679596229</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.6160605106765402</v>
+        <v>0.5895888811585905</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.6715662038991823</v>
+        <v>0.644986409204229</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.5134262184907641</v>
+        <v>0.4870070077443884</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.001171</t>
+          <t>X &lt; 0.00117</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3010</v>
+        <v>3014</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.063834561042583</v>
+        <v>-0.06824256947410845</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1133943724808688</v>
+        <v>0.1086975638440393</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1102239946015544</v>
+        <v>0.1053026734541049</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3058561670120525</v>
+        <v>0.3005618859277419</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2563568167402934</v>
+        <v>0.2471410668147485</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3962243416689546</v>
+        <v>0.3868478625821936</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.07157001014726205</v>
+        <v>0.06249478051609003</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1754295523391747</v>
+        <v>0.16616777956866</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2029184260228263</v>
+        <v>0.1936212041954519</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4071100387349702</v>
+        <v>0.3974154738054665</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.4692733898833055</v>
+        <v>0.459534060586904</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.540384499682979</v>
+        <v>0.5305012745572455</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5276674470776825</v>
+        <v>0.5176176212301584</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.3592184272005952</v>
+        <v>0.3493504112315975</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.2500832918685134</v>
+        <v>0.240249551959117</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.2687298998695624</v>
+        <v>0.2589595491647074</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.1213143030849579</v>
+        <v>0.1117119443020584</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.06331284714641328</v>
+        <v>-0.07269322109165444</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.2389512292551927</v>
+        <v>0.2291987433336402</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.3794790975447881</v>
+        <v>0.3695640238692306</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.5862801751374604</v>
+        <v>0.5759987248602627</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.4640118660367278</v>
+        <v>0.4538743359022277</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.5595967858668089</v>
+        <v>0.5493699386280326</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.4704590934701116</v>
+        <v>0.4603323121383696</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.001345</t>
+          <t>X &lt; 0.001344</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3095</v>
+        <v>3099</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.05000338137619309</v>
+        <v>-0.05340316724362992</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.08117468691960283</v>
+        <v>0.07756416896157248</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1992696245046162</v>
+        <v>0.1953313981615921</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2738064130800026</v>
+        <v>0.2696838789942433</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2799035506990961</v>
+        <v>0.2726991411677062</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4210700795534166</v>
+        <v>0.4137028911386764</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.1484487951694646</v>
+        <v>0.1413335153862718</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2097405690648841</v>
+        <v>0.2025084922916207</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.3019325367294243</v>
+        <v>0.2945827294046595</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3829227075357409</v>
+        <v>0.3753704510369289</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.386531510912512</v>
+        <v>0.3790034801977242</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4802206162038871</v>
+        <v>0.4725337147206474</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.3404717001138948</v>
+        <v>0.3328231698469963</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2671323878067469</v>
+        <v>0.2595467008907448</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.2395614422767594</v>
+        <v>0.2319264043703342</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.2417673866258951</v>
+        <v>0.234197462230938</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.030233607768686</v>
+        <v>0.02291519145820331</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1844875003129687</v>
+        <v>-0.1915465979352433</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.1476336237344</v>
+        <v>0.1401685291915911</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.353944820909966</v>
+        <v>0.3462321064682712</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.5078809338038539</v>
+        <v>0.499898688252749</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.3868584197637048</v>
+        <v>0.3790182742399182</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4550383064927246</v>
+        <v>0.4471391570520353</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.4308496065149399</v>
+        <v>0.4229676893058638</v>
       </c>
     </row>
     <row r="29">
@@ -7714,79 +7714,79 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3137</v>
+        <v>3141</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.02841023981882529</v>
+        <v>0.02539814573364652</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.004865138185564888</v>
+        <v>-0.0078717777318289</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1874813995592746</v>
+        <v>0.1840799993390334</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.2832023336844713</v>
+        <v>0.2796035891845321</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2843603031063537</v>
+        <v>0.2781188763111402</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3627491382322532</v>
+        <v>0.3564242540290081</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1468594313551179</v>
+        <v>0.1407237796132321</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2670553793770338</v>
+        <v>0.2607347275526593</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.3585902807025363</v>
+        <v>0.3521542022819659</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4282043751260431</v>
+        <v>0.4215954988019632</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4354375598185598</v>
+        <v>0.4288442992987882</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.4924140641828885</v>
+        <v>0.4857155094082231</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3712969831460384</v>
+        <v>0.3646306681739944</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.2324394281749278</v>
+        <v>0.2259223066070533</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.1646422190445023</v>
+        <v>0.1581383305822612</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.2383346349987931</v>
+        <v>0.2317955676164587</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.0278342692478688</v>
+        <v>0.02154472432936672</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1854211742697203</v>
+        <v>-0.1914544927326745</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.01784162767683029</v>
+        <v>0.01156880183366127</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.2875278573702644</v>
+        <v>0.280927849395141</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.3684237948237055</v>
+        <v>0.3616598765528352</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.3116744174875095</v>
+        <v>0.304970747362681</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.3507280511086108</v>
+        <v>0.3439995911293678</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.3576907948332178</v>
+        <v>0.3509414972908829</v>
       </c>
     </row>
     <row r="30">
@@ -7796,79 +7796,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3185</v>
+        <v>3189</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.08933337582560341</v>
+        <v>-0.0916565779400571</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.02874486320325786</v>
+        <v>0.0262446649855832</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.07190093117688434</v>
+        <v>0.06922308280093858</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3426695207343116</v>
+        <v>0.3395918636210808</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.2759345235437394</v>
+        <v>0.2707796294914786</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.3247301059561494</v>
+        <v>0.3195272833413654</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1004790975672307</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2146811659191172</v>
+        <v>0.2095200087073295</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2741994177583749</v>
+        <v>0.2689644632200512</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.29987166563226</v>
+        <v>0.2945355366923579</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3110741183819457</v>
+        <v>0.305744318587621</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3629659361595614</v>
+        <v>0.3575443354976073</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2580280144701348</v>
+        <v>0.2526382823871884</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1178955821094405</v>
+        <v>0.1126589683038404</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.07248754728033902</v>
+        <v>0.06724819091163425</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.1539887611501527</v>
+        <v>0.1486952730305902</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.02406073543942711</v>
+        <v>-0.02914602156806012</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.235703780865002</v>
+        <v>-0.2405361876474217</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.0009152689746656506</v>
+        <v>-0.00602617221375823</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.26752116650988</v>
+        <v>0.2620869528990752</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.3076465169744367</v>
+        <v>0.3021121522803227</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.2505888089709885</v>
+        <v>0.2451161990002859</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.2931746296507356</v>
+        <v>0.2876690387387626</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.2988698853360532</v>
+        <v>0.2933473857272304</v>
       </c>
     </row>
     <row r="31">
@@ -7878,243 +7878,243 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3240</v>
+        <v>3244</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1650806457140206</v>
+        <v>-0.1667118211148519</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.02401181923019635</v>
+        <v>-0.02583824123676948</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.005881775772280662</v>
+        <v>-0.007823665253816614</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2175774004850908</v>
+        <v>0.2153147844503707</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1150815854205902</v>
+        <v>0.1113177264800882</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1968573531444164</v>
+        <v>0.1930030128776679</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.02470898382384235</v>
+        <v>0.02101398071366134</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.07082831588069638</v>
+        <v>0.06705664146098655</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1299981888797248</v>
+        <v>0.1261543290635672</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.142112624075601</v>
+        <v>0.1382018969013856</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1269750417034103</v>
+        <v>0.1230982635909044</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.05021116644733326</v>
+        <v>0.04640845735141141</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.02020766921390305</v>
+        <v>0.01636716103542568</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2136801973536606</v>
+        <v>-0.2172497520188301</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1464613783849487</v>
+        <v>-0.1501582845080804</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1179075822981943</v>
+        <v>-0.1216034887621618</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.2337009431345223</v>
+        <v>-0.2372652909254356</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.2895656030377651</v>
+        <v>-0.2930701951110066</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.1783766153430761</v>
+        <v>-0.1820063350806862</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.02697287299630347</v>
+        <v>0.02310011438687809</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.05713107419661867</v>
+        <v>0.05318370242145676</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.0305206612076816</v>
+        <v>0.02659881540853348</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.1078335247357316</v>
+        <v>0.1038318356145922</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.08122157244964257</v>
+        <v>0.0772454106502849</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.002042</t>
+          <t>X &lt; 0.002041</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3280</v>
+        <v>3284</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1773003339978416</v>
+        <v>-0.1784945280071142</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1025737223333465</v>
+        <v>-0.1038755754236433</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.01125124694717528</v>
+        <v>-0.01273524523032421</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.07963354474981799</v>
+        <v>0.07800350400599143</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.02609018866997559</v>
+        <v>-0.02884219091965434</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.08724239592384464</v>
+        <v>0.08436068362772176</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.03156606604658663</v>
+        <v>-0.03434359494595896</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.04093577992020414</v>
+        <v>0.03805496828752553</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.0998822705656579</v>
+        <v>0.09693033946069107</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1328017726234307</v>
+        <v>0.1297699771151954</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.09081042867457967</v>
+        <v>0.08784138144471854</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.04195379347262218</v>
+        <v>0.03902850458311491</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.06212681291398781</v>
+        <v>-0.06498311366743792</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1439116680106665</v>
+        <v>-0.1466813348001494</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1159072709911442</v>
+        <v>-0.1187452946159695</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.08045237872167377</v>
+        <v>-0.08330571817813848</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1660341661259679</v>
+        <v>-0.1687918641949508</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.2529082853933957</v>
+        <v>-0.2555672725017004</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.1099890010998834</v>
+        <v>-0.1128127454727874</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.03425700365408346</v>
+        <v>0.03126534876655995</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.08789158003646236</v>
+        <v>0.08480588082132812</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.06068914230642264</v>
+        <v>0.05763096922001409</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.04898300571234415</v>
+        <v>0.04595096045950697</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.1132149479389568</v>
+        <v>0.1100990927407892</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.002216</t>
+          <t>X &lt; 0.002215</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3304</v>
+        <v>3308</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0522398307583174</v>
+        <v>-0.05333585555145248</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.0706318572562239</v>
+        <v>-0.0717200078778788</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.05050114387975668</v>
+        <v>-0.05167239908252697</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.06464612543027926</v>
+        <v>0.06330686589833334</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.01722991754228076</v>
+        <v>0.01491943027506437</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1010065987008559</v>
+        <v>0.09860158356519122</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.03769840174722106</v>
+        <v>0.03533681632153218</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.01279857497510761</v>
+        <v>-0.01511208126940744</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.07613524180175801</v>
+        <v>0.07371499511236834</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.103212108254759</v>
+        <v>0.1007264139610555</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.06350078390229186</v>
+        <v>0.06107263736459601</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.04312635494783024</v>
+        <v>0.04070998779752699</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.0985073983856708</v>
+        <v>-0.1008002533163364</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1813140119398042</v>
+        <v>-0.1835174475856221</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1582971964503983</v>
+        <v>-0.1605566079498786</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1489932299505554</v>
+        <v>-0.1512409986475163</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.2651497158184952</v>
+        <v>-0.267264182089221</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.3521850854404676</v>
+        <v>-0.3542001333682876</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.2389854698422553</v>
+        <v>-0.241129683721617</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1549274486094347</v>
+        <v>-0.1571668949655916</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.01496484806659737</v>
+        <v>-0.01739697995830625</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.07280035272283669</v>
+        <v>-0.07516715079108849</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.08246653113876334</v>
+        <v>-0.08481182706751866</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.01929258173682769</v>
+        <v>-0.02171880120692293</v>
       </c>
     </row>
     <row r="34">
@@ -8124,79 +8124,79 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3326</v>
+        <v>3330</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01631310476543035</v>
+        <v>-0.01722647519755327</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.06664459064601402</v>
+        <v>-0.06750935330922658</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.0335242767078654</v>
+        <v>0.0324925211329159</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.08347349838057738</v>
+        <v>0.08235824362508026</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.004077035986135513</v>
+        <v>0.002228850571349028</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.08852996762890086</v>
+        <v>0.08658590175337366</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.02054849780559209</v>
+        <v>0.01865932935643144</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.03145488783876971</v>
+        <v>-0.03329209469132621</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.02722994753986541</v>
+        <v>0.02532282692461507</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.01086353792124584</v>
+        <v>-0.0127515162648848</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.04853967887566313</v>
+        <v>-0.0503747163484789</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.07065283428374869</v>
+        <v>-0.07247164357536917</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1888333791733245</v>
+        <v>-0.1905486376966152</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2126287308345738</v>
+        <v>-0.2143238275923309</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2540899279144355</v>
+        <v>-0.2557580455782684</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2109554751826721</v>
+        <v>-0.2126568258982928</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.3272489489976209</v>
+        <v>-0.328816384169194</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4144214603529619</v>
+        <v>-0.4158888632534214</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2705397427834484</v>
+        <v>-0.2721736244738437</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1858108108108141</v>
+        <v>-0.1875412548762085</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1104503339003244</v>
+        <v>-0.1122901902095634</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1383862338713371</v>
+        <v>-0.1401961835522272</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.116134130439761</v>
+        <v>-0.1179628659769847</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.08395663442028933</v>
+        <v>-0.08582765007998461</v>
       </c>
     </row>
     <row r="35">
@@ -8206,79 +8206,79 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.001041605511801436</v>
+        <v>0.0003607018433484654</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.007898454641939168</v>
+        <v>0.0072010808152001</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05160711164614895</v>
+        <v>-0.05226855322982971</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.05198236669817646</v>
+        <v>0.05118079752227089</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.0592177527281379</v>
+        <v>-0.06049059447439475</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.05566097210114407</v>
+        <v>0.05425557883269505</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.0472536882065171</v>
+        <v>-0.04855619021616064</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1009593559069728</v>
+        <v>-0.1022055424861747</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.07213153886669943</v>
+        <v>-0.07341172085253334</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1454383704256159</v>
+        <v>-0.1466507324507376</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1808355843975136</v>
+        <v>-0.1820001285438479</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.204898431927873</v>
+        <v>-0.2060417950988338</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2116250840267142</v>
+        <v>-0.2127880396567861</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2071436812069081</v>
+        <v>-0.2083180086210632</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2531975169770462</v>
+        <v>-0.2543335943747991</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2654965169594306</v>
+        <v>-0.2666044927418696</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2925998616946117</v>
+        <v>-0.2936795439141804</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3501061900089013</v>
+        <v>-0.3511206837476308</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2652619124261477</v>
+        <v>-0.2663729533808237</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2393815201192169</v>
+        <v>-0.2405196440153006</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1388324900951474</v>
+        <v>-0.1401041687485787</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.167134886054221</v>
+        <v>-0.1683754624130174</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.1430079831226365</v>
+        <v>-0.1442715084868098</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.1116451229536111</v>
+        <v>-0.1129486608075538</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_6_13.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/macd/macd_histogram_6_13.xlsx
@@ -618,1969 +618,1969 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.002401</t>
+          <t>X ≈ -0.002386</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.704200504269892</v>
+        <v>-7.337344933373821</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>2.086936337141161</v>
+        <v>0.05871129713236201</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-3.544352923131257</v>
+        <v>-5.010276725993933</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.428559390427623</v>
+        <v>-9.423827185161521</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.4843660443549211</v>
+        <v>-2.052712293792176</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>6.191574204418302</v>
+        <v>5.753640202764053</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>9.571110160404864</v>
+        <v>8.791241773834372</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.296793417901611</v>
+        <v>8.49009780544371</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.341112789273851</v>
+        <v>4.791188510827013</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.873308010784633</v>
+        <v>-3.660171996682756</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.5491518715186459</v>
+        <v>0.4413750015572759</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>4.42301500640675</v>
+        <v>0.1655449096159813</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.457456490340327</v>
+        <v>2.887568260418838</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.239259843151942</v>
+        <v>2.640928285733111</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>6.585307575128333</v>
+        <v>1.961640851399672</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>11.33691105624916</v>
+        <v>6.359184260810679</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>7.048685404530218</v>
+        <v>2.419221019431752</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-1.37226386480873</v>
+        <v>-5.391323929402404</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>7.163709766158611</v>
+        <v>2.502047970122206</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-0.9708994675005513</v>
+        <v>-4.96605240650446</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>2.649572410526233</v>
+        <v>-1.691841578899066</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-1.589672641280835</v>
+        <v>-5.611390375994304</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.849546698176631</v>
+        <v>-1.524598454337287</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>2.158931239824255</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.002227</t>
+          <t>X ≈ -0.002213</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1.903341225841338</v>
+        <v>10.0722729462873</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-9.469691168337746</v>
+        <v>-1.224664662465571</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-5.379351259485247</v>
+        <v>2.977614041619873</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-17.13724203429611</v>
+        <v>-11.12227863485624</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-17.47771637753542</v>
+        <v>-11.40100051462156</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.76682920169833</v>
+        <v>-5.723280219542694</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.483885319012231</v>
+        <v>4.538832946586112</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.761473740086551</v>
+        <v>4.236469567894105</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.720441422565862</v>
+        <v>4.365476493254349</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.042129297107792</v>
+        <v>9.106957479181929</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-2.217784234556355</v>
+        <v>3.846893137167271</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.03894557083445</v>
+        <v>9.107727633772924</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.154363395919759</v>
+        <v>-3.075790838013567</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-3.838685595531942</v>
+        <v>2.214754406582252</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-4.495919598111762</v>
+        <v>1.535377250901107</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-9.446574579477449</v>
+        <v>-3.446547887206108</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-4.039180418257629</v>
+        <v>1.992704385264055</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-9.690496258183941</v>
+        <v>-3.684860521435404</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-9.477972931988596</v>
+        <v>-3.471946467213812</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>1.80354736402284</v>
+        <v>7.839183774094153</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-4.288616770450041</v>
+        <v>1.723911811620503</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>1.186443236937698</v>
+        <v>7.201484495261163</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-9.64669179522862</v>
+        <v>-3.660703678896461</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>-3.823974743081727</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.002053</t>
+          <t>X ≈ -0.002039</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-9.823754183965583</v>
+        <v>-11.92276992428574</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.948536658123572</v>
+        <v>-8.867543663556702</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>7.045433528477993</v>
+        <v>3.09655029978066</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.339448528856209</v>
+        <v>5.79799083080907</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-6.42577801291786</v>
+        <v>-9.190531167257028</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>6.191183880693316</v>
+        <v>4.222999275067231</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2.315991477844229</v>
+        <v>0.1168010100807777</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.180104365747994</v>
+        <v>-6.821404773357948</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-13.47214740436512</v>
+        <v>-16.65053222437781</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-8.021953905255216</v>
+        <v>-10.80921963075406</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.751268525662205</v>
+        <v>-10.54116123873059</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.031834523316107</v>
+        <v>-10.82038397531595</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.039342157741821</v>
+        <v>-8.612768537090908</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.03066912808507993</v>
+        <v>-2.216377143310048</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-6.919634595339538</v>
+        <v>-9.545612825854562</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-3.211425257642816</v>
+        <v>-5.663279450580106</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-3.346079405827552</v>
+        <v>-5.768690264008754</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-9.690223082761349</v>
+        <v>-12.55753926272757</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-9.47775092198102</v>
+        <v>-12.34732822694887</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-9.294062335192777</v>
+        <v>-12.13677122078932</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-19.20547066956738</v>
+        <v>-22.69838353856568</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-16.16410000455165</v>
+        <v>-19.44911509338843</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-15.89474262945792</v>
+        <v>-19.21153754815137</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-15.97546728971891</v>
+        <v>-19.37953029863804</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.001878</t>
+          <t>X ≈ -0.001865</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.649726016415187</v>
+        <v>1.480294572855549</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.378646746139395</v>
+        <v>1.229100675159486</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-5.533190768131092</v>
+        <v>-2.599178293547062</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.8908286886933183</v>
+        <v>-3.206034906435463</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>9.522461745186533</v>
+        <v>9.265035393730713</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.653442755665885</v>
+        <v>3.202501989361608</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.8649456285328796</v>
+        <v>2.412532523627192</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-2.1097517576831</v>
+        <v>-0.4417081769275271</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.762471419960562</v>
+        <v>-5.418465966570359</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-2.864186217708209</v>
+        <v>-3.659398546906253</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.971340998393423</v>
+        <v>-8.497121281625184</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-5.563061722811661</v>
+        <v>-3.666344086938288</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.324281669386814</v>
+        <v>-2.223422158348605</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-4.244411701025498</v>
+        <v>-5.028136932121406</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-7.620482021956974</v>
+        <v>-8.266528648425371</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-7.013123329006653</v>
+        <v>-5.151415060118403</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-1.757351504937333</v>
+        <v>-0.1394643656369325</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-7.266544019106234</v>
+        <v>-5.39072686287151</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-9.745795187934554</v>
+        <v>-7.738597604580619</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-1.457149694294991</v>
+        <v>0.1561819160791842</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-2.016809480287577</v>
+        <v>-0.4107239551371364</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.236930410240568</v>
+        <v>2.076416492491916</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>2.511849552404279</v>
+        <v>2.320454889495494</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-5.671413235666186</v>
+        <v>-2.969273888380286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.001704</t>
+          <t>X ≈ -0.001692</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.626848882083422</v>
+        <v>-4.262990766213711</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.971497052815941</v>
+        <v>-3.131583546133399</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.84355137661322</v>
+        <v>-6.394470349665902</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.02867424526066742</v>
+        <v>1.303856391771347</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9168557021558286</v>
+        <v>-1.733742255850864</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.6748052578639587</v>
+        <v>-0.1977508147309806</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>5.50305216395931</v>
+        <v>3.156004594398809</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.385622546566708</v>
+        <v>-2.67403565337078</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.057024279107267</v>
+        <v>0.2183519667233185</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.530306225976041</v>
+        <v>-3.339702240514207</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.8517935293655796</v>
+        <v>-1.686017601998103</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.132475812189206</v>
+        <v>-3.346538314546287</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-5.076246839586908</v>
+        <v>-5.843158638869781</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.086228647534789</v>
+        <v>-1.938977279015866</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.3498190503470084</v>
+        <v>-1.234247889792407</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-2.559595122665868</v>
+        <v>-4.831247719574073</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.1170603296417596</v>
+        <v>-2.164913490687091</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.008002161762910021</v>
+        <v>-2.297878332273804</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-1.180380333601569</v>
+        <v>-3.471344024831723</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.9905700246299318</v>
+        <v>-3.258336936349124</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.134275410244399</v>
+        <v>-2.438706561020233</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.2101213716535</v>
+        <v>-2.514761146977328</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.4944586294342415</v>
+        <v>-3.660599887548052</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.8379129919705122</v>
+        <v>-3.823974743081727</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.00153</t>
+          <t>X ≈ -0.001518</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2.206625251189386</v>
+        <v>3.25809490564373</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1.864695511206101</v>
+        <v>0.7547982600275986</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-6.707126002759217</v>
+        <v>-7.271908464981571</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.066143897225523</v>
+        <v>-5.601312531784153</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-5.404308536175527</v>
+        <v>-3.616525941893961</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-5.209626309265907</v>
+        <v>-1.202077901389501</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-9.38376782138409</v>
+        <v>-8.775176059298403</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-9.662901299438225</v>
+        <v>-9.080390227951419</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-7.252946491770203</v>
+        <v>-6.693171788678001</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-10.39668542536479</v>
+        <v>-7.48734534361602</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.381525365023691</v>
+        <v>-4.955039044889077</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.831816926262995</v>
+        <v>6.087716567415235</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>5.087019353630716</v>
+        <v>7.243217661341696</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.867681459858332</v>
+        <v>6.997536119877871</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>6.588623236644473</v>
+        <v>8.586341111769563</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>2.431096889208291</v>
+        <v>4.61492990064346</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-2.456442383988737</v>
+        <v>-0.02301618864256483</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>4.572024193407927</v>
+        <v>6.649914172289641</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>4.789030301606651</v>
+        <v>4.596882189982743</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>7.35651232109214</v>
+        <v>7.082234215034617</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>9.19657312224799</v>
+        <v>8.788074883681418</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.360342802754282</v>
+        <v>4.172978890312393</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>4.634696802645152</v>
+        <v>4.417689168133364</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>2.179294615042281</v>
+        <v>1.984106064998556</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.001356</t>
+          <t>X ≈ -0.001344</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12.35987603446801</v>
+        <v>12.39524941570946</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10.25547405398414</v>
+        <v>11.40613164838227</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>10.60543557098722</v>
+        <v>13.3445745027767</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.344972712188692</v>
+        <v>11.14243007097872</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.786845220966143</v>
+        <v>7.658059873890345</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>7.971805469488444</v>
+        <v>6.215590143107882</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.872268442784666</v>
+        <v>2.204201933373092</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-5.513734584406549</v>
+        <v>-2.00401901166542</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.917367876991591</v>
+        <v>-0.2716135554571721</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.427731063863064</v>
+        <v>5.358842568865064</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.922754059839924</v>
+        <v>5.63165929485406</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.20469424532719</v>
+        <v>8.569986603140393</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>8.647585891285239</v>
+        <v>9.068726871845818</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>8.429458241704225</v>
+        <v>8.823721920546539</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>9.557610154075071</v>
+        <v>9.755149492877329</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>6.589523092228305</v>
+        <v>5.492054602267132</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>8.240587291417654</v>
+        <v>6.999211305339834</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>11.70543525435731</v>
+        <v>8.478803267732744</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>6.572872931308005</v>
+        <v>5.475003451414025</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>4.976966214308987</v>
+        <v>4.079968413840419</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>6.221261560547852</v>
+        <v>5.12567327349997</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>6.145436358878676</v>
+        <v>5.052093936636844</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>6.419786512919913</v>
+        <v>5.297125725966957</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>8.131675567423237</v>
+        <v>6.749501959427597</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.001182</t>
+          <t>X ≈ -0.001171</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-4.187913023039322</v>
+        <v>-4.738462308737631</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.822329615957294</v>
+        <v>-2.805856460969068</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.726933630071329</v>
+        <v>2.463195741977714</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.188167108760013</v>
+        <v>4.042049767824068</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>13.08723029129274</v>
+        <v>9.231821540804745</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>11.15897069483329</v>
+        <v>8.30675526388459</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>7.205474854783326</v>
+        <v>5.9166087619761</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>9.044331285420355</v>
+        <v>6.695490518551857</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6.969477827093172</v>
+        <v>7.448278412586269</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>4.073187934340019</v>
+        <v>2.905514210965016</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>10.71184251521687</v>
+        <v>9.742475532942109</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>4.073098331552018</v>
+        <v>1.807042607601375</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>7.187052551699203</v>
+        <v>6.170979224986489</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>5.906327103240187</v>
+        <v>4.829928285258475</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>5.243039775851891</v>
+        <v>4.151987622083453</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>5.843332612774077</v>
+        <v>6.905535818219178</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>7.835626861915401</v>
+        <v>10.09294444496397</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>5.606096484330195</v>
+        <v>7.770453231655807</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>6.888012658674477</v>
+        <v>9.084306471067478</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>6.016400611742327</v>
+        <v>8.20395846583591</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>6.533539051155167</v>
+        <v>8.737562416964579</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>5.393171605640696</v>
+        <v>7.56709996007941</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>6.735626286581635</v>
+        <v>8.911576508233402</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>8.359639093259098</v>
+        <v>9.851238932131942</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.001008</t>
+          <t>X ≈ -0.0009972</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-6.443477210350004</v>
+        <v>-6.250113328066384</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-1.203359406323806</v>
+        <v>-1.116045690501288</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.508414622948322</v>
+        <v>-5.066833189845589</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.809167285080463</v>
+        <v>1.5132696116967</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.263361743104468</v>
+        <v>5.722165335084242</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.448547491815866</v>
+        <v>5.880886110102288</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.54139054731808</v>
+        <v>5.978197161866071</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>7.128408512586432</v>
+        <v>8.361327855320681</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.588543180113525</v>
+        <v>1.314517803379786</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.973419623807914</v>
+        <v>-2.17643564327917</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1609630685050121</v>
+        <v>-0.49046443472254</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.117307028190254</v>
+        <v>-0.7666408667018487</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.557996087477221</v>
+        <v>0.8141120274975862</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.120661037401042</v>
+        <v>-7.513368222729724</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.2506243207271837</v>
+        <v>-1.908577322979198</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.275818940201624</v>
+        <v>-1.349237982385908</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>6.741994943688496</v>
+        <v>3.039818011020003</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>2.905380328789462</v>
+        <v>0.2116073732768555</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.3203755789366838</v>
+        <v>-2.272148676411618</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>1.441461922501176</v>
+        <v>-0.2594609102582908</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.03517967541998246</v>
+        <v>-1.726361710038368</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.8235538024232483</v>
+        <v>-0.9017784320119375</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>2.032607954157854</v>
+        <v>0.2419688556295938</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>1.022196261682026</v>
+        <v>-0.8209717400787255</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.0008333</t>
+          <t>X ≈ -0.0008235</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3.021737195604132</v>
+        <v>4.246762137752725</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.189100904027093</v>
+        <v>2.514584799190153</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.134280352939406</v>
+        <v>4.227743702524911</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>3.165151283921148</v>
+        <v>3.634489139990393</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.333626089025607</v>
+        <v>1.130484154794537</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.7760323409258021</v>
+        <v>-0.9403898115097249</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.7544409688436033</v>
+        <v>-2.481590348211661</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-4.033806464641529</v>
+        <v>-5.760117251994927</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.000494062532418</v>
+        <v>-2.660819336716145</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.786237006420173</v>
+        <v>-1.974222874911099</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-2.570537169475017</v>
+        <v>-3.186447090248222</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.665131653333972</v>
+        <v>-3.035595638635257</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-4.285814211486944</v>
+        <v>-5.634827765603234</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-3.007414426378318</v>
+        <v>-3.652630327994224</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-4.415461060444756</v>
+        <v>-5.077744901401161</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-3.07312208507895</v>
+        <v>-3.775622651554478</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-4.710049523872343</v>
+        <v>-4.625924508346358</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-3.313919254734799</v>
+        <v>-3.270146043998764</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-2.347917147167777</v>
+        <v>-2.312050039990787</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.8443497760761502</v>
+        <v>0.1366641964652189</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>1.053991851528615</v>
+        <v>0.3154115546825409</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.525613508376729</v>
+        <v>-1.25106660240607</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.2511387958948461</v>
+        <v>-1.008089983704352</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.928668048626413</v>
+        <v>0.3219622386761429</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.0006591</t>
+          <t>X ≈ -0.0006499</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.058144795008268</v>
+        <v>2.385797244912602</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.793029467865303</v>
+        <v>-0.02659563885207916</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>2.554150623994161</v>
+        <v>0.3337705755871951</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>3.503603861286919</v>
+        <v>0.8220974983185911</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.95380661732753</v>
+        <v>2.712774016030806</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>5.033893523240337</v>
+        <v>2.871970134270775</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>2.014772895645116</v>
+        <v>-0.6375041942652615</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.724311955470085</v>
+        <v>-1.488319783923764</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.082734215442521</v>
+        <v>-0.2784048014544567</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>4.406331022734115</v>
+        <v>1.083482482917766</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2275802782904393</v>
+        <v>-1.889235159836332</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5050495393464871</v>
+        <v>-0.001342188239433995</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.525260574677141</v>
+        <v>-2.970590938318985</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-2.748438616761902</v>
+        <v>-2.899530568734313</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.6224209488338133</v>
+        <v>-1.413961479823691</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-1.141510618793092</v>
+        <v>-1.396831285997756</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.514807615426946</v>
+        <v>0.6660151332379627</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>1.96716056827362</v>
+        <v>1.076524026524737</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>1.067354853890471</v>
+        <v>1.291165257050736</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.6983979588801503</v>
+        <v>1.505377869521872</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.604250178911016</v>
+        <v>2.024938424770198</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.528404217502043</v>
+        <v>1.407597103304944</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.802878929984097</v>
+        <v>2.19479389952604</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.285705894637914</v>
+        <v>2.576991440493146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.0004848</t>
+          <t>X ≈ -0.0004763</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.786982602589582</v>
+        <v>1.918441433615648</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6760867742293115</v>
+        <v>2.062813745526029</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.7631582965225832</v>
+        <v>0.8136324001530113</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.07529735100045087</v>
+        <v>2.166946129669675</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1276658006249107</v>
+        <v>1.50127589518388</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.642458905198076</v>
+        <v>4.379305074672253</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.869449878197543</v>
+        <v>3.590069925413943</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4.527935406261328</v>
+        <v>6.010922545875083</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>4.957820978223296</v>
+        <v>6.527961230578505</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>5.739559552720145</v>
+        <v>7.292024006449182</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>5.624985095869469</v>
+        <v>6.396261483083819</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>6.898179289852408</v>
+        <v>7.675450415778727</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>6.166479829593989</v>
+        <v>7.343455338746232</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>5.560884681629403</v>
+        <v>6.707949087800053</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>4.906253833613242</v>
+        <v>6.420111072511482</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>3.559551675194001</v>
+        <v>4.257144181625904</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.7064038411300331</v>
+        <v>1.427593052537603</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.99104309195355</v>
+        <v>1.296342810071721</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>3.152054669815321</v>
+        <v>3.849805180118565</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>4.507511952381158</v>
+        <v>5.234902573930214</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>4.354070842780892</v>
+        <v>5.450773021962718</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>6.612855231566336</v>
+        <v>7.719892088019272</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>3.774489477122323</v>
+        <v>4.062029454014102</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.364026873704503</v>
+        <v>1.167344701362715</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.0003106</t>
+          <t>X ≈ -0.0003027</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-4.744418375244109</v>
+        <v>-5.396216679824555</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6154362675033553</v>
+        <v>-1.151321068777669</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.535400563754031</v>
+        <v>-3.521436819836453</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.33023310947214</v>
+        <v>0.3757066288218596</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.609737663167351</v>
+        <v>-2.145776401021138</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8062935947837246</v>
+        <v>-1.24397156296078</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.03908492132134711</v>
+        <v>-1.657610897626306</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.5062157972915315</v>
+        <v>-0.463572348826915</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-2.054847942301308</v>
+        <v>-2.954422878012345</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.5935141600785201</v>
+        <v>-1.501198018730172</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.063908086684656</v>
+        <v>-1.603912218725178</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.5992407986457735</v>
+        <v>-1.507220690975849</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.9743942889127695</v>
+        <v>-1.493913699870951</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.2938107346008678</v>
+        <v>0.1307131127663865</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.851379146416626</v>
+        <v>-1.296888871998135</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-3.120553983342873</v>
+        <v>-2.235222434808996</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-4.373843967158855</v>
+        <v>-3.839303135452354</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.225859784939686</v>
+        <v>-4.347545070019862</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-4.639622481015593</v>
+        <v>-4.511103053759555</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-6.320642992737604</v>
+        <v>-6.551257751152768</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-5.743786175629005</v>
+        <v>-5.619161840654641</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-5.446497808679894</v>
+        <v>-5.696773705223315</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-5.17202309619784</v>
+        <v>-4.328368320208774</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-5.247855349421116</v>
+        <v>-4.492312253524503</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0001364</t>
+          <t>X ≈ -0.0001291</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.619461919489595</v>
+        <v>3.468301811860066</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-2.893295769010301</v>
+        <v>-1.445617137406195</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.582064314698883</v>
+        <v>-0.6542179539706581</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-3.51526747613363</v>
+        <v>-1.247868739605579</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-4.155821050352337</v>
+        <v>-2.69028802322886</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-2.45002575300623</v>
+        <v>-1.660251701667967</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.1346082550610888</v>
+        <v>0.1739631274016773</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7509353783072044</v>
+        <v>-0.4217645387412432</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5108009455995699</v>
+        <v>1.748965927363088</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.263695336763938</v>
+        <v>2.121591701961123</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6234656739114328</v>
+        <v>1.226625049361516</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-4.224536239881004</v>
+        <v>-3.717969018672193</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-3.819494768924166</v>
+        <v>-3.954877581146597</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-3.431912197527637</v>
+        <v>-3.619000023457609</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-3.17442720575503</v>
+        <v>-3.250685746993099</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-2.277227118784914</v>
+        <v>-2.400077149617864</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-4.244220730917725</v>
+        <v>-3.9656617642596</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-4.045625880486902</v>
+        <v>-2.930242464897923</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-2.915689704164635</v>
+        <v>-2.426471813006835</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.507552481988625</v>
+        <v>-1.337021857528853</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.744288252401041</v>
+        <v>-1.611750574325377</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-3.654996599131309</v>
+        <v>-3.15244348148326</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-3.074711489095733</v>
+        <v>-2.324623401644089</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-2.233112549658465</v>
+        <v>-1.608269301569834</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 3.779e-05</t>
+          <t>X ≈ 4.451e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-2.941113040614219</v>
+        <v>-2.477488797882408</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5453306640423818</v>
+        <v>-0.6346708159507699</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.974194617997199</v>
+        <v>-1.878701375879416</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.9849478902011981</v>
+        <v>-2.12770169549065</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.66152182826157</v>
+        <v>-1.359448989287479</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-4.207975784297219</v>
+        <v>-3.294917284360444</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-2.247648712939153</v>
+        <v>-1.301233220195797</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8187957661942491</v>
+        <v>-0.21305760460816</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.5875418580995415</v>
+        <v>-0.08512869492405173</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.8640797817518902</v>
+        <v>-1.919107702949049</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2492366740768404</v>
+        <v>-1.299058309025085</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.519861779486149</v>
+        <v>1.555424567067348</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>2.788478099086554</v>
+        <v>3.575642071959443</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.206279839039929</v>
+        <v>2.286538830972205</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-1.154279742683002</v>
+        <v>-0.1277009889835128</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-1.92792356332648</v>
+        <v>-0.6113212514185733</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-1.379419271837882</v>
+        <v>-0.01869554840460097</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.511172087142278</v>
+        <v>-1.543376027122477</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-2.982865251212637</v>
+        <v>-2.02943995637937</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-4.168731318233412</v>
+        <v>-3.213833241748809</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-4.368811732774859</v>
+        <v>-3.782756061534045</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-3.759726187334564</v>
+        <v>-3.511277758878741</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-3.485251474852511</v>
+        <v>-3.270834063889936</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-5.273412495199082</v>
+        <v>-4.134775053882045</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.000212</t>
+          <t>X ≈ 0.0002181</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1420283136776632</v>
+        <v>-0.527465459630541</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2.204790864271594</v>
+        <v>0.8295602878606303</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.958063537015619</v>
+        <v>0.3814923946894595</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.247995744929533</v>
+        <v>-0.2132463703631302</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.311318927156748</v>
+        <v>2.314818477762628</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7034736008487101</v>
+        <v>0.4663826085471854</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7279059340180822</v>
+        <v>1.677059499235412</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.04822417692085423</v>
+        <v>0.5721331181320295</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.7106054228013221</v>
+        <v>-0.9018969861104082</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.2869816909596707</v>
+        <v>0.3074209938837384</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.012139697059034</v>
+        <v>-1.022303005438474</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-2.69209702854603</v>
+        <v>-2.499964792647198</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.219090866492593</v>
+        <v>-4.012815383481538</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.004638046426564</v>
+        <v>-5.461155708383671</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.06459170447610774</v>
+        <v>-0.5327539783057986</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.2719520868519751</v>
+        <v>-0.5321835833604496</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.3938919135869412</v>
+        <v>-0.2350730501376361</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.489330190106244</v>
+        <v>0.4369623439943524</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.3013234874207456</v>
+        <v>-0.154669421614706</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.2695730412899735</v>
+        <v>-0.7475051406933133</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.8121192092560037</v>
+        <v>-2.119390424393707</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4863587449622884</v>
+        <v>-1.794380033775859</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.6134904581830938</v>
+        <v>-1.151043476103496</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1138901399992491</v>
+        <v>-0.5085625567017971</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.0003862</t>
+          <t>X ≈ 0.0003918</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.8190865732738715</v>
+        <v>-0.6457889485871107</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4493288179806427</v>
+        <v>-1.844613392246742</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.197035817697277</v>
+        <v>2.641258768947402</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1.611043294113607</v>
+        <v>0.1332380628665533</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8059960442814287</v>
+        <v>-0.1465129163876284</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.3466739810478</v>
+        <v>-1.903800204610484</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-2.113747703273155</v>
+        <v>-2.213688331292929</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.388856899693927</v>
+        <v>-2.036908921780125</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.345597004446425</v>
+        <v>-1.429376578751985</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.24636053300847</v>
+        <v>-0.7880153869910131</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5034872918947784</v>
+        <v>-0.03617693904275399</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.6215450315132003</v>
+        <v>1.121159760837187</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.307719131701781</v>
+        <v>2.876900178192201</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>3.492194695443963</v>
+        <v>3.58927059649865</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>1.903864749339206</v>
+        <v>1.48018562552037</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>3.435411951269458</v>
+        <v>3.471914266062214</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>2.366845865253893</v>
+        <v>1.939886904128741</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>5.077417134191293</v>
+        <v>5.156534060425628</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>7.643586805170493</v>
+        <v>7.763662001308361</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>3.135596934387394</v>
+        <v>3.193867617264011</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>4.940468606796848</v>
+        <v>5.027339539447155</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>3.925655509237508</v>
+        <v>4.955923151559752</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>3.261163085569379</v>
+        <v>4.241246732448637</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>2.715847264270991</v>
+        <v>4.082008162901175</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.0005604</t>
+          <t>X ≈ 0.0005654</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.263508788238575</v>
+        <v>2.431138426331671</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2059171770856523</v>
+        <v>0.5615433012634199</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.174297468623351</v>
+        <v>4.186512195651694</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.059141441863027</v>
+        <v>5.216007009502384</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.5156707974517971</v>
+        <v>0.6055978563223761</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.835943463134704</v>
+        <v>2.385144985661476</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.139711158911567</v>
+        <v>2.135591467310292</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>7.673691315648909</v>
+        <v>6.707109722111582</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>7.183698072826857</v>
+        <v>6.294525712689811</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>8.01663651380558</v>
+        <v>7.667332745375205</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>9.361041786079419</v>
+        <v>9.565405581390735</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>7.481809015171464</v>
+        <v>7.66477708221386</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>6.899526184773826</v>
+        <v>6.552751007491871</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>7.21731251370241</v>
+        <v>7.390558359046175</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>6.037580413325152</v>
+        <v>6.169682334760701</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>7.173767433939702</v>
+        <v>6.72991158755714</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>7.048810165250742</v>
+        <v>8.038958922853972</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>5.340624120414844</v>
+        <v>6.288954534676904</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.561200011288911</v>
+        <v>5.417486108678034</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>10.04912109007408</v>
+        <v>10.53242920678456</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>10.04420933071027</v>
+        <v>11.61223773387094</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>10.50599777790332</v>
+        <v>12.09616552093463</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>9.705203673181074</v>
+        <v>9.623812630928477</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>9.629371419957771</v>
+        <v>9.472928717756155</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.0007346</t>
+          <t>X ≈ 0.000739</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.30932080903704</v>
+        <v>-5.786747592782106</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.35834447964492</v>
+        <v>2.490252033475556</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.25323731630354</v>
+        <v>0.58898628117106</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-2.1267528581512</v>
+        <v>-2.638650438702776</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-2.462612609763148</v>
+        <v>-2.911411554835681</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-3.609025943042333</v>
+        <v>-4.731952723624232</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-7.048668933059531</v>
+        <v>-8.132900505274279</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-3.325737273244521</v>
+        <v>-4.512240150757798</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.283886376239892</v>
+        <v>-2.413829026203466</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.056871331341171</v>
+        <v>-3.205684985472963</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-3.116537603879344</v>
+        <v>-4.898338137806078</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.061803569353735</v>
+        <v>-3.858002087736146</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-3.185277392001204</v>
+        <v>-4.961706109320872</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.406564105641948</v>
+        <v>-5.201549098854507</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-3.402833309677661</v>
+        <v>-5.216154150577864</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.8050589391333602</v>
+        <v>-2.694157500770558</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-4.293256007927759</v>
+        <v>-6.068655988108148</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-4.410271504582454</v>
+        <v>-6.205333234313471</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.445583563799488</v>
+        <v>-4.694504383883853</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.587596814234139</v>
+        <v>-3.175684286352194</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.1167201634082247</v>
+        <v>-2.426732632357052</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.8637070644146405</v>
+        <v>-3.163230529511061</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.5892323519325871</v>
+        <v>-2.92328443286948</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.678487423947772</v>
+        <v>-5.074894537047882</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.0009089</t>
+          <t>X ≈ 0.0009126</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.779184382630973</v>
+        <v>1.499984265153508</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.595399710265454</v>
+        <v>2.021553577062321</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.872530267533634</v>
+        <v>2.315396641167546</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5.503135303209028</v>
+        <v>4.806483903581494</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>8.627628295228661</v>
+        <v>8.392241750047589</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>7.963444875026937</v>
+        <v>7.001285088657049</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>8.029795403734973</v>
+        <v>8.531272970548102</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>8.634859549533076</v>
+        <v>7.448526001796097</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5.207496337746925</v>
+        <v>5.26108849647904</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>7.89486412627744</v>
+        <v>8.326999886433143</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.162498571588905</v>
+        <v>8.601175596862092</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>10.4736074358574</v>
+        <v>10.64254765182473</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>13.66187843986749</v>
+        <v>12.62084847471856</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>10.82952397286968</v>
+        <v>10.06048249132498</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>13.27328739848725</v>
+        <v>10.92751217404484</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>14.38616936161841</v>
+        <v>12.25693923908537</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>16.01952687140096</v>
+        <v>13.70224289196532</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>15.94371910254785</v>
+        <v>14.81605903730063</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>13.55091483129822</v>
+        <v>12.72091228967946</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>9.389934554309818</v>
+        <v>9.073698274205313</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>10.58651882112635</v>
+        <v>10.0790464105991</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>10.51067285971725</v>
+        <v>10.02753758054897</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>11.6547127895906</v>
+        <v>11.07140391161384</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>13.3180109711499</v>
+        <v>12.49546970136272</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.001083</t>
+          <t>X ≈ 0.001086</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.702656823575936</v>
+        <v>10.57837382263258</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.271587374307479</v>
+        <v>4.902280149455905</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>2.80896202606386</v>
+        <v>2.563099848655938</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-6.192213778155697</v>
+        <v>-6.717178244130729</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-11.72813548429887</v>
+        <v>-12.42174809398595</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-12.55822966565562</v>
+        <v>-12.26575459016139</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-14.4210576146377</v>
+        <v>-15.22957397466745</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-21.95402627723858</v>
+        <v>-22.0503425821741</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-14.64547872786984</v>
+        <v>-15.40750561056547</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-14.36852563750217</v>
+        <v>-16.20402715687139</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-7.856769144946476</v>
+        <v>-9.417119105885995</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-6.056286264929902</v>
+        <v>-7.522378407106942</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-8.237519197927774</v>
+        <v>-8.636330422384283</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-5.370507523193197</v>
+        <v>-5.625465274051578</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-7.090822736784339</v>
+        <v>-6.306209502676381</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-9.596829515628727</v>
+        <v>-10.08919596916105</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-7.078548360454761</v>
+        <v>-9.106004901000688</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-7.625121477162288</v>
+        <v>-11.4095065827826</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-4.28423009623787</v>
+        <v>-7.95268456581114</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.014050952936628</v>
+        <v>-5.566956590032355</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-1.514930454236001</v>
+        <v>-3.951815115176096</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-3.674109748978367</v>
+        <v>-5.604107552966973</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-2.357968369829706</v>
+        <v>-5.367509155980805</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.3504672897195391</v>
+        <v>-2.23667315578011</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.001257</t>
+          <t>X ≈ 0.00126</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.4767999453915621</v>
+        <v>-1.073289921424369</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.034447441193542</v>
+        <v>-2.53125218605107</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>3.409886450951966</v>
+        <v>2.241768173506642</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8324793331966873</v>
+        <v>-1.965091856626856</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.184671370726655</v>
+        <v>0.168988557490664</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.371637556823998</v>
+        <v>0.3114498598598345</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.952630049404206</v>
+        <v>1.965805236823499</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.497948016415876</v>
+        <v>0.4524474403992897</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3.892376374801202</v>
+        <v>2.975542600671346</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4099510659412147</v>
+        <v>-0.2301474487648818</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.488832600249872</v>
+        <v>-2.371169064284672</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.591111415462578</v>
+        <v>-1.453785969369221</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-6.243685247024573</v>
+        <v>-6.157809386794689</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.935352358765321</v>
+        <v>-2.780731389180801</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>0.162426287981134</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.6461675579322943</v>
+        <v>-0.488325122122113</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-3.133025871380362</v>
+        <v>-2.976517556713354</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-4.414337163436798</v>
+        <v>-4.292512483539952</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-3.021975194277218</v>
+        <v>-2.915782698107826</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.4821882078386324</v>
+        <v>-0.3010489938638159</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-2.20120496403986</v>
+        <v>-2.079302514508221</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-2.277050925449032</v>
+        <v>-2.148580952909498</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-3.179046801202198</v>
+        <v>-3.120984734265242</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.9019378779549498</v>
+        <v>-0.8429449327836593</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.001432</t>
+          <t>X ≈ 0.001434</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>42</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5.882962410377559</v>
+        <v>8.056490926370344</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-6.35657629273409</v>
+        <v>-3.948530436614213</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6517381989080064</v>
+        <v>1.854451031280668</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.016260162601625</v>
+        <v>3.618285444764346</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>0.9864906923731098</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.894468885752957</v>
+        <v>-1.16867524556227</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.09548719226145153</v>
+        <v>2.627339028803007</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.579180509413142</v>
+        <v>7.045926077067975</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>4.620667691327775</v>
+        <v>4.861755442818549</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.847752015291285</v>
+        <v>4.065703947599211</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>4.121811657453208</v>
+        <v>4.348973229293186</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.462109873052832</v>
+        <v>1.749257463798848</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.719900187149165</v>
+        <v>2.913362089012686</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.263083451202327</v>
+        <v>-2.080447998273286</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-5.302179129735194</v>
+        <v>-5.151941793719239</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.05411255411248561</v>
+        <v>0.1439039838635807</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.07980458286491654</v>
+        <v>-0.03721629748879707</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1846452866860986</v>
+        <v>-2.59254261748022</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-9.492563429571298</v>
+        <v>-10.3183244418053</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-4.543812857698441</v>
+        <v>-5.370173909435024</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-9.848263787569302</v>
+        <v>-10.67646968022866</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-5.162204987073714</v>
+        <v>-3.658199115719484</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-7.268682655543962</v>
+        <v>-6.825142240736938</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-4.963562527814858</v>
+        <v>-4.617625536732518</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.001606</t>
+          <t>X ≈ 0.001607</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-7.807513780098638</v>
+        <v>-4.703763451707623</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>2.274376088218162</v>
+        <v>5.173706794513755</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-7.496976294146101</v>
+        <v>-4.184733007338586</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4.290069686411186</v>
+        <v>7.428923687999145</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2123874528027869</v>
+        <v>3.076272525816982</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.108754600038708</v>
+        <v>1.238794921953001</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.880703283929151</v>
+        <v>0.3302221352592127</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-3.158914728682227</v>
+        <v>0.06313195000429062</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.200760880100795</v>
+        <v>-1.803350350173673</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-8.057009889470621</v>
+        <v>-4.631643313408816</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.782950247308698</v>
+        <v>-4.346798212753157</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-8.061699650756694</v>
+        <v>-6.630401463137815</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-7.101528384279476</v>
+        <v>-7.820954096895989</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-7.322607260725952</v>
+        <v>-8.13223858858521</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-5.897417224973296</v>
+        <v>-6.832591846659405</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-5.303030303030305</v>
+        <v>-6.220847483634849</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-3.353614106674442</v>
+        <v>-4.380757029702629</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-3.458454810495624</v>
+        <v>-4.601911737222764</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-1.159230096237962</v>
+        <v>-2.266937439702652</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-0.9723842862699357</v>
+        <v>-0.7902074817763705</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-3.598263787569302</v>
+        <v>-2.247398125516433</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-3.674109748978402</v>
+        <v>-2.321096647237532</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-3.399635036496349</v>
+        <v>-2.078926162193341</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-3.475467289719624</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="30">
@@ -2590,79 +2590,79 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.549938022522873</v>
+        <v>-2.739805599659185</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.066533002690875</v>
+        <v>-1.18499214724789</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-4.504552051721866</v>
+        <v>-2.454692251540344</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-7.03568788934647</v>
+        <v>-4.780287727659484</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-9.189660180075514</v>
+        <v>-6.864069157074589</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-7.184512175796343</v>
+        <v>-4.906415262961239</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.320097223323039</v>
+        <v>-2.197595714569701</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-8.234672304439741</v>
+        <v>-6.051435725805447</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-8.193185122525065</v>
+        <v>-5.908500813720451</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-8.966100798561527</v>
+        <v>-6.712055310140215</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-10.51022297458142</v>
+        <v>-8.218031580049718</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-18.06169965075669</v>
+        <v>-15.62996767617769</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-13.73031626306736</v>
+        <v>-11.43273494368846</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-19.40594059405946</v>
+        <v>-17.07562686826684</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-12.79135661891269</v>
+        <v>-10.63743311089615</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-15.83333333333328</v>
+        <v>-13.61754565870313</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-12.33088683394717</v>
+        <v>-10.1950155062025</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-3.344818446859264</v>
+        <v>-1.451849191196061</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-10.4016543386622</v>
+        <v>-8.32022009730354</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-13.85117216505782</v>
+        <v>-13.38774649738265</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-14.39371833302385</v>
+        <v>-12.16947671304904</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-12.65138247625108</v>
+        <v>-12.25214223620483</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-10.55872594558723</v>
+        <v>-8.429576178297403</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-12.45274001699235</v>
+        <v>-11.16524458435155</v>
       </c>
     </row>
     <row r="31">
@@ -2672,79 +2672,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-1.140847113431995</v>
+        <v>-2.323114532988676</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.475623911781781</v>
+        <v>-5.00804575893639</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4136429608127656</v>
+        <v>1.054333309903711</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-11.12659698025548</v>
+        <v>-9.294166449880123</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-11.46238745280275</v>
+        <v>-9.569724589979394</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-8.775421266705408</v>
+        <v>-6.973766593737473</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-4.547369950595787</v>
+        <v>-2.890799825482418</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-2.325581395348827</v>
+        <v>-0.7566958786471005</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.284094213434123</v>
+        <v>-0.6287669689629922</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.5570098894706561</v>
+        <v>1.014205926061535</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.78295024730869</v>
+        <v>-1.152583449577996</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5616996507566512</v>
+        <v>1.009858986194637</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-6.684861717612812</v>
+        <v>-4.983081911743938</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>5.594059405940598</v>
+        <v>6.963805978042465</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.43591610836004</v>
+        <v>3.842627205913438</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>3.030303030303031</v>
+        <v>4.403931224733135</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>5.396385893325558</v>
+        <v>6.739075203252064</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>2.791545189504376</v>
+        <v>4.167166707846526</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>5.507436570428702</v>
+        <v>6.820653325236165</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>2.157190989807411</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.651736212430663</v>
+        <v>1.589746488426577</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>2.575890251021598</v>
+        <v>1.514583966471392</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-4.649635036496392</v>
+        <v>-5.558854718981962</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>2.774532710280411</v>
+        <v>4.035103847704178</v>
       </c>
     </row>
     <row r="32">
@@ -2757,240 +2757,240 @@
         <v>24</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>17.19248621990143</v>
+        <v>17.2907066052228</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.357709421551611</v>
+        <v>4.544799769518924</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-5.413642960812837</v>
+        <v>-5.043227665706112</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.959930313588849</v>
+        <v>-1.468963197847607</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>6.037612547197213</v>
+        <v>6.588811995386394</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>2.057912066627949</v>
+        <v>2.579078934717835</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>9.619296716071027</v>
+        <v>10.11733025581854</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-7.325581395348834</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-3.117427546767402</v>
+        <v>-2.559661277906024</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.890343222803892</v>
+        <v>-3.355712773125362</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.616283580641969</v>
+        <v>-3.083477758521028</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.2716336825765211</v>
+        <v>0.8066069536741622</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-5.018195050946147</v>
+        <v>-4.47495183044316</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.239273927392794</v>
+        <v>-4.723185891876327</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-5.897417224973353</v>
+        <v>-5.405340273761382</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-13.77028077334111</v>
+        <v>-13.28125000000001</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-13.8751214771623</v>
+        <v>-13.41413410516161</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-17.82589676290463</v>
+        <v>-17.36633854468249</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-25.97238428626994</v>
+        <v>-25.48508543295685</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-14.01493045423591</v>
+        <v>-13.55252993433752</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-18.25744308231173</v>
+        <v>-17.79435912295953</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-17.98296836982968</v>
+        <v>-17.55072463768115</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-18.05880062305302</v>
+        <v>-17.71286363197068</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.002302</t>
+          <t>X ≈ 0.002301</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>22</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>5.450061977477127</v>
+        <v>5.548282362798496</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.5698306336727299</v>
+        <v>0.7569209816400431</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>12.76817522100547</v>
+        <v>13.1385905161122</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2.96431211065358</v>
+        <v>3.455279226394822</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.916932907348276</v>
+        <v>-1.365733459159095</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.729966721250896</v>
+        <v>-1.208799853161011</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-2.501915405141247</v>
+        <v>-2.00388186539373</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.780126849894295</v>
+        <v>-2.308802308802321</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-7.284094213434095</v>
+        <v>-6.726327944572716</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-17.14791898037971</v>
+        <v>-16.61328853070118</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-16.87385933821785</v>
+        <v>-16.34105351609691</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-17.15260874166575</v>
+        <v>-16.61763547056811</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-13.73031626306736</v>
+        <v>-13.18707304256437</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-4.860486048604791</v>
+        <v>-4.344398013088323</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-14.60953843709451</v>
+        <v>-14.11746148588254</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-9.469696969696969</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-9.603614106674442</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-9.70845481049556</v>
+        <v>-9.247467438494873</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-4.947108884116815</v>
+        <v>-4.48755066589468</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-4.760263074148732</v>
+        <v>-4.27296422083564</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-14.39371833302385</v>
+        <v>-13.93131781312546</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-9.924109748978402</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-5.104180491041809</v>
+        <v>-4.671936758893281</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-9.725467289719624</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.002477</t>
+          <t>X ≈ 0.002475</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.359152886568005</v>
+        <v>4.790706605222702</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>10.02437608821816</v>
+        <v>8.711466436185496</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-11.41364296081277</v>
+        <v>-9.209894332372684</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-4.126596980255542</v>
+        <v>-1.468963197847629</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-8.462387452802815</v>
+        <v>-5.911188004613635</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.275421266705436</v>
+        <v>-1.587587731948879</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-9.047369950595787</v>
+        <v>-6.549336410848269</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-9.325581395348834</v>
+        <v>-6.85425685425686</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-13.28409421343419</v>
+        <v>-10.89299461123945</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-18.05700988947062</v>
+        <v>-15.85571277312542</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-17.78295024730867</v>
+        <v>-19.75014442518776</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-18.06169965075669</v>
+        <v>-20.02672637965902</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.184861717612804</v>
+        <v>-4.47495183044316</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.5940594059405981</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.06408389163990336</v>
+        <v>-1.238673607094562</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-7.469696969696969</v>
+        <v>-9.010702921608292</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>4.396385893325586</v>
+        <v>3.385416666666664</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>8.291545189504319</v>
+        <v>7.419199228171635</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>0.5074365704287587</v>
+        <v>-0.6996718780157352</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-7.305717619603271</v>
+        <v>-8.818418766290179</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-3.848263787569273</v>
+        <v>-5.219196601004249</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-3.924109748978431</v>
+        <v>-5.294359122959534</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-3.649635036496321</v>
+        <v>-5.050724637681157</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-3.725467289719617</v>
+        <v>-5.21286363197062</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2051 +3180,2051 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.002488</t>
+          <t>X &gt; -0.002473</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.1779805952714071</v>
+        <v>0.1610769755931116</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2440977346499551</v>
+        <v>0.2249918698815065</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2735608306564217</v>
+        <v>0.2508899813527776</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.3178474641889295</v>
+        <v>0.2925843161270976</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1469782851936543</v>
+        <v>0.1217725604246525</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.08390277717244743</v>
+        <v>0.05969908975657034</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1293797528443434</v>
+        <v>0.1055516928031182</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.07578318489441926</v>
+        <v>0.05295964058849734</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1343034126786335</v>
+        <v>0.1092642769947219</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.1798556492649084</v>
+        <v>0.1846644741483772</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.233676831076103</v>
+        <v>0.2380631219820586</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1800585910015542</v>
+        <v>0.155373295952856</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.08430049272586615</v>
+        <v>0.06044639964533616</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.08885881158695952</v>
+        <v>0.06559152525760226</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>0.1915641464099735</v>
+        <v>0.1682527998317482</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>0.2091611926580725</v>
+        <v>0.1862265144707962</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>0.2119718540632221</v>
+        <v>0.1884290706832061</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.2141872603166348</v>
+        <v>0.191232709215555</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.2395794275715559</v>
+        <v>0.2164037721023746</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.2655833628319755</v>
+        <v>0.2415871456223257</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.2470310307749486</v>
+        <v>0.2238351356407406</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>0.2486635605241361</v>
+        <v>0.2254574993415659</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>0.1239048919899446</v>
+        <v>0.1021353228711135</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>0.06588889507918338</v>
+        <v>0.04633534208482359</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.002314</t>
+          <t>X &gt; -0.002299</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3331</v>
+        <v>3353</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1915417920258307</v>
+        <v>0.2192216131216327</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2308200022993674</v>
+        <v>0.2262812510003442</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3010690654480399</v>
+        <v>0.2916863829009486</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.3808657063116527</v>
+        <v>0.3679277992865053</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1515271485707643</v>
+        <v>0.1386340594433335</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.03989673866932719</v>
+        <v>0.01554684730557199</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.06135167425490096</v>
+        <v>0.03820068113988384</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.009345404770677135</v>
+        <v>-0.01246403739725821</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.06796795034350822</v>
+        <v>0.07295946635361616</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.2090588698716829</v>
+        <v>0.2144782970656465</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.2314038196769417</v>
+        <v>0.2364865908550229</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.149487905330659</v>
+        <v>0.1552944227183559</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.03117658280610414</v>
+        <v>0.03852419016722308</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.03733986089420682</v>
+        <v>0.04562172037469736</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>0.1454969466833873</v>
+        <v>0.1543464206665988</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>0.1289852704947023</v>
+        <v>0.1383598573265061</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>0.1627130353267532</v>
+        <v>0.171130952380949</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>0.2256177097321341</v>
+        <v>0.2345212486143211</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.189690767071383</v>
+        <v>0.1986803157503019</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.2744922754491981</v>
+        <v>0.2819684842311219</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>0.2297206155500788</v>
+        <v>0.2386897716616261</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>0.2619088528817812</v>
+        <v>0.2707178765436993</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>0.1042665241278939</v>
+        <v>0.1147494231417454</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>0.01635198377181979</v>
+        <v>0.02995374550229002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.00214</t>
+          <t>X &gt; -0.002126</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3313</v>
+        <v>3335</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1822413423401485</v>
+        <v>0.1660417258661653</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2835242585841442</v>
+        <v>0.2341124433369046</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.3319315966429741</v>
+        <v>0.2771896219243573</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.4760440761670495</v>
+        <v>0.429943905977531</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.247309334948639</v>
+        <v>0.2009169447006514</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.1040443592327449</v>
+        <v>0.04652102637702171</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.06974716652136692</v>
+        <v>0.0139094125407766</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.0189665169371338</v>
+        <v>-0.03539681247828952</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.07768463271971626</v>
+        <v>0.04979145841231514</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1936663954707711</v>
+        <v>0.1664829071771621</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.2447106065698392</v>
+        <v>0.2170001387310023</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1337890710478149</v>
+        <v>0.1069754428685883</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.08108292739320433</v>
+        <v>0.05533308687104466</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.05839885824273949</v>
+        <v>0.03391425760056421</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>0.1707144226285493</v>
+        <v>0.1468925811031099</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>0.1810106484903216</v>
+        <v>0.1577086847332794</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>0.1855425198315785</v>
+        <v>0.1612993716337527</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>0.2794933666661734</v>
+        <v>0.255675333130327</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>0.2422165583732436</v>
+        <v>0.218491794638858</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>0.2661847017714649</v>
+        <v>0.2411799159500063</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>0.2542693849276816</v>
+        <v>0.2306735807413105</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>0.2568857261347191</v>
+        <v>0.2333104405206399</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>0.1572448669436</v>
+        <v>0.1351266812636851</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>0.06928067285206652</v>
+        <v>0.05075455893393155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.001966</t>
+          <t>X &gt; -0.001952</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3281</v>
+        <v>3305</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.279831057927403</v>
+        <v>0.2757737529477282</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.3248000736815726</v>
+        <v>0.3167295940802646</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2664539795083414</v>
+        <v>0.2515978457259607</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.4188575651990334</v>
+        <v>0.3812173075675602</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3123927836324967</v>
+        <v>0.2861645826306827</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.04467573238522249</v>
+        <v>0.008610482515990725</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04783926711193942</v>
+        <v>0.01297544947686902</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.05992057614039226</v>
+        <v>0.02620083920896121</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2098378254008182</v>
+        <v>0.2013828988007376</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.2737943593912888</v>
+        <v>0.2661110693974251</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.3226963829281004</v>
+        <v>0.3146536459394298</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2134294108892192</v>
+        <v>0.2061647870578653</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.1407761924722379</v>
+        <v>0.1340147960144193</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.05926754936205469</v>
+        <v>0.05434050329719042</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0.2398674761411925</v>
+        <v>0.2348729630119593</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>0.214097496706195</v>
+        <v>0.2105467010901307</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>0.2199868665615696</v>
+        <v>0.2151268115942031</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>0.3767292479163018</v>
+        <v>0.3719828786297938</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>0.3370166069472589</v>
+        <v>0.3325537010375399</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>0.3594269770481731</v>
+        <v>0.3535365072063428</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.4440626436121846</v>
+        <v>0.4388042051223096</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>0.4170416369491008</v>
+        <v>0.4119708840962133</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>0.3138018922056602</v>
+        <v>0.3107393671585328</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>0.2257670900426376</v>
+        <v>0.227126282300695</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.001791</t>
+          <t>X &gt; -0.001778</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3244</v>
+        <v>3266</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.2642064853429176</v>
+        <v>0.2613903138857481</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3442290293946897</v>
+        <v>0.3058347771292205</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.3326028252736535</v>
+        <v>0.2856395693731244</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.4337954170467597</v>
+        <v>0.4240534485186132</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.2073457578687794</v>
+        <v>0.1789459783340135</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.02632666337739664</v>
+        <v>-0.02952845464475473</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.03851961995638931</v>
+        <v>-0.01567817143306627</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.08466714714886336</v>
+        <v>0.0317882401977343</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.2665503537850284</v>
+        <v>0.2684907082769925</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.3095851366270139</v>
+        <v>0.3129864138664473</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4172954529370045</v>
+        <v>0.4198769227841908</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.2793141741280962</v>
+        <v>0.2524072384007425</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.157486161920076</v>
+        <v>0.1621654516237783</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1083539033276324</v>
+        <v>0.1150314463410709</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>0.329520044399402</v>
+        <v>0.3363900061369023</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>0.2965288069871335</v>
+        <v>0.2745750258565494</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>0.2425397394794047</v>
+        <v>0.2193610601894278</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>0.4639059158817247</v>
+        <v>0.4407966201847699</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.4520178512168798</v>
+        <v>0.42893303383579</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>0.3801462547422716</v>
+        <v>0.3558931603153255</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>0.4721305439156041</v>
+        <v>0.4489486014022006</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>0.3962845825065031</v>
+        <v>0.3920953854044029</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>0.2887316815313881</v>
+        <v>0.2867409270571386</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>0.2930283946206984</v>
+        <v>0.2652951759493618</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.001617</t>
+          <t>X &gt; -0.001605</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3173</v>
+        <v>3194</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.3065213076206632</v>
+        <v>0.3633801190727226</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3960464110010449</v>
+        <v>0.3833219779040817</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4484260047044657</v>
+        <v>0.4362243890884727</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.4428605299357642</v>
+        <v>0.4042206958842343</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.232501227034156</v>
+        <v>0.2220623067188967</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.01181611178314768</v>
+        <v>-0.02573634133034375</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.08375639978019933</v>
+        <v>-0.08717509038732629</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.09519049043716876</v>
+        <v>0.09278364418550922</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2488624720649284</v>
+        <v>0.2696209491636168</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3731313978135233</v>
+        <v>0.3953262958687631</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4456929687717022</v>
+        <v>0.4673485589095279</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3109048104434322</v>
+        <v>0.3335356290745679</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.2745977418466481</v>
+        <v>0.2975390691928226</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1350842408981521</v>
+        <v>0.1613334589352178</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0.3447211398065875</v>
+        <v>0.3717957445548379</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>0.3604382929642398</v>
+        <v>0.3896718441630611</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>0.2453475044017068</v>
+        <v>0.2731080131208969</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>0.4741073550693784</v>
+        <v>0.5025325615050633</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>0.4885448827712722</v>
+        <v>0.5168541196917928</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>0.4108178134675882</v>
+        <v>0.4373660992507808</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>0.4856996654867842</v>
+        <v>0.5140428943559954</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.4098537040776833</v>
+        <v>0.4576225207617881</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>0.3062565829113382</v>
+        <v>0.3757229366537445</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>0.2808358933878452</v>
+        <v>0.3574765892775602</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.001443</t>
+          <t>X &gt; -0.001431</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3131</v>
+        <v>3150</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2810328484606899</v>
+        <v>0.3229460077682305</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.3763455926654942</v>
+        <v>0.3781331028521961</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.5444123299403216</v>
+        <v>0.5438935464151697</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.5167596631011335</v>
+        <v>0.4881075092230986</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.3081147722448918</v>
+        <v>0.2756806822550786</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.08185781784640511</v>
+        <v>-0.009304903666027542</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.0409962286795178</v>
+        <v>0.03418111362286425</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2260879210263624</v>
+        <v>0.2209168665264656</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3494935728254163</v>
+        <v>0.3668790064540985</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.5176003555182476</v>
+        <v>0.5054334552774407</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.5238607011317811</v>
+        <v>0.5430898460737055</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2636744339297152</v>
+        <v>0.2531597683485316</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.2100427409859194</v>
+        <v>0.2005200666358249</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.07160002397181842</v>
+        <v>0.06584364398871401</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>0.2609639095072609</v>
+        <v>0.2570528886318399</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>0.3326619719670418</v>
+        <v>0.3306523665487333</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>0.2815899749582087</v>
+        <v>0.2772443511772735</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>0.4191368960434474</v>
+        <v>0.4166643739258475</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>0.4308571192480954</v>
+        <v>0.4598632514083647</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>0.3176465680762703</v>
+        <v>0.344548893823962</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>0.3688498778202316</v>
+        <v>0.3984691141876411</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>0.3568608768198089</v>
+        <v>0.4057254794093339</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>0.2481938268497572</v>
+        <v>0.3192637258013349</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>0.2553695036371266</v>
+        <v>0.3347554156484378</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.001269</t>
+          <t>X &gt; -0.001258</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3075</v>
+        <v>3088</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.06106041970738119</v>
+        <v>0.08056167768651079</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1964330093048972</v>
+        <v>0.1567160336090367</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3611871912415836</v>
+        <v>0.2868850557110179</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4106198482234475</v>
+        <v>0.2741930018303336</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.1719167543169604</v>
+        <v>0.1274593383815699</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.06182903369569459</v>
+        <v>-0.1342866047346831</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.007646230634023254</v>
+        <v>-0.009387957239994194</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3306180219383137</v>
+        <v>0.2655885065678802</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3907762528871217</v>
+        <v>0.379698481466562</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.4463914710735963</v>
+        <v>0.4079880650434973</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.480173537526035</v>
+        <v>0.4409229724259163</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1554802519985756</v>
+        <v>0.08617684614740284</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.05638341857395801</v>
+        <v>0.02246669166075321</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.0806081256844422</v>
+        <v>-0.1099945856572049</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0.09165913237041678</v>
+        <v>0.06635276251033417</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>0.21871588327285</v>
+        <v>0.2270231765828825</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>0.1366456335852959</v>
+        <v>0.1422825794291853</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>0.2135978039896003</v>
+        <v>0.2547950049439791</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.3190025223455351</v>
+        <v>0.3591706696724941</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.2327939176082978</v>
+        <v>0.2695501858443592</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.2622693723786895</v>
+        <v>0.3035576317143978</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>0.2514429168213326</v>
+        <v>0.3124369935453188</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.1358005941928582</v>
+        <v>0.219319605331691</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>0.1119310842641141</v>
+        <v>0.2059619293419885</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.001095</t>
+          <t>X &gt; -0.001084</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2981</v>
+        <v>2997</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.195043480297187</v>
+        <v>0.2268850619923555</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.1451635423390059</v>
+        <v>0.2466706872649027</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.16045583758509</v>
+        <v>0.2208042173892721</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1338370765057562</v>
+        <v>0.1597869405338912</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2353423776775827</v>
+        <v>-0.148982757187504</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4156549895768578</v>
+        <v>-0.3905878426540426</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2193232060214712</v>
+        <v>-0.1893231262251973</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.05584813036927727</v>
+        <v>0.07035290994107868</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.183329775874256</v>
+        <v>0.165070262003141</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.332027543684454</v>
+        <v>0.3321539378233211</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1575378837511465</v>
+        <v>0.1584934485663965</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.03194583419313801</v>
+        <v>0.03392499953669414</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1684682749898627</v>
+        <v>-0.1642248800885469</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.2693944093204408</v>
+        <v>-0.2599889070630468</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.07077957292553805</v>
+        <v>-0.05770221654243102</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>0.04135460431508164</v>
+        <v>0.02423884211879113</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.1061266694885177</v>
+        <v>-0.1598563027075031</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.043555913364969</v>
+        <v>0.02659183556433931</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1118616458561306</v>
+        <v>0.09424328965016571</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.05041920132228483</v>
+        <v>0.02863221671548644</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.06451715842197103</v>
+        <v>0.04747006566242362</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.08930856702293966</v>
+        <v>0.09215860517206664</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.07231199053861559</v>
+        <v>-0.04460944977810755</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.1481442437618909</v>
+        <v>-0.08690433934466313</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.0009204</t>
+          <t>X &gt; -0.0009103</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2874</v>
+        <v>2886</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.442197869266991</v>
+        <v>0.4760003846869125</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.195369511548094</v>
+        <v>0.2990828556405205</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.3342794768603525</v>
+        <v>0.4241748868982995</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.07146396157273927</v>
+        <v>0.1077299147199398</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.4028306660991845</v>
+        <v>-0.3747961453517945</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5967509065946004</v>
+        <v>-0.6317983792985231</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.433796543393548</v>
+        <v>-0.4265354449979455</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.2074657043200858</v>
+        <v>-0.2485307418042879</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1310132016732837</v>
+        <v>0.1208607411809623</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.4178601278604077</v>
+        <v>0.4286381524811134</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1574103629548205</v>
+        <v>0.1834533671544278</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.03750256915312633</v>
+        <v>0.06471599439201725</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2327451319084375</v>
+        <v>-0.2018532226880083</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.05154975754430069</v>
+        <v>0.01898722046259138</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.0640838916399602</v>
+        <v>0.01348528755128342</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.00460492384771527</v>
+        <v>0.07706487383050842</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.3610845722755514</v>
+        <v>-0.2829206993893294</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.06299078546955172</v>
+        <v>0.01947585334462332</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1040986010267559</v>
+        <v>0.1852583652679272</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.001369793516317941</v>
+        <v>0.03971272159909489</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.06822890554134631</v>
+        <v>0.1156943647278368</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.06197236654004712</v>
+        <v>0.1303869527560693</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.1506788778324619</v>
+        <v>-0.05563169229378673</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.1917164198518364</v>
+        <v>-0.05867097777796459</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.0007462</t>
+          <t>X &gt; -0.0007367</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2741</v>
+        <v>2752</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3170323346435637</v>
+        <v>0.2923949795594396</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.1471512425952639</v>
+        <v>0.1912059441450111</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1984166105639105</v>
+        <v>0.2389720448583432</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.07864928683015648</v>
+        <v>-0.06399455337099624</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4870877797188768</v>
+        <v>-0.4480910436874126</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.6633616953287245</v>
+        <v>-0.6167724883405583</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.4182380944388342</v>
+        <v>-0.326470998402506</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.02180232558139039</v>
+        <v>0.01983865949132735</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1859166916912827</v>
+        <v>0.256305919392517</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.5248082923475579</v>
+        <v>0.5456379263439501</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2897770254185801</v>
+        <v>0.3475400900076124</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1201185310614861</v>
+        <v>0.2156759358257574</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.03608034256734527</v>
+        <v>0.06268841566614469</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.09187599982706729</v>
+        <v>0.1977651098133251</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>0.1470555331871282</v>
+        <v>0.2613867575075446</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.1442870069964073</v>
+        <v>0.2646593972322435</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.1500621941061411</v>
+        <v>-0.07145176392413077</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.09475218658892004</v>
+        <v>0.179653663753065</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.2230763808552396</v>
+        <v>0.3068569576751443</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.04240616810800901</v>
+        <v>0.03499197391301578</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.02039728503193317</v>
+        <v>0.1059697631820811</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>0.09048346517701589</v>
+        <v>0.1976524965030677</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.1458043177805521</v>
+        <v>-0.009254726069585217</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.2946026417809193</v>
+        <v>-0.07720471724193345</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005719</t>
+          <t>X &gt; -0.0005631</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.05565094104274237</v>
+        <v>0.1424004247210533</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.03215818938553383</v>
+        <v>0.2068116650451159</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.03382785630785179</v>
+        <v>0.2321796267687404</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3289316106057072</v>
+        <v>-0.1274840150185312</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.9370956240090109</v>
+        <v>-0.6745704716423049</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.061413484604238</v>
+        <v>-0.8667447011756479</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5882259817241646</v>
+        <v>-0.3041851307861734</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.143798600487024</v>
+        <v>0.1278998563715348</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.05339118944636567</v>
+        <v>0.2946185255591303</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.2536168135266479</v>
+        <v>0.5071007774305585</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2941225436605563</v>
+        <v>0.5078074755104538</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.09322444422189591</v>
+        <v>0.2312255210391569</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1378319375059078</v>
+        <v>0.280026188693121</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.2903210881835889</v>
+        <v>0.4196897222949261</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.200816770611695</v>
+        <v>0.3814272854160166</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.2341222041144135</v>
+        <v>0.3837070162798781</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2663821378635305</v>
+        <v>-0.1242920711974165</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.03606791501980666</v>
+        <v>0.115391924364431</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.1640889309437199</v>
+        <v>0.2363301947915275</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.09416414575471777</v>
+        <v>-0.07036277873185526</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.0902622262890489</v>
+        <v>-0.03152643375414499</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.00998016271766744</v>
+        <v>0.1109586461714684</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.281953537667313</v>
+        <v>-0.1671772132617946</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.4748818096259484</v>
+        <v>-0.2673807659270082</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003977</t>
+          <t>X &gt; -0.0003895</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2305</v>
+        <v>2312</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.1373869058195183</v>
+        <v>-0.05425463508734651</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.03963775261223645</v>
+        <v>0.001302784161417492</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1226892191180227</v>
+        <v>0.1677973127607899</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.3740018245461769</v>
+        <v>-0.3815385639113487</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.055813058339119</v>
+        <v>-0.9154946368272121</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.47438320442167</v>
+        <v>-1.447622185006558</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.8622488433293256</v>
+        <v>-0.7353829224761483</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.6646817413695985</v>
+        <v>-0.5235075002516894</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4934367739877601</v>
+        <v>-0.395578590567581</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.358047951754358</v>
+        <v>-0.2441709987929528</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3002512853709831</v>
+        <v>-0.1442012727329711</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.6655058791303929</v>
+        <v>-0.5930485157486274</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.5343426864709429</v>
+        <v>-0.5020836133888906</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2973296031463804</v>
+        <v>-0.2765881313250205</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.3238241513802222</v>
+        <v>-0.2872159020824512</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.1366523616415307</v>
+        <v>-0.04518568022902514</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.374844609274092</v>
+        <v>-0.2961271021992289</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.1505874502875599</v>
+        <v>-0.01537080346474085</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.169059526709205</v>
+        <v>-0.1637777620612866</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.6072360577811438</v>
+        <v>-0.6577970046321511</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.5857909025367647</v>
+        <v>-0.6385630516881875</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.748404759824389</v>
+        <v>-0.7315530152096059</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.7342337349779129</v>
+        <v>-0.6354630726141366</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.679914144383396</v>
+        <v>-0.4262431014054542</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.0002235</t>
+          <t>X &gt; -0.0002159</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2037</v>
+        <v>2046</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.4687419276639275</v>
+        <v>0.6402526493213045</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.03611777119277804</v>
+        <v>0.1511551521388341</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.6039695636490592</v>
+        <v>0.6474338128931763</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.5982212464003283</v>
+        <v>-0.4799878411679614</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.9829353980082658</v>
+        <v>-0.7555459812672964</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.774442793124187</v>
+        <v>-1.474098756592177</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.9808337470732482</v>
+        <v>-0.6154842707704162</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8187320802803342</v>
+        <v>-0.5312996558132781</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2880081077589836</v>
+        <v>-0.06290382005913386</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3270685978854928</v>
+        <v>-0.08074519854695694</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.1997799929055688</v>
+        <v>0.04557541917021979</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6742241125962209</v>
+        <v>-0.4741971967796772</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.476446844814383</v>
+        <v>-0.3731360068374485</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3751035896541097</v>
+        <v>-0.3295412744962363</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.1228498074088193</v>
+        <v>-0.1559485462674033</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.2559277240805855</v>
+        <v>0.239540505850286</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.1512878541098672</v>
+        <v>0.1645204172755257</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.5171459742027622</v>
+        <v>0.5478541989319652</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.4191146862285038</v>
+        <v>0.4014170217078856</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.1444542017025725</v>
+        <v>0.1084105020024992</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.09282605042775316</v>
+        <v>0.008963477082623683</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.130295315988711</v>
+        <v>-0.08602578962619845</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.1503714135213841</v>
+        <v>-0.15534929164631</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.07892826173729617</v>
+        <v>0.1023856348915544</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -4.931e-05</t>
+          <t>X &gt; -4.227e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1710</v>
+        <v>1705</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.05746389413937436</v>
+        <v>0.07464281681355089</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.5963038692316118</v>
+        <v>0.4705096100478414</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.02200060354366</v>
+        <v>0.9077641662659488</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.04040012527589454</v>
+        <v>-0.3264116614804351</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.3761905978231681</v>
+        <v>-0.3685975728749824</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.64525236746254</v>
+        <v>-1.436868167577011</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.194137568534025</v>
+        <v>-0.7733737504048293</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.8316967127629269</v>
+        <v>-0.5532066792276851</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.4407628214714023</v>
+        <v>-0.4252777695435768</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6312673152132007</v>
+        <v>-0.5212125786485657</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.3572076730512777</v>
+        <v>-0.1906345068680366</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.004695224024899858</v>
+        <v>0.1745571675988202</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.1628377582171296</v>
+        <v>0.3432123080243699</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2094440213252113</v>
+        <v>0.3283504752960411</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.4606974494679079</v>
+        <v>0.4629988938777316</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.740338036137338</v>
+        <v>0.7674640369439203</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.9918324782642642</v>
+        <v>0.9905568535825466</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.389676030625878</v>
+        <v>1.243473531697937</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>1.056822894215962</v>
+        <v>0.9669947886508368</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.4603642517417654</v>
+        <v>0.3974969739087655</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.444133873249406</v>
+        <v>0.3331062873642168</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.5437265083315381</v>
+        <v>0.5272577487452139</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.4088444956673953</v>
+        <v>0.278505530353236</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.33301224244412</v>
+        <v>0.4445166221838335</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0001249</t>
+          <t>X &gt; 0.0001313</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6749423602522384</v>
+        <v>0.5890259329538239</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8313936320778694</v>
+        <v>0.6932591532723649</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.63898861813459</v>
+        <v>1.46937737631076</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1541047741304524</v>
+        <v>0.03663904304875842</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.111510259820335</v>
+        <v>-0.1688910858460986</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.117526529863305</v>
+        <v>-1.062377647915234</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.9771945119992651</v>
+        <v>-0.66698346967177</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.8343533251733959</v>
+        <v>-0.621763857057978</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.6525152660657056</v>
+        <v>-0.4938349473738697</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5833256789442984</v>
+        <v>-0.2394662745259879</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3794414753788757</v>
+        <v>0.03276874007834607</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.307313685844413</v>
+        <v>-0.1037571919839877</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.3778441737531608</v>
+        <v>-0.308285163776489</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.004171765491157942</v>
+        <v>-0.06632314677822393</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.7932597485568138</v>
+        <v>0.5820546842218661</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>1.289796701189111</v>
+        <v>1.045358746226285</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>1.480129735690092</v>
+        <v>1.193972066386166</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>2.1929536402086</v>
+        <v>1.805164140452433</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>1.888690974938925</v>
+        <v>1.570927372920494</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>1.413605370523676</v>
+        <v>1.125361978614947</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>1.435234096774849</v>
+        <v>1.162659939080143</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>1.4299099971429</v>
+        <v>1.341226145630657</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.210731677184896</v>
+        <v>0.9938763012859795</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>1.487508732847374</v>
+        <v>1.367474634414158</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0002991</t>
+          <t>X &gt; 0.000305</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7884544197877972</v>
+        <v>0.825481838471255</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.5388564970768215</v>
+        <v>0.6643926448369299</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.571024841572239</v>
+        <v>1.699774878823213</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.07889680989776338</v>
+        <v>0.0895609751803903</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8405816606392378</v>
+        <v>-0.6949030173362516</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.505404230930274</v>
+        <v>-1.386145832033669</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.340385282793378</v>
+        <v>-1.163416139431789</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.022344598074554</v>
+        <v>-0.8746130883535486</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.6401419136044808</v>
+        <v>-0.407413610391238</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.6464477088914009</v>
+        <v>-0.3552886849150738</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.03167256417411579</v>
+        <v>0.2562168979674624</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2006512862109417</v>
+        <v>0.4037231538439201</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.4403512295762866</v>
+        <v>0.4762780253668524</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>1.071061109518112</v>
+        <v>1.076220384629245</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.9759843095535601</v>
+        <v>0.8181542130919368</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>1.622453200951497</v>
+        <v>1.379458231911599</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>1.711501179405829</v>
+        <v>1.49662209960384</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>2.342827240786427</v>
+        <v>2.094928483340233</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>2.355169675646842</v>
+        <v>1.936382543752885</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>1.772126691773977</v>
+        <v>1.522006765624717</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>1.913926118333173</v>
+        <v>1.857748316656171</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>1.838080156924072</v>
+        <v>2.005299871072864</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>1.599295673512202</v>
+        <v>1.448137705891085</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>1.780093018235895</v>
+        <v>1.764790794445545</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.0004733</t>
+          <t>X &gt; 0.0004786</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.7816294734566895</v>
+        <v>1.143264106080956</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7590274930049006</v>
+        <v>1.206317105598508</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.9859408060966928</v>
+        <v>1.496422179814033</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4554211217747621</v>
+        <v>0.08012708708202609</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.207444684852732</v>
+        <v>-0.8133507234601538</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.540769861918726</v>
+        <v>-1.274336787904922</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-1.168077546849666</v>
+        <v>-0.93656607099242</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7178810831740208</v>
+        <v>-0.6235668439582014</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.260160810728614</v>
+        <v>-0.1866780990526706</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5127851236017307</v>
+        <v>-0.2618233120886941</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.07344933645820362</v>
+        <v>0.3193715377370694</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.1068747509082328</v>
+        <v>0.2487628067467185</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.02429541037886196</v>
+        <v>-0.04223641678026979</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.531624442360993</v>
+        <v>0.5334224157104117</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.7692494416933684</v>
+        <v>0.6751609277491397</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>1.218519922899489</v>
+        <v>0.9275051113473936</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>1.565488189776495</v>
+        <v>1.400880584192436</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>1.733551459096851</v>
+        <v>1.433647112588659</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>1.176892637374308</v>
+        <v>0.6777385903037256</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>1.468340957802582</v>
+        <v>1.160898710441984</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.239602321217312</v>
+        <v>1.173142943509205</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.372961380728711</v>
+        <v>1.367989754415255</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>1.229026051369758</v>
+        <v>0.8448493595525903</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.571603839987489</v>
+        <v>1.264291092847657</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.0006475</t>
+          <t>X &gt; 0.0006522</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>770</v>
+        <v>780</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4236690156002894</v>
+        <v>0.8411089770990614</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.9921180237020906</v>
+        <v>1.357590959692523</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4573247811227148</v>
+        <v>0.8652856760982743</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-1.545951818965193</v>
+        <v>-1.124829356255056</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-1.623677775383435</v>
+        <v>-1.146257890255285</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.598001911866703</v>
+        <v>-2.132907511703195</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-2.208660273176406</v>
+        <v>-1.657341493440356</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-2.744936234058514</v>
+        <v>-2.343456345997645</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.058287761821227</v>
+        <v>-1.707268224115325</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-2.573138921728685</v>
+        <v>-2.122125310185993</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.170047021502242</v>
+        <v>-1.849890295581659</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-1.674602876563149</v>
+        <v>-1.491148234805181</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.636474620838619</v>
+        <v>-1.589521927859501</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.083359948898106</v>
+        <v>-1.075367170995278</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.5033603774280735</v>
+        <v>-0.6139383254343471</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.2200203849621687</v>
+        <v>-0.4338287157633545</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.2409454788177854</v>
+        <v>-0.1565147183396931</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>0.8622326084408201</v>
+        <v>0.2945172943294878</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.1178261808183123</v>
+        <v>-0.4342790966994841</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.6044189183045745</v>
+        <v>-1.037806521392227</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.8872248265303426</v>
+        <v>-1.276029295767977</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.833200658069309</v>
+        <v>-1.149005329268135</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.8184662053275176</v>
+        <v>-1.214830484885596</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.3748179390702688</v>
+        <v>-0.6615815806885621</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.0008218</t>
+          <t>X &gt; 0.0008258</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.039152886568026</v>
+        <v>2.432216039185001</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.4243760882182244</v>
+        <v>1.085680272663524</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.2663570391872199</v>
+        <v>0.93161510158955</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.406596980255514</v>
+        <v>-0.7614160280362796</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-1.422387452802788</v>
+        <v>-0.7225087593305801</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.355421266705406</v>
+        <v>-1.508971379747592</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.047369950595751</v>
+        <v>-0.1027955303450909</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-2.605581395348835</v>
+        <v>-1.822810313376358</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.244094213434131</v>
+        <v>-1.537648699289726</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.697009889470621</v>
+        <v>-1.862002081301526</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.942950247308694</v>
+        <v>-1.11806895348964</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.581699650756697</v>
+        <v>-0.9229527947533924</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-1.26486171761281</v>
+        <v>-0.7799832769840407</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.5259405940594064</v>
+        <v>-0.08482111200205367</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>0.1923263647702953</v>
+        <v>0.4908861413330143</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.07964881560386772</v>
+        <v>0.1087939337375801</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.328861777569934</v>
+        <v>1.262775157232703</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.127293981774905</v>
+        <v>1.854894766229478</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>0.7328794045671927</v>
+        <v>0.5884458927517784</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.3685195519704223</v>
+        <v>-0.5245799037309382</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-1.072096315749661</v>
+        <v>-0.9997873183038237</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.8258810855323517</v>
+        <v>-0.6654631905770643</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.8734675646767087</v>
+        <v>-0.8046928916494025</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>0.1779143527924489</v>
+        <v>0.3978941846695534</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.000996</t>
+          <t>X &gt; 0.0009994</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.870963910190085</v>
+        <v>2.670391023368687</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1582343559347592</v>
+        <v>0.8465749174478603</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.09868233089151346</v>
+        <v>0.5780741094418786</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.976990681042906</v>
+        <v>-2.183953335914673</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.706481940991765</v>
+        <v>-3.051227452345358</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-4.700618117099111</v>
+        <v>-3.683248481455756</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.110362076580003</v>
+        <v>-2.308705247140153</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-5.160227064640175</v>
+        <v>-4.191534960765736</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-3.937637520520738</v>
+        <v>-3.274651415973153</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-5.104253983958813</v>
+        <v>-4.465180228746718</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-4.23964316069452</v>
+        <v>-3.601229237811033</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-4.321542170441731</v>
+        <v>-3.87781119228233</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-4.6573026624947</v>
+        <v>-4.20374867462462</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-3.106727995634202</v>
+        <v>-2.676834807063649</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-2.780619324710827</v>
+        <v>-2.175557236285975</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-3.367334764972561</v>
+        <v>-2.99492382890616</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-2.009925743755304</v>
+        <v>-1.915372287968438</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.012802636582578</v>
+        <v>-1.456540416798688</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-2.180310465144416</v>
+        <v>-2.511266080914382</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-2.586350030670474</v>
+        <v>-2.976834607874331</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-3.721781574130567</v>
+        <v>-3.830307712115356</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-3.402370618543621</v>
+        <v>-3.397407499367745</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-3.720781281555638</v>
+        <v>-3.838905248570931</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-2.808471242288789</v>
+        <v>-2.692903552130296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.00117</t>
+          <t>X &gt; 0.001173</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>410</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.5054943499826692</v>
+        <v>0.9152045971906091</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8048922044647071</v>
+        <v>-0.05359380477831621</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.7794966193493522</v>
+        <v>0.1374952258602207</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.224157955865266</v>
+        <v>-1.177798539213065</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.828241111339366</v>
+        <v>-0.9714289684690343</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-2.860787120363938</v>
+        <v>-1.778350784157688</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.4620040969372283</v>
+        <v>0.5590973240915176</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.228020419739074</v>
+        <v>-0.2277508301604669</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.430435676848759</v>
+        <v>-0.5817496313197381</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.935058669958423</v>
+        <v>-1.859728837382455</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-3.392706344869673</v>
+        <v>-2.310385389043184</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-3.915358187342058</v>
+        <v>-3.068895054357846</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.819008059076218</v>
+        <v>-3.219931750121873</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.576672301376483</v>
+        <v>-2.022382679024858</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.771400964810695</v>
+        <v>-1.258753928379797</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.908721359940877</v>
+        <v>-1.420341475825197</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8231263017963997</v>
+        <v>-0.3194026104417631</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>0.5354476285287646</v>
+        <v>0.7525325615050633</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-1.687685380790818</v>
+        <v>-1.303536612315348</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-2.720351765944741</v>
+        <v>-2.401953875249013</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-4.238507690008319</v>
+        <v>-3.803338995826259</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-3.338743895319872</v>
+        <v>-2.907627731373772</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-4.039878938935367</v>
+        <v>-3.499629747170204</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-3.384003875085483</v>
+        <v>-2.794164444978755</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.001344</t>
+          <t>X &gt; 0.001347</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.5129990404141864</v>
+        <v>1.412328226844359</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.7448546810125549</v>
+        <v>0.5658207905398811</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.87518142235124</v>
+        <v>-0.3885730110513919</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.58813544179398</v>
+        <v>-0.9809752098596149</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-2.61623360664894</v>
+        <v>-1.25653334995895</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.967728959013094</v>
+        <v>-2.300800945162067</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.355062258288065</v>
+        <v>0.2074203459085169</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.940966010733447</v>
+        <v>-0.3978003978004025</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-2.822555751895671</v>
+        <v>-1.471072689317502</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-3.595471427932161</v>
+        <v>-2.26712418453684</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-3.629104093462544</v>
+        <v>-2.295189470232799</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.523238112295161</v>
+        <v>-3.472672325604997</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-3.184861717612804</v>
+        <v>-2.485462340953667</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.482863670982482</v>
+        <v>-1.832795501485876</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-2.217930045486113</v>
+        <v>-1.614048982470031</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-2.238927738927742</v>
+        <v>-1.653345564250976</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.2189987220590623</v>
+        <v>0.3448761261261239</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>1.830006727965916</v>
+        <v>2.013793822766317</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.338717275725145</v>
+        <v>-0.9004750908672321</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-3.305717619603264</v>
+        <v>-2.927180095595311</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-4.771340710646221</v>
+        <v>-4.234348116155765</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-3.616417441286096</v>
+        <v>-3.097389425989839</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-4.265019651880962</v>
+        <v>-3.594291000396453</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-4.033159597411931</v>
+        <v>-3.281969323027525</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.001519</t>
+          <t>X &gt; 0.00152</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2839566540680067</v>
+        <v>0.436612026214668</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.08798032850089754</v>
+        <v>1.228767474247817</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.056752501448813</v>
+        <v>-0.7179681501351141</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-3.12306341135092</v>
+        <v>-1.656391110189006</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-3.105496993438827</v>
+        <v>-1.585928489042672</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-3.97860147871954</v>
+        <v>-2.467057166781615</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.570338148475621</v>
+        <v>-0.1479523278032602</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.908620264606789</v>
+        <v>-1.490935054948899</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.92720375407017</v>
+        <v>-2.401068429001818</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.70011943010666</v>
+        <v>-3.197119924221155</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-4.779416678404104</v>
+        <v>-3.27090567086249</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.411522972311467</v>
+        <v>-4.239529147825145</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.061186805952033</v>
+        <v>-3.278296697801864</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.515481230101798</v>
+        <v>-1.796426953006602</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-1.760196965844905</v>
+        <v>-1.094498289908962</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-2.579237605739365</v>
+        <v>-1.917277316071996</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.2396565095012946</v>
+        <v>0.4009876009227185</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>2.129001019893067</v>
+        <v>2.690248824480847</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.1286058323981507</v>
+        <v>0.4825657229068909</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-3.121972036564401</v>
+        <v>-2.568418766290179</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-4.017875094989797</v>
+        <v>-3.288302292061154</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-3.387007275480165</v>
+        <v>-3.01503275826731</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-3.819246343916845</v>
+        <v>-3.119830328738061</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-3.89507859714012</v>
+        <v>-3.085824004930991</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.001693</t>
+          <t>X &gt; 0.001694</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.25276990784463</v>
+        <v>1.499390078612095</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3586026351860383</v>
+        <v>0.4131471084544387</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.9455578544297936</v>
+        <v>-0.001210858983355934</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-4.637235278127861</v>
+        <v>-3.534789528379811</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.69643000599428</v>
+        <v>-2.549843466798478</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-4.360527649684137</v>
+        <v>-3.233245995254173</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.302689099531925</v>
+        <v>-0.2468154024448808</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-2.857496288965855</v>
+        <v>-1.812240047534168</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.667072936838387</v>
+        <v>-2.524647272303845</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.014456697981259</v>
+        <v>-2.900530700296294</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.165928970712955</v>
+        <v>-3.048463752918849</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-4.870210289054569</v>
+        <v>-3.745213774617035</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.440180866548978</v>
+        <v>-2.339097488706464</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-1.533600168527492</v>
+        <v>-0.4864912140051132</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.9151477214271964</v>
+        <v>0.09185860579049887</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.022888459058663</v>
+        <v>-1.027509644297396</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.396385893325558</v>
+        <v>1.389618347338931</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.270268593759695</v>
+        <v>4.197910712765562</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.08190465553508375</v>
+        <v>1.051028402096215</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-3.561036768539438</v>
+        <v>-2.936065825113708</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-4.103582936505468</v>
+        <v>-3.503510326494442</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-3.328365068127333</v>
+        <v>-3.158504781222838</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-3.904954185432516</v>
+        <v>-3.33503836317135</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-3.980786438655791</v>
+        <v>-3.26138683872167</v>
       </c>
     </row>
     <row r="31">
@@ -5234,79 +5234,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.025819553234697</v>
+        <v>2.810964432110396</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.4688205326626615</v>
+        <v>0.9075990328706212</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.1419125947427844</v>
+        <v>0.7578773066696414</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.904374758033285</v>
+        <v>-3.149442019210404</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-2.017943008358344</v>
+        <v>-1.215055407928517</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-3.497643488927629</v>
+        <v>-2.715580365466352</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.380703283929094</v>
+        <v>0.3567409372180563</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.21447028423772</v>
+        <v>-0.5006656940358667</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-2.284094213434123</v>
+        <v>-1.477709160042359</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-2.501454333915063</v>
+        <v>-1.7212744674164</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-2.22739469175314</v>
+        <v>-1.449039452812066</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.8394774285344724</v>
+        <v>-0.06816284374745152</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2959728287239187</v>
+        <v>0.474403602337695</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>3.927392739273927</v>
+        <v>4.646059043667016</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>2.713693886137818</v>
+        <v>3.411418473936642</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>2.196969696969703</v>
+        <v>2.867750117065704</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>4.285274782214444</v>
+        <v>4.973814456721918</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>5.291545189504376</v>
+        <v>5.945902727250925</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>3.28521434820648</v>
+        <v>3.950420203015469</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.4168287307143785</v>
+        <v>0.2976033331573404</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.9593748986804087</v>
+        <v>-0.8223273560687119</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.4796653045339596</v>
+        <v>-0.3450036901786788</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-1.871857258718578</v>
+        <v>-1.75882776843622</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-1.392133956386289</v>
+        <v>-0.815994387035083</v>
       </c>
     </row>
     <row r="32">
@@ -5319,76 +5319,76 @@
         <v>140</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>4.216295743710894</v>
+        <v>4.314516129032263</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2.452947516789649</v>
+        <v>2.640037864756962</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.3006427534729426</v>
+        <v>0.6710580485796669</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-1.840882694541229</v>
+        <v>-1.349915578799987</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.6804696900543519</v>
+        <v>1.231669138243532</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-1.989706980991123</v>
+        <v>-1.468540112901238</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.8097729065471029</v>
+        <v>1.30780644629462</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.8970099667774036</v>
+        <v>-0.4256854256854297</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2.284094213434123</v>
+        <v>-1.726327944572745</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.057009889470613</v>
+        <v>-2.522379439792083</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-2.068664533022982</v>
+        <v>-1.535858710902041</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>1.529423996672897</v>
+        <v>2.072667217175884</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.451202263083452</v>
+        <v>3.96729029859992</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>2.793058965502894</v>
+        <v>3.285135916714864</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>1.958874458874462</v>
+        <v>2.417868506963103</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>3.967814464754127</v>
+        <v>4.456845238095234</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>6.005830903790084</v>
+        <v>6.466818275790772</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.650293713285848</v>
+        <v>3.109851931507983</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.7342890481746949</v>
+        <v>-0.2469901948616027</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-1.99112093042644</v>
+        <v>-1.528720410528052</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-1.352681177549826</v>
+        <v>-0.8895972181976219</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-1.078206465067773</v>
+        <v>-0.6459627329192443</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-2.582610146862486</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="33">
@@ -5401,240 +5401,240 @@
         <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.531566679671478</v>
+        <v>1.629787064992847</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>2.058858846838902</v>
+        <v>2.245949194806215</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.482908763325163</v>
+        <v>1.853324058431888</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.816252152669307</v>
+        <v>-1.325285036928065</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4279046941821036</v>
+        <v>0.1232947540070768</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2.827145404636447</v>
+        <v>-2.305978536546561</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.012887191975075</v>
+        <v>-0.5148536522275577</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.4330392943063401</v>
+        <v>0.9043638353983141</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2.111680420330686</v>
+        <v>-1.553914151469307</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-2.884596096367176</v>
+        <v>-2.349965646688645</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.748467488688014</v>
+        <v>-1.215661666567073</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.165147926618758</v>
+        <v>-0.6301746555211167</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>2.884103799628569</v>
+        <v>3.427347020131556</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>5.249231819733708</v>
+        <v>5.765319855250176</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.59108852215315</v>
+        <v>5.083165473365121</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.323406478578896</v>
+        <v>4.782400526667537</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>7.637765203670384</v>
+        <v>8.12679597701149</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>10.11913139640093</v>
+        <v>10.58011876840162</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>6.886746915256289</v>
+        <v>7.346305133478424</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>4.487385828672593</v>
+        <v>4.974684681985686</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>0.4965637986375953</v>
+        <v>0.9589643185359833</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>2.144855768262978</v>
+        <v>2.607939727615182</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>2.419330480745032</v>
+        <v>2.85157421289356</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>0.6193602964872724</v>
+        <v>0.9652972875696122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.00239</t>
+          <t>X &gt; 0.002388</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>94</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.6144720355041997</v>
+        <v>0.7126924208255687</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.407354811622469</v>
+        <v>2.594445159589782</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.158323811876606</v>
+        <v>-0.7879085167698818</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-2.935107618553388</v>
+        <v>-2.444140502812147</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.07940872939853705</v>
+        <v>0.4717907187906434</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-3.083931905003283</v>
+        <v>-2.562765036913397</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.6643912271915084</v>
+        <v>-0.1663576874439912</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.185056902523506</v>
+        <v>1.65638144361548</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.9011154900298806</v>
+        <v>-0.3433492211685021</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.4536284084017197</v>
+        <v>0.9882588580802505</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>1.791517837797684</v>
+        <v>2.324323659918626</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.576598221583737</v>
+        <v>3.111571492681378</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>6.772585090897827</v>
+        <v>7.315828311400814</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.615336001685279</v>
+        <v>8.131424037201747</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>9.084852278572818</v>
+        <v>9.576929229784788</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.551579626047712</v>
+        <v>8.010573674136353</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>11.67298163800641</v>
+        <v>12.16201241134751</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>14.75963029588735</v>
+        <v>15.22061766788804</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>9.65637274064148</v>
+        <v>10.11593095886361</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>6.651729188907368</v>
+        <v>7.13902804222046</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>3.981523446473254</v>
+        <v>4.443923966371642</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>4.969507272298195</v>
+        <v>5.432591231650399</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>4.180152197546207</v>
+        <v>4.612395929694735</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>3.040490157088882</v>
+        <v>3.386427148171222</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.002564</t>
+          <t>X &gt; 0.002562</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.01765870763485822</v>
+        <v>-0.6854838709677367</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.3524355059846727</v>
+        <v>0.4971807218998165</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.557371531940852</v>
+        <v>2.09962947715109</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-2.503408574458405</v>
+        <v>-2.77848700737141</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>2.957902402269674</v>
+        <v>2.66024056681497</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-2.652232860908299</v>
+        <v>-2.897111541472661</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>2.372919904476703</v>
+        <v>2.022092160580335</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>4.993259184361307</v>
+        <v>4.57431457431457</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>3.585471003957181</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>7.160381414877207</v>
+        <v>6.763334845922202</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.88371641935796</v>
+        <v>9.892712717669383</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>10.05424237822882</v>
+        <v>11.04470219176952</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>10.38035567369153</v>
+        <v>11.35838150289018</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>10.15927679724494</v>
+        <v>11.11014744145707</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>12.39968422430207</v>
+        <v>13.28513591671486</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>12.99407114624506</v>
+        <v>13.84643993553452</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>14.30942937158642</v>
+        <v>15.17113095238096</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>17.10313939240292</v>
+        <v>17.89538970436222</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>12.97120468637073</v>
+        <v>13.82413764579368</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>11.70877513401992</v>
+        <v>12.61015266228125</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>6.818402879097356</v>
+        <v>7.756993875186225</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>8.191832280007112</v>
+        <v>9.110402781802371</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>7.017031630170308</v>
+        <v>7.925465838509318</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>5.491924014628204</v>
+        <v>6.334755415648424</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2051 +5824,2051 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.002488</t>
+          <t>X &lt; -0.002473</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.713310881547912</v>
+        <v>-7.828341013824883</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-11.94663840453541</v>
+        <v>-10.93139070667161</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-13.3846574535664</v>
+        <v>-12.18608480856319</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.54688683532797</v>
+        <v>-14.20705843594284</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.187025133962202</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.10150822322715</v>
+        <v>-2.897111541472661</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.322732269436337</v>
+        <v>-5.120764982276818</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-3.702392989551726</v>
+        <v>-2.568542568542576</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-6.559456532274709</v>
+        <v>-5.297756516001328</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-8.781647570630035</v>
+        <v>-8.95095086836352</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-11.4061386531058</v>
+        <v>-11.53585871090204</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.786337331916108</v>
+        <v>-7.526726379659053</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-4.112397949496867</v>
+        <v>-2.927332782824109</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.333476825943457</v>
+        <v>-3.175566844257219</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-9.339446210480538</v>
+        <v>-8.143435511856566</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-10.19433465085638</v>
+        <v>-9.010702921608328</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-10.32825178783386</v>
+        <v>-9.114583333333336</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-10.43309249165504</v>
+        <v>-9.247467438494937</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-11.66647647304956</v>
+        <v>-10.46157663992059</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-12.92890602540037</v>
+        <v>-11.67556162343304</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-12.02217683104756</v>
+        <v>-10.81443469624234</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-12.09802279245666</v>
+        <v>-10.88959721819763</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-6.02644663069924</v>
+        <v>-4.931677018633536</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-3.203728159284843</v>
+        <v>-2.236673155780146</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.002314</t>
+          <t>X &lt; -0.002299</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-6.832336475134092</v>
+        <v>-7.709293394777269</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.230943060717955</v>
+        <v>-7.95520023048114</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.73279189698299</v>
+        <v>-10.25156099903938</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-13.57340549089381</v>
+        <v>-12.92729653118094</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.398557665568745</v>
+        <v>-4.869521337946942</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-1.436711589286055</v>
+        <v>-0.5459210652821866</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-2.208660273176406</v>
+        <v>-1.341003077514905</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-0.3363340835208746</v>
+        <v>0.437409812409804</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.445384536014778</v>
+        <v>-2.559661277906088</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-7.519375480868469</v>
+        <v>-7.52237943979209</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-8.320584655910849</v>
+        <v>-8.291811091854427</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-5.373527607745942</v>
+        <v>-5.443393046325717</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-1.120345588580548</v>
+        <v>-1.34995183044316</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.341424465027139</v>
+        <v>-1.59818589187627</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-5.225374214220608</v>
+        <v>-5.405340273761325</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-4.630987292277617</v>
+        <v>-4.844036254941663</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-5.840173246459393</v>
+        <v>-5.989583333333336</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-8.095551584689176</v>
+        <v>-8.205800771828272</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-6.804391386560546</v>
+        <v>-6.949671878015828</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-9.843352028205423</v>
+        <v>-9.860085432956851</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-8.235360561762853</v>
+        <v>-8.344196601004249</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-9.386475340376251</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-3.7356565418727</v>
+        <v>-4.009057971014485</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.5856823434830645</v>
+        <v>-1.046196965303949</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.00214</t>
+          <t>X &lt; -0.002126</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-5.426561399146252</v>
+        <v>-4.846974554197551</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.439909626067497</v>
+        <v>-6.832011824684031</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-9.877928675098488</v>
+        <v>-8.086705926575611</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-14.1623112659698</v>
+        <v>-12.65317372416339</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-7.355244595659933</v>
+        <v>-5.911188004613606</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.122268113552252</v>
+        <v>-1.368289486334817</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.092414995640802</v>
+        <v>-0.4089855336552617</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.5688246385920763</v>
+        <v>1.040479987848407</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.329139258479174</v>
+        <v>-1.463170049835902</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.804757637218373</v>
+        <v>-4.890800492423672</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.332499796858251</v>
+        <v>-6.372951442731612</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-4.007645596702638</v>
+        <v>-3.140761467378347</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-2.428104960856054</v>
+        <v>-1.624074637460701</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.748282936401743</v>
+        <v>-0.9951157164376667</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-5.109128936685003</v>
+        <v>-4.30884904569114</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-5.415642915642913</v>
+        <v>-4.624738009327622</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-5.549560052620386</v>
+        <v>-4.72861842105263</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-8.357103459144277</v>
+        <v>-7.493081473582649</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-7.24031117731905</v>
+        <v>-6.401426263980746</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-7.954366268251924</v>
+        <v>-7.064032801377891</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-7.596011535317054</v>
+        <v>-6.754284320302496</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.671857496726155</v>
+        <v>-6.829446842257781</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-4.694680081541392</v>
+        <v>-3.954233409610971</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-2.067809632061966</v>
+        <v>-1.484793456532017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.001966</t>
+          <t>X &lt; -0.001952</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.418624891209745</v>
+        <v>-6.282352755507858</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.447846134004003</v>
+        <v>-7.213191098061046</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.108087405257216</v>
+        <v>-5.728159172555365</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-9.598819202477735</v>
+        <v>-8.739078140376343</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-7.15683189724723</v>
+        <v>-6.605632449058049</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.030666021950168</v>
+        <v>-0.1986988430599652</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.103314006539811</v>
+        <v>-0.299336410848241</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-1.381525451292887</v>
+        <v>-0.6042568542568603</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-4.836541765881684</v>
+        <v>-4.642994611239416</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-6.308758141218874</v>
+        <v>-6.133490550903204</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-7.433299897658344</v>
+        <v>-7.250144425187756</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.914846503903547</v>
+        <v>-4.748948601881274</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-3.240805773556865</v>
+        <v>-3.086062941554268</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.363982552101362</v>
+        <v>-1.250963669654048</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-5.518629346185421</v>
+        <v>-5.405340273761325</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-4.924242424242429</v>
+        <v>-4.844036254941663</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-5.058159561219902</v>
+        <v>-4.947916666666671</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-8.65950376154457</v>
+        <v>-8.553022994050494</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-7.744311681319552</v>
+        <v>-7.644116322460278</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-8.256766570652218</v>
+        <v>-8.123974321845736</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-10.19791413721965</v>
+        <v>-10.08030771211536</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-9.574459399328049</v>
+        <v>-9.461025789626198</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-7.202082588943902</v>
+        <v>-7.134057971014485</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-5.180012744265085</v>
+        <v>-5.21286363197062</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.001791</t>
+          <t>X &lt; -0.001778</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-4.739748212333069</v>
+        <v>-4.617895545314902</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.173426109583978</v>
+        <v>-5.401436789620917</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-5.96309351026332</v>
+        <v>-5.043227665706048</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-7.774948628607163</v>
+        <v>-7.527521756406159</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-3.715134705550035</v>
+        <v>-3.193796700265779</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.4743162943297179</v>
+        <v>0.5298986068489526</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.6937787903747648</v>
+        <v>0.281264682047933</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.524476422973144</v>
+        <v>-0.5701038487923853</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.797906368130263</v>
+        <v>-4.81375963856182</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-5.570822044166754</v>
+        <v>-5.609811133781157</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-7.506707153386039</v>
+        <v>-7.523368468903605</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-5.023025617607523</v>
+        <v>-4.521261898784729</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.831270557391818</v>
+        <v>-2.903913579077042</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-1.947377058147801</v>
+        <v>-2.05925146564676</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-5.920437482800189</v>
+        <v>-6.020094372121974</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-5.326050560857198</v>
+        <v>-4.91234226587062</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-4.354995322144049</v>
+        <v>-3.923326502732245</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-8.327239340882365</v>
+        <v>-7.881347219915703</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-8.111347959958039</v>
+        <v>-7.66688499276993</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-6.819529774299404</v>
+        <v>-6.359402372847555</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-8.467048317956042</v>
+        <v>-8.01974304909168</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-7.146331971200624</v>
+        <v>-7.002009396183574</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-5.205190592051906</v>
+        <v>-5.119030648610114</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-5.281022845275182</v>
+        <v>-4.734721555467878</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.001617</t>
+          <t>X &lt; -0.001605</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.836925544804515</v>
+        <v>-4.507877693361564</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.95601606864453</v>
+        <v>-4.753784529065435</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-5.609721392185321</v>
+        <v>-5.430824564930852</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.538361686137868</v>
+        <v>-5.051972276965635</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.919080366188609</v>
+        <v>-2.786188004613606</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.1489390532666732</v>
+        <v>0.324176973933497</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.055396847823211</v>
+        <v>1.097722412681165</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-1.1990991819101</v>
+        <v>-1.167982344452938</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-3.133896584975631</v>
+        <v>-3.392994611239416</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-4.697326095004215</v>
+        <v>-4.973359831948947</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.609037203830439</v>
+        <v>-5.877595405579918</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-3.911502022298194</v>
+        <v>-4.193393046325717</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-3.453636421170124</v>
+        <v>-3.739657712796095</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.69843071263648</v>
+        <v>-2.027107460503721</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.332858595197273</v>
+        <v>-4.67004615611426</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-4.528985507246368</v>
+        <v>-4.893055862784799</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-3.081874976239661</v>
+        <v>-3.428308823529413</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-5.953514099033171</v>
+        <v>-6.306290967906698</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-6.132879635104892</v>
+        <v>-6.483985603506021</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-5.155519991144772</v>
+        <v>-5.485085432956843</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-6.093323076106849</v>
+        <v>-6.444686797082674</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-5.162204987073636</v>
+        <v>-5.735535593547766</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.872742606217471</v>
+        <v>-4.707587382779195</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-3.550168484938752</v>
+        <v>-4.477569514323555</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.001443</t>
+          <t>X &lt; -0.001431</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.969706173834652</v>
+        <v>-3.377610226460433</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.953550065464633</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-5.749213430611427</v>
+        <v>-5.705479321335183</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-5.455456040658198</v>
+        <v>-5.137290994082377</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-3.263734254149583</v>
+        <v>-2.911188004613606</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.8700158613000042</v>
+        <v>0.09858841074902358</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.4372004590703398</v>
+        <v>-0.3620454409485774</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.410327158060696</v>
+        <v>-2.339206687032785</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.724772179535826</v>
+        <v>-3.883518580024258</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-5.514637008114683</v>
+        <v>-5.348466396313832</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-5.579560416800227</v>
+        <v>-5.745127702779733</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-2.807462362621109</v>
+        <v>-2.67722805189986</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-2.235709175239926</v>
+        <v>-2.119879366675043</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7618727974492359</v>
+        <v>-0.6958726254325711</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-2.775948298419628</v>
+        <v>-2.715819649458098</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-3.537493579866464</v>
+        <v>-3.492308272778899</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-2.993444615149023</v>
+        <v>-2.927292363433672</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.45421752236004</v>
+        <v>-4.397969110735744</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-4.57730919228316</v>
+        <v>-4.852403204660206</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-3.373514229772766</v>
+        <v>-3.634472277995869</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-3.916060397738796</v>
+        <v>-4.201916779376603</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-3.801660769386572</v>
+        <v>-4.277079301331888</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-2.653048005779624</v>
+        <v>-3.364548494983275</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-2.728880259002899</v>
+        <v>-3.526687489272739</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.001269</t>
+          <t>X &lt; -0.001258</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.5335024806636071</v>
+        <v>-0.6815913057672702</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.715736906132065</v>
+        <v>-1.329517170371844</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.153755955163057</v>
+        <v>-2.440487939678654</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.584224098899575</v>
+        <v>-2.338926567810972</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.504880370649808</v>
+        <v>-1.090251365495149</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5427605514764124</v>
+        <v>1.151822949450775</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.06731297053877938</v>
+        <v>0.08049784329541154</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.909626979394417</v>
+        <v>-2.283619735143283</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-3.437940367280284</v>
+        <v>-3.263724066456412</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.925955758416485</v>
+        <v>-3.505758941177135</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-4.221696686055132</v>
+        <v>-3.787540547071416</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.366542955600003</v>
+        <v>-0.7400227785510154</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.4954030281541293</v>
+        <v>-0.1928650345059495</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.7080195199007164</v>
+        <v>0.9439424553074787</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.8048246323807078</v>
+        <v>-0.5692368573254925</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-1.91983941983942</v>
+        <v>-1.94699101025099</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-1.199055702116041</v>
+        <v>-1.219846491228068</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-1.873696975737793</v>
+        <v>-2.183755527137599</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-2.797406734414608</v>
+        <v>-3.077326540989056</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-2.040760354646011</v>
+        <v>-2.308723475431449</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-2.298406237711752</v>
+        <v>-2.599159666562876</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-2.209824034692687</v>
+        <v>-2.674322188518161</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-1.196912973459092</v>
+        <v>-1.876671082741176</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.9862122753929725</v>
+        <v>-1.761801766781325</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.001095</t>
+          <t>X &lt; -0.001084</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.302317046616821</v>
+        <v>-1.481889200995631</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.9689423973051632</v>
+        <v>-1.61462052033621</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.070658551013217</v>
+        <v>-1.448456423875982</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.8927439735739995</v>
+        <v>-1.05047702608632</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1.573326832911505</v>
+        <v>0.9815909888218357</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.784981417858354</v>
+        <v>2.579078934717813</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.472809421601553</v>
+        <v>1.252861391349555</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.3749087496089274</v>
+        <v>-0.46659165601897</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.230282554241313</v>
+        <v>-1.097188871725074</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.22741347691457</v>
+        <v>-2.212644926517754</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.056492848205558</v>
+        <v>-1.055454159701029</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.2141660184696974</v>
+        <v>-0.2258414239068429</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.129039627678665</v>
+        <v>1.092894777226462</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.804821737779164</v>
+        <v>1.729616468005744</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.4740327002882907</v>
+        <v>0.3837452719613879</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.2768718575893416</v>
+        <v>-0.1611453994844325</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.7102872386170347</v>
+        <v>1.062407817109147</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.2914144517512227</v>
+        <v>-0.1766709783179508</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-0.7481688107372122</v>
+        <v>-0.6259255653314639</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.3371077541324183</v>
+        <v>-0.1901001822193891</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-0.4312234288249002</v>
+        <v>-0.3150668074939276</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.5982670523491862</v>
+        <v>-0.6114682675023033</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.4855000986387807</v>
+        <v>0.2958830319353609</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.9968803400772117</v>
+        <v>0.576221913752093</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.0009204</t>
+          <t>X &lt; -0.0009103</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.294348011098037</v>
+        <v>-2.408246274358419</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.013325886647138</v>
+        <v>-1.515806291087195</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.733212081100028</v>
+        <v>-2.153560415268217</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.3712012968022762</v>
+        <v>-0.547910566268655</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.096171105755772</v>
+        <v>1.909550132469001</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.110860321742244</v>
+        <v>3.224618840821101</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.265469109078744</v>
+        <v>2.180822319310494</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.083098532318438</v>
+        <v>1.272951626308512</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6837325497813325</v>
+        <v>-0.6201332543072624</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.179975531423601</v>
+        <v>-2.203230503621874</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.8209249308529962</v>
+        <v>-0.9446382084914902</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.1955152022937625</v>
+        <v>-0.3331206958224655</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>1.212968300470372</v>
+        <v>1.038665694719654</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2685621184179965</v>
+        <v>-0.09766783385376954</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>0.3337461264432235</v>
+        <v>-0.06934264202656948</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.02397391637897783</v>
+        <v>-0.3961380903472218</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>1.879206869817416</v>
+        <v>1.453800325636472</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.3277115547846634</v>
+        <v>-0.1000429269496479</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-0.5413880226996852</v>
+        <v>-0.9513000603722475</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.007121440071230722</v>
+        <v>-0.2038539350290733</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-0.3545929014933549</v>
+        <v>-0.593678542981749</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.3226604736160823</v>
+        <v>-0.668841064937034</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.7859366513439454</v>
+        <v>0.2852729940535994</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.001805437553102</v>
+        <v>0.3007538931921943</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.0007462</t>
+          <t>X &lt; -0.0007367</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.25989473247958</v>
+        <v>-1.141496784607774</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5845705207283913</v>
+        <v>-0.7475151762614303</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.7893655041653744</v>
+        <v>-0.9355789404935848</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.3133451326243701</v>
+        <v>0.2508949581807656</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.943409648646487</v>
+        <v>1.759266540840933</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.650558413991256</v>
+        <v>2.424977464826874</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.673560281962388</v>
+        <v>1.28542142390959</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.08720930232558999</v>
+        <v>-0.07822261745229753</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.7433965390155279</v>
+        <v>-1.012042230287037</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-2.097707563889223</v>
+        <v>-2.1575725728393</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-1.159951702912778</v>
+        <v>-1.37621892375509</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4815247236429911</v>
+        <v>-0.8552773122271944</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1445843465271324</v>
+        <v>-0.248505154211685</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3680397194238267</v>
+        <v>-0.7836832615558436</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.5888652327478354</v>
+        <v>-1.035421574574336</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.5775686898135888</v>
+        <v>-1.048005647576765</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>0.6004675259786225</v>
+        <v>0.2828341702534658</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.3790087463556802</v>
+        <v>-0.710882072641283</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.8919803391922869</v>
+        <v>-1.213779960273115</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.1695010392888534</v>
+        <v>-0.1383613774809973</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.08149993917280085</v>
+        <v>-0.4188618329506824</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.3620659533579698</v>
+        <v>-0.7809684008170166</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>0.5842830921586213</v>
+        <v>0.03655417628345248</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.182292593150073</v>
+        <v>0.3048312508605591</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005719</t>
+          <t>X &lt; -0.0005631</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>862</v>
+        <v>881</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1630820051081372</v>
+        <v>-0.4106356766564545</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.09434537296900203</v>
+        <v>-0.5970442021123432</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.09935724652705602</v>
+        <v>-0.671030356289009</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9672245300419675</v>
+        <v>0.3688594733083974</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.758689294047159</v>
+        <v>1.95398053471223</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>3.128248458065237</v>
+        <v>2.513462136817544</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1.735638086143624</v>
+        <v>0.8830960215841941</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.424131578244733</v>
+        <v>-0.3717314878532463</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.1576574318249371</v>
+        <v>-0.8572534524734294</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7497601771576186</v>
+        <v>-1.477181699679093</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.870507850995331</v>
+        <v>-1.480913655956982</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2762325227290177</v>
+        <v>-0.6750842505537378</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4088801933633874</v>
+        <v>-0.8184892454091468</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.8609059520270677</v>
+        <v>-1.228104544922047</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.5952617207392663</v>
+        <v>-1.115707280950126</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.6937154454475447</v>
+        <v>-1.121940152028301</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>0.7889955930946115</v>
+        <v>0.3632827279606445</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.1067876837307011</v>
+        <v>-0.3371382670988012</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.4856350231047912</v>
+        <v>-0.6902129298508584</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.278577992405971</v>
+        <v>0.2054177830855295</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.2673431488468836</v>
+        <v>0.09200279362306674</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>0.02959395472530701</v>
+        <v>-0.3236818622709166</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>0.8370393551606625</v>
+        <v>0.4874895129053058</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.411423661556476</v>
+        <v>0.7793800305341136</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003977</t>
+          <t>X &lt; -0.0003895</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1119</v>
+        <v>1137</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2798577323830145</v>
+        <v>0.1095471849328788</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.08081347798894711</v>
+        <v>-0.002632780524649547</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2503596421896503</v>
+        <v>-0.3393949130928107</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.7638623837020901</v>
+        <v>0.7723910596356873</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.158302202369619</v>
+        <v>1.854955101843643</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>3.016614131524683</v>
+        <v>2.935701933262202</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1.765738995374122</v>
+        <v>1.492621631109799</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.362361867062511</v>
+        <v>1.063503425708141</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.012267809635972</v>
+        <v>0.8043200414167373</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.7351748352185439</v>
+        <v>0.4969018923726765</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.617049752691301</v>
+        <v>0.2937152239350524</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>1.36890533144971</v>
+        <v>1.209006719550779</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>1.100089306429929</v>
+        <v>1.02446234647541</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.6118688449432668</v>
+        <v>0.564852806452663</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.6661031074695671</v>
+        <v>0.5863044052184492</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2809708842656349</v>
+        <v>0.09219945306185906</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.770384112381663</v>
+        <v>0.6039742744063261</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.3093546285070445</v>
+        <v>0.03133643133796227</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.3471516194046629</v>
+        <v>0.3337494060650883</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>1.246374989479548</v>
+        <v>1.33989257935626</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>1.203429617065275</v>
+        <v>1.300152563463655</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>1.538869733626413</v>
+        <v>1.488842284252435</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>1.511079249217943</v>
+        <v>1.292723031624035</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>1.400538072210665</v>
+        <v>0.8667317945904998</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.0002235</t>
+          <t>X &lt; -0.0002159</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1387</v>
+        <v>1403</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.6828998575517105</v>
+        <v>-0.9296323778281135</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.05265672205283067</v>
+        <v>-0.2196289701748881</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.8811661585286927</v>
+        <v>-0.9413889104019475</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8734030197444795</v>
+        <v>0.6984111829025679</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.436111475002789</v>
+        <v>1.100143440145601</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.594392753323206</v>
+        <v>2.147942624772149</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.435092468874537</v>
+        <v>0.8974720997900647</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.198773905510762</v>
+        <v>0.7752676311938203</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.4219989765300269</v>
+        <v>0.09185387360906816</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.4795754763830331</v>
+        <v>0.117990140875996</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.293144512203142</v>
+        <v>-0.06664513642530778</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.9900244871743453</v>
+        <v>0.6939141897359704</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.7001131206330555</v>
+        <v>0.5464156909243627</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.5509249702828001</v>
+        <v>0.4829200715354744</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.1803445770875669</v>
+        <v>0.2284207145969575</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-0.3755201185107708</v>
+        <v>-0.3506886664408242</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-0.2218743511029118</v>
+        <v>-0.2407415656925664</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.7580594115020958</v>
+        <v>-0.8012806958007062</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-0.6140587566741047</v>
+        <v>-0.5868184686549327</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-0.2115407684170734</v>
+        <v>-0.1584045111226757</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.1360335717419687</v>
+        <v>-0.01309063759250506</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.1910810357588133</v>
+        <v>0.1255743529254758</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.2206819663854986</v>
+        <v>0.2266571632216809</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.1159169929047437</v>
+        <v>-0.1493093435410628</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -4.931e-05</t>
+          <t>X &lt; -4.227e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1714</v>
+        <v>1744</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.05703208453022768</v>
+        <v>-0.07277462344620034</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5921652651652352</v>
+        <v>-0.4589945769049564</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.01549481266462</v>
+        <v>-0.8860522670727846</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.04016619287708068</v>
+        <v>0.3187860899016854</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3742290014266416</v>
+        <v>0.3601916989211702</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.637622211555467</v>
+        <v>1.404901334413566</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.189288982118853</v>
+        <v>0.7565996622111157</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.8288004966999196</v>
+        <v>0.5415169892611331</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.43948302233823</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.6298001047188038</v>
+        <v>0.5107823669546221</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3565846364122365</v>
+        <v>0.1869265130273519</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.004689761286073235</v>
+        <v>-0.1712598656350082</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.1627429748887153</v>
+        <v>-0.3369220480834727</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.209200198250322</v>
+        <v>-0.3225173149899234</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.459892971965921</v>
+        <v>-0.4550344633637664</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.7386143154478475</v>
+        <v>-0.7538221876633813</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.988945887815305</v>
+        <v>-0.972381498470952</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-1.384822680111448</v>
+        <v>-1.219944502715116</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-1.052516863797145</v>
+        <v>-0.9481428260280609</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.4582205299641586</v>
+        <v>-0.3895196837213746</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.4423231935098997</v>
+        <v>-0.3262302401479715</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.5418253666940274</v>
+        <v>-0.5160716611858334</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.4076525292077235</v>
+        <v>-0.2724371759074558</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3322350843520638</v>
+        <v>-0.4345761701969195</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0001249</t>
+          <t>X &lt; 0.0001313</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2006</v>
+        <v>2030</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4756641262905177</v>
+        <v>-0.4115112682280184</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5862127291988983</v>
+        <v>-0.4845688061052158</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.15621721823851</v>
+        <v>-1.027556754834357</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.108766371043032</v>
+        <v>-0.02563476407331677</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.07874237871357082</v>
+        <v>0.1182237600922775</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.7895266757834349</v>
+        <v>0.7440290736748096</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.6907252874994754</v>
+        <v>0.4673466117229026</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5900513589935912</v>
+        <v>0.4358756936076418</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4616853297634833</v>
+        <v>0.3463636074901189</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4129354657206363</v>
+        <v>0.1680382506256066</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.2687396135262929</v>
+        <v>-0.02300578211990967</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.2177633029976533</v>
+        <v>0.07288011320863319</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.2678746007951531</v>
+        <v>0.2166492194256051</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.002955519432532583</v>
+        <v>0.04663193185588455</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.5615963294509072</v>
+        <v>-0.4094453640733136</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.9124830393487073</v>
+        <v>-0.7348408526428045</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-1.046400176326181</v>
+        <v>-0.8387212643678126</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-1.549250830396119</v>
+        <v>-1.267171871992474</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-1.333359449471793</v>
+        <v>-1.101970728590537</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.9972599081604869</v>
+        <v>-0.7888621160438731</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-1.013022373930674</v>
+        <v>-0.814434696242337</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-1.009767119496324</v>
+        <v>-0.9388583019414725</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.8554148072985441</v>
+        <v>-0.6952238166630949</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-1.051489223917038</v>
+        <v>-0.9558849784402383</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0002991</t>
+          <t>X &lt; 0.000305</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2255</v>
+        <v>2278</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4072351468679543</v>
+        <v>-0.4244409452933269</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2784408131902296</v>
+        <v>-0.3417621851059209</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.8121458229880218</v>
+        <v>-0.8747422881416682</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.04080390080176244</v>
+        <v>-0.04611021385925085</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.434924138206469</v>
+        <v>0.3579251452334873</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7792524546349782</v>
+        <v>0.7142770699159442</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.6941386510804719</v>
+        <v>0.5997672183603342</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.5296701492230937</v>
+        <v>0.4510799786390294</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3317998263009656</v>
+        <v>0.2102147250114896</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3352162589392762</v>
+        <v>0.1833998947087849</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.01643110487866295</v>
+        <v>-0.1323170051264384</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1041399690590836</v>
+        <v>-0.2085843989403813</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2286476530396158</v>
+        <v>-0.2461779008801059</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5563830719355067</v>
+        <v>-0.5565192252095983</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.506561767746156</v>
+        <v>-0.4232574889141603</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8413783856261787</v>
+        <v>-0.7139513851728623</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.8867999473824142</v>
+        <v>-0.7739336406204274</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-1.212879589256687</v>
+        <v>-1.082410370891772</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-1.218227146385452</v>
+        <v>-0.999642612578306</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.9170500675891091</v>
+        <v>-0.7850561675193219</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.9908678619714237</v>
+        <v>-0.9574172624031405</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.9520229080391047</v>
+        <v>-1.032579784358425</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.8287130506807472</v>
+        <v>-0.7450471428025978</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.9228065358393565</v>
+        <v>-0.9071861370920615</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.0004733</t>
+          <t>X &lt; 0.0004786</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2468</v>
+        <v>2486</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.3021504119034049</v>
+        <v>-0.4438662323089204</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.2935313564497832</v>
+        <v>-0.4685335638144679</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3814368416501352</v>
+        <v>-0.5814429518204989</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.1762624639651875</v>
+        <v>-0.03114627764477973</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.4675077929667566</v>
+        <v>0.3162849629474707</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.5968076732381604</v>
+        <v>0.4957456013844777</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.4526300494042346</v>
+        <v>0.3644912444623785</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2782911338968219</v>
+        <v>0.242776024652521</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.1008936800283351</v>
+        <v>0.07270935987971683</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.1989448945423007</v>
+        <v>0.1020186340441924</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.02850759787413182</v>
+        <v>-0.1244920767333184</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.04149763055468014</v>
+        <v>-0.09700750415704107</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.009437303708203615</v>
+        <v>0.01647712362139941</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.206587581524019</v>
+        <v>-0.2081805328194619</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.2986168475639346</v>
+        <v>-0.2636032411919658</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.4725275398546671</v>
+        <v>-0.36227170680543</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.6064446768321403</v>
+        <v>-0.5466026414588399</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.6708486641147076</v>
+        <v>-0.5588109622278381</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.4549572831903816</v>
+        <v>-0.2638982121536628</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.5678535419333741</v>
+        <v>-0.4515643817366808</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.479587138439399</v>
+        <v>-0.4558552226186166</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.531397198371117</v>
+        <v>-0.5310177445739015</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.4758804799957375</v>
+        <v>-0.3276085207597248</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.6087736106272459</v>
+        <v>-0.4897475150491886</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.0006475</t>
+          <t>X &lt; 0.0006522</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2654</v>
+        <v>2669</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1228830415756832</v>
+        <v>-0.2465373426357331</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.287866517547414</v>
+        <v>-0.3980715667950889</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.1327440844082801</v>
+        <v>-0.2538128315651633</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.4488994603589447</v>
+        <v>0.3300673763507618</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4716455307054588</v>
+        <v>0.3364807756922517</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.7549499368941426</v>
+        <v>0.6263426163098487</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.6420524049931373</v>
+        <v>0.4868711292786756</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.798245996771243</v>
+        <v>0.6886856401419479</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.5987886694487514</v>
+        <v>0.501912623227021</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7488481653547652</v>
+        <v>0.6241078546772698</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6317755227889776</v>
+        <v>0.5442480981767375</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.4877178614567583</v>
+        <v>0.438868235150224</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.4767924177255409</v>
+        <v>0.4679961680603952</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.3157592931162228</v>
+        <v>0.316734267804371</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.1465215991460482</v>
+        <v>0.1808945945776301</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.06396230070543396</v>
+        <v>0.1278738574178888</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.06995483627203924</v>
+        <v>0.04615102410390648</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.2500117868025029</v>
+        <v>-0.08673308105769451</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.034120405878177</v>
+        <v>0.1277291460880789</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.1750950214802529</v>
+        <v>0.3048483749612245</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>0.2571182222161639</v>
+        <v>0.3743465487397231</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>0.2415529016240114</v>
+        <v>0.3366512429702766</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>0.2373706132211666</v>
+        <v>0.3554824311336375</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>0.1087452197001255</v>
+        <v>0.1933434368441738</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.0008218</t>
+          <t>X &lt; 0.0008258</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2803</v>
+        <v>2820</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.4516196152037608</v>
+        <v>-0.5454476025816817</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.09402164308273342</v>
+        <v>-0.243560018840931</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.05903303173475649</v>
+        <v>-0.2090709966869966</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.3118563719970595</v>
+        <v>0.1709356137772886</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.315469183109208</v>
+        <v>0.162258323070013</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.5225908028721591</v>
+        <v>0.3389988687811609</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.2324595948587813</v>
+        <v>0.02310175169592554</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.5785038622000087</v>
+        <v>0.4097940471217214</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.4984217780370841</v>
+        <v>0.3458078404343183</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.5992290013932262</v>
+        <v>0.418901069581807</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4318434938008266</v>
+        <v>0.2516248600210176</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.3516763720109992</v>
+        <v>0.2077868946772341</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.2813304532056975</v>
+        <v>0.1756619561479695</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1170213140929732</v>
+        <v>0.0191095385169362</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.04272397707961062</v>
+        <v>-0.1106320290176441</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>0.01766508085482599</v>
+        <v>-0.02452780640095398</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.2942513441254988</v>
+        <v>-0.2847960992907801</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.470291763147813</v>
+        <v>-0.4176802044523811</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.1620790990869665</v>
+        <v>-0.1322959914910058</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>0.08152855068529163</v>
+        <v>0.1177514464757792</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>0.2372672174200119</v>
+        <v>0.2240658103432764</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>0.1828421226793537</v>
+        <v>0.1489032883879915</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>0.1934462759144893</v>
+        <v>0.1797718162195565</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.03941662971248405</v>
+        <v>-0.0887501567933171</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.000996</t>
+          <t>X &lt; 0.0009994</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2918</v>
+        <v>2948</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.3233921967936624</v>
+        <v>-0.456623355429322</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.02735978652651028</v>
+        <v>-0.1448088674581953</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.01706864967412258</v>
+        <v>-0.09891446962100048</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.5150923930414848</v>
+        <v>0.3738232077342118</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.6415307754765962</v>
+        <v>0.5224492800875069</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8138766201384939</v>
+        <v>0.6308807365196145</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5387193777370101</v>
+        <v>0.3955774113889987</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.894063897966312</v>
+        <v>0.7184273918553785</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.6824700990871975</v>
+        <v>0.561463736184777</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.8849696327136769</v>
+        <v>0.7658478944433611</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.7353153723567161</v>
+        <v>0.6178758793807688</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.7497757590793697</v>
+        <v>0.6655552723382385</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.8083053476417135</v>
+        <v>0.7217407985217292</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.5393772459952757</v>
+        <v>0.4597409373920271</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.482924655368592</v>
+        <v>0.3737741507275487</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.5850225925465296</v>
+        <v>0.5147208072052365</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>0.3485062763624924</v>
+        <v>0.3292959477789097</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>0.1752661197369321</v>
+        <v>0.2504972833503842</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>0.3774331492860412</v>
+        <v>0.4310382079181352</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>0.4478758095548443</v>
+        <v>0.5099394426650434</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>0.6447180679596229</v>
+        <v>0.6548422954227107</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>0.5895888811585905</v>
+        <v>0.5796797734674257</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>0.644986409204229</v>
+        <v>0.653707745855705</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>0.4870070077443884</v>
+        <v>0.457647448988233</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.00117</t>
+          <t>X &lt; 0.001173</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3014</v>
+        <v>3039</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.06824256947410845</v>
+        <v>-0.124242691473377</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1086975638440393</v>
+        <v>0.007277954510144014</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.1053026734541049</v>
+        <v>-0.01867774753910822</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.3005618859277419</v>
+        <v>0.1600479350927984</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2471410668147485</v>
+        <v>0.132048156539355</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3868478625821936</v>
+        <v>0.2418137534159328</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.06249478051609003</v>
+        <v>-0.07604896410946793</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.16616777956866</v>
+        <v>0.03098904738249075</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.1936212041954519</v>
+        <v>0.07918205870701911</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.3974154738054665</v>
+        <v>0.2532111113890068</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.459534060586904</v>
+        <v>0.3146734284387591</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.5305012745572455</v>
+        <v>0.4181193196186825</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.5176176212301584</v>
+        <v>0.4388412730051243</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.3493504112315975</v>
+        <v>0.2757190577514237</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.240249551959117</v>
+        <v>0.1716670654872274</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.2589595491647074</v>
+        <v>0.1937678213239522</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.1117119443020584</v>
+        <v>0.04358832072782803</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.07269322109165444</v>
+        <v>-0.1027305963896765</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.2291987433336402</v>
+        <v>0.1775211044403022</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.3695640238692306</v>
+        <v>0.326318075815081</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.5759987248602627</v>
+        <v>0.5154525218027715</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>0.4538743359022277</v>
+        <v>0.3941897417986127</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.5493699386280326</v>
+        <v>0.4732964218779117</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>0.4603323121383696</v>
+        <v>0.3769685496680779</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.001344</t>
+          <t>X &lt; 0.001347</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3099</v>
+        <v>3121</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.05340316724362992</v>
+        <v>-0.149826473252368</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.07756416896157248</v>
+        <v>-0.06004408006685935</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1953313981615921</v>
+        <v>0.04124794793756337</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2696838789942433</v>
+        <v>0.1041660538530778</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2726991411677062</v>
+        <v>0.133469092675071</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4137028911386764</v>
+        <v>0.2444692771981352</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.1413335153862718</v>
+        <v>-0.02204627359959943</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.2025084922916207</v>
+        <v>0.04229486988107567</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.2945827294046595</v>
+        <v>0.1564571081260624</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.3753704510369289</v>
+        <v>0.2411988349682943</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.3790034801977242</v>
+        <v>0.244262733648938</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4725337147206474</v>
+        <v>0.3696930576810971</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.3328231698469963</v>
+        <v>0.2646814709106451</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2595467008907448</v>
+        <v>0.1952402117705603</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.2319264043703342</v>
+        <v>0.1719930595720101</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.234197462230938</v>
+        <v>0.1762368991343095</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.02291519145820331</v>
+        <v>-0.03677353506243719</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.1915465979352433</v>
+        <v>-0.2147960739850134</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.1401685291915911</v>
+        <v>0.09575840171938665</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.3462321064682712</v>
+        <v>0.3103448467783707</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.499898688252749</v>
+        <v>0.4475768348274869</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>0.3790182742399182</v>
+        <v>0.3275035279002267</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4471391570520353</v>
+        <v>0.3788919382026421</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>0.4229676893058638</v>
+        <v>0.3449169938971579</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.001519</t>
+          <t>X &lt; 0.00152</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3141</v>
+        <v>3163</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.02539814573364652</v>
+        <v>-0.03964212239272769</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.0078717777318289</v>
+        <v>-0.1116008171142795</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1840799993390334</v>
+        <v>0.0652287945265897</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.2796035891845321</v>
+        <v>0.1505336574983076</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2781188763111402</v>
+        <v>0.1441753171857059</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3564242540290081</v>
+        <v>0.2243484962869289</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.1407237796132321</v>
+        <v>0.01345867885903118</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.2607347275526593</v>
+        <v>0.1356675789925106</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.3521542022819659</v>
+        <v>0.2185539451910259</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.4215954988019632</v>
+        <v>0.2911051222747076</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.4288442992987882</v>
+        <v>0.2979173460067059</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.4857155094082231</v>
+        <v>0.3862622710345107</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.3646306681739944</v>
+        <v>0.2987788538835545</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.2259223066070533</v>
+        <v>0.1637752017094343</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.1581383305822612</v>
+        <v>0.09981382321985421</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.2317955676164587</v>
+        <v>0.1749031389977276</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.02154472432936672</v>
+        <v>-0.03659154299547396</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1914544927326745</v>
+        <v>-0.2455723026768624</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.01156880183366127</v>
+        <v>-0.04406366316591459</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.280927849395141</v>
+        <v>0.2337139351316182</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.3616598765528352</v>
+        <v>0.2981809661363499</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>0.304970747362681</v>
+        <v>0.2734874847100883</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>0.3439995911293678</v>
+        <v>0.2830829289749772</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>0.3509414972908829</v>
+        <v>0.2790217089504452</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.001693</t>
+          <t>X &lt; 0.001694</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3189</v>
+        <v>3212</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.0916565779400571</v>
+        <v>-0.1103447244000222</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.0262446649855832</v>
+        <v>-0.03041417006253511</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.06922308280093858</v>
+        <v>8.91659771156128e-05</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3395918636210808</v>
+        <v>0.2603775635265819</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.2707796294914786</v>
+        <v>0.1878832028167352</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.3195272833413654</v>
+        <v>0.2383129596997478</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.018197665979514</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2095200087073295</v>
+        <v>0.1336576173886357</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.2689644632200512</v>
+        <v>0.1862573003125547</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.2945355366923579</v>
+        <v>0.2140546687350451</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.305744318587621</v>
+        <v>0.2250416790306105</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.3575443354976073</v>
+        <v>0.2765624816502879</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.2526382823871884</v>
+        <v>0.1727824960621192</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1126589683038404</v>
+        <v>0.03594688262440116</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.06724819091163425</v>
+        <v>-0.006789549123638494</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.1486952730305902</v>
+        <v>0.07596995816799534</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.02914602156806012</v>
+        <v>-0.1027747565775812</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.2405361876474217</v>
+        <v>-0.3105697076898437</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.00602617221375823</v>
+        <v>-0.07778133075214555</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.2620869528990752</v>
+        <v>0.2173510626367303</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.3021121522803227</v>
+        <v>0.259438536933942</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.2451161990002859</v>
+        <v>0.2339633171276176</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>0.2876690387387626</v>
+        <v>0.2471167902972624</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.2933473857272304</v>
+        <v>0.2406440475644658</v>
       </c>
     </row>
     <row r="31">
@@ -7878,79 +7878,79 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3244</v>
+        <v>3268</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1667118211148519</v>
+        <v>-0.1545987730817231</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.02583824123676948</v>
+        <v>-0.04993174010625978</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.007823665253816614</v>
+        <v>-0.04170744679452554</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.2153147844503707</v>
+        <v>0.1733725685757577</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.1113177264800882</v>
+        <v>0.06690752322332827</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1930030128776679</v>
+        <v>0.1495800505628111</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.02101398071366134</v>
+        <v>-0.01965604555143585</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.06705664146098655</v>
+        <v>0.02759454647396353</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.1261543290635672</v>
+        <v>0.08146980139130733</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.1382018969013856</v>
+        <v>0.09492708062229127</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1230982635909044</v>
+        <v>0.07993786679639925</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.04640845735141141</v>
+        <v>0.003761425218996806</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.01636716103542568</v>
+        <v>-0.0261869631055518</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.2172497520188301</v>
+        <v>-0.2565395628138276</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-0.1501582845080804</v>
+        <v>-0.1884243954173073</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-0.1216034887621618</v>
+        <v>-0.1584440693494713</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-0.2372652909254356</v>
+        <v>-0.2748886768447889</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.2930701951110066</v>
+        <v>-0.3287136205352539</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.1820063350806862</v>
+        <v>-0.2184619788407645</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.02310011438687809</v>
+        <v>-0.01646277607013502</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>0.05318370242145676</v>
+        <v>0.04550328689955307</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>0.02659881540853348</v>
+        <v>0.019096534532828</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>0.1038318356145922</v>
+        <v>0.09738385625175283</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>0.0772454106502849</v>
+        <v>0.04519430356589993</v>
       </c>
     </row>
     <row r="32">
@@ -7960,79 +7960,79 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3284</v>
+        <v>3309</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1784945280071142</v>
+        <v>-0.1812821902954695</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1038755754236433</v>
+        <v>-0.1109592618030604</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.01273524523032421</v>
+        <v>-0.02821265069103873</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.07800350400599143</v>
+        <v>0.05677025564193627</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.02884219091965434</v>
+        <v>-0.05181300461360649</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.08436068362772176</v>
+        <v>0.06179609732676994</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.03434359494595896</v>
+        <v>-0.05504897849706225</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.03805496828752553</v>
+        <v>0.01792359687095768</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.09693033946069107</v>
+        <v>0.07270935987971683</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.1297699771151954</v>
+        <v>0.1062693715229841</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.08784138144471854</v>
+        <v>0.0647261347159187</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.03902850458311491</v>
+        <v>0.01618238276189743</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.06498311366743792</v>
+        <v>-0.08740162963994891</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1466813348001494</v>
+        <v>-0.1673457793925834</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-0.1187452946159695</v>
+        <v>-0.1386133298191936</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-0.08330571817813848</v>
+        <v>-0.102050524864282</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-0.1687918641949508</v>
+        <v>-0.1881659630076484</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.2555672725017004</v>
+        <v>-0.2731084641359587</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.1128127454727874</v>
+        <v>-0.1313757605344321</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.03126534876655995</v>
+        <v>0.01043725544239038</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>0.08480588082132812</v>
+        <v>0.06461982411652656</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>0.05763096922001409</v>
+        <v>0.03761510436353177</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>0.04595096045950697</v>
+        <v>0.02732168658873491</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>0.1100990927407892</v>
+        <v>0.09463107942255533</v>
       </c>
     </row>
     <row r="33">
@@ -8042,243 +8042,243 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3308</v>
+        <v>3333</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.05333585555145248</v>
+        <v>-0.05633352191274099</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.0717200078778788</v>
+        <v>-0.07765427916468326</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.05167239908252697</v>
+        <v>-0.06409826797199969</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.06330686589833334</v>
+        <v>0.045849407779194</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.01491943027506437</v>
+        <v>-0.004266763563485654</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.09860158356519122</v>
+        <v>0.07982498067424615</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.03533681632153218</v>
+        <v>0.01782776825623955</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.01511208126940744</v>
+        <v>-0.03132463568415034</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.07371499511236834</v>
+        <v>0.05383931946547449</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.1007264139610555</v>
+        <v>0.08144488049473608</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.06107263736459601</v>
+        <v>0.04214487546975221</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.04070998779752699</v>
+        <v>0.02185359044557345</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.1008002533163364</v>
+        <v>-0.1188912243825513</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1835174475856221</v>
+        <v>-0.2000529773284612</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-0.1605566079498786</v>
+        <v>-0.1764354263645487</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-0.1512409986475163</v>
+        <v>-0.1660456333712688</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-0.267264182089221</v>
+        <v>-0.2822480039920237</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.3542001333682876</v>
+        <v>-0.3675632755719036</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.241129683721617</v>
+        <v>-0.2552940070351966</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.1571668949655916</v>
+        <v>-0.1729288052473308</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.01739697995830625</v>
+        <v>-0.03334528205940757</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.07516715079108849</v>
+        <v>-0.09071094704749072</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.08481182706751866</v>
+        <v>-0.099214939620758</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.02171880120692293</v>
+        <v>-0.03359570517793742</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.00239</t>
+          <t>X &lt; 0.002388</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3330</v>
+        <v>3355</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.01722647519755327</v>
+        <v>-0.01983217512066204</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.06750935330922658</v>
+        <v>-0.07221730678159588</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.0324925211329159</v>
+        <v>0.02193821107120897</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.08235824362508026</v>
+        <v>0.06807383918943088</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.002228850571349028</v>
+        <v>-0.01314413976476203</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.08658590175337366</v>
+        <v>0.07142007514671178</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.01865932935643144</v>
+        <v>0.004637491880110645</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.03329209469132621</v>
+        <v>-0.04618803194893673</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.02532282692461507</v>
+        <v>0.009577099937629896</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.0127515162648848</v>
+        <v>-0.02757385950120295</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.0503747163484789</v>
+        <v>-0.06487126604286431</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.07247164357536917</v>
+        <v>-0.08686893980160448</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.1905486376966152</v>
+        <v>-0.2043041774425589</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.2143238275923309</v>
+        <v>-0.2271482494790362</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-0.2557580455782684</v>
+        <v>-0.2676074160522504</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-0.2126568258982928</v>
+        <v>-0.2239054193781769</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-0.328816384169194</v>
+        <v>-0.3400443684314922</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4158888632534214</v>
+        <v>-0.4256882061236169</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2721736244738437</v>
+        <v>-0.2830052113491632</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1875412548762085</v>
+        <v>-0.1997822673321608</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.1122901902095634</v>
+        <v>-0.1243981098388787</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1401961835522272</v>
+        <v>-0.1521190276363242</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1179628659769847</v>
+        <v>-0.1291910659688043</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.08582765007998461</v>
+        <v>-0.09488052218422638</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.002564</t>
+          <t>X &lt; 0.002562</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3355</v>
+        <v>3379</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.0003607018433484654</v>
+        <v>0.01410460639851152</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.0072010808152001</v>
+        <v>-0.01023306396148627</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.05226855322982971</v>
+        <v>-0.04322766570604131</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.05118079752227089</v>
+        <v>0.05722097396763814</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.06049059447439475</v>
+        <v>-0.05480189513744449</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.05425557883269505</v>
+        <v>0.05969908975657034</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.04855619021616064</v>
+        <v>-0.04168034488828454</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.1022055424861747</v>
+        <v>-0.09431576441886591</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.07341172085253334</v>
+        <v>-0.06751828045960906</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1466507324507376</v>
+        <v>-0.1395324017726409</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.1820001285438479</v>
+        <v>-0.2041538591500114</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.2060417950988338</v>
+        <v>-0.2279944421774829</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2127880396567861</v>
+        <v>-0.2345388510921254</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.2083180086210632</v>
+        <v>-0.2294807674541204</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-0.2543335943747991</v>
+        <v>-0.2744862792709668</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-0.2666044927418696</v>
+        <v>-0.2861679348944222</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-0.2936795439141804</v>
+        <v>-0.3136382654065812</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-0.3511206837476308</v>
+        <v>-0.3700671430739604</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-0.2663729533808237</v>
+        <v>-0.2859602940914812</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-0.2405196440153006</v>
+        <v>-0.2609254171917428</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.1401041687485787</v>
+        <v>-0.1605528004917289</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1683754624130174</v>
+        <v>-0.1886211756066771</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.1442715084868098</v>
+        <v>-0.1641368664780032</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.1129486608075538</v>
+        <v>-0.1312319855268953</v>
       </c>
     </row>
   </sheetData>
